--- a/master Quotations_October_2026/Master_Quotation_Comparison Sheet.xlsx
+++ b/master Quotations_October_2026/Master_Quotation_Comparison Sheet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Purchase_List_October_2026\master Quotations_October_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93A47E85-2EAF-425F-AEA9-6BEA3001C17E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1D50ECD-8E41-4308-8EC5-610F72A81FFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" tabRatio="783" activeTab="5" xr2:uid="{EA74EA6A-41FE-42B7-B5E3-F15DF1371829}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" tabRatio="783" xr2:uid="{EA74EA6A-41FE-42B7-B5E3-F15DF1371829}"/>
   </bookViews>
   <sheets>
     <sheet name="Cutting &amp; Grinding wheels" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>USER:</t>
         </r>
@@ -64,7 +64,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -79,7 +79,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>USER:</t>
         </r>
@@ -88,7 +88,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="184">
   <si>
     <t>CUTTING &amp; GRINDING WHEEL  MASTER SUPPLIER QUOTATION COMPARISON SHEET - KRISHI INFRATECH</t>
   </si>
@@ -1320,9 +1320,6 @@
     <t xml:space="preserve">4" &amp; 7" Grinding wheels Total </t>
   </si>
   <si>
-    <t>4" &amp; 7" Cutting &amp; Grinding  wheels Total,  Each one 200 No's</t>
-  </si>
-  <si>
     <t xml:space="preserve">Total For Foam sheet &amp; bentonite Powder &amp;gum&amp; 4" &amp; 7" cutting wheels Ms Bolts &amp; Nuts </t>
   </si>
   <si>
@@ -1349,6 +1346,9 @@
   </si>
   <si>
     <t xml:space="preserve">Unit Rate (For Piece) </t>
+  </si>
+  <si>
+    <t>4" &amp; 7" Cutting &amp; Grinding  wheels Total</t>
   </si>
 </sst>
 </file>
@@ -1672,6 +1672,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1686,19 +1687,20 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1712,18 +1714,21 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF595959"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF1F497D"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2437,6 +2442,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2449,25 +2475,19 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2499,21 +2519,6 @@
     </xf>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2849,7 +2854,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D11C5405-7040-4163-93EF-7BD4AFBEFA7F}">
-  <dimension ref="A1:L47"/>
+  <dimension ref="A1:L48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.42578125" customWidth="1"/>
@@ -2869,15 +2874,15 @@
     <row r="1" spans="1:12">
       <c r="A1" s="4"/>
       <c r="B1" s="4"/>
-      <c r="C1" s="149" t="s">
+      <c r="C1" s="156" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="150"/>
-      <c r="G1" s="150"/>
-      <c r="H1" s="150"/>
-      <c r="I1" s="150"/>
+      <c r="D1" s="157"/>
+      <c r="E1" s="157"/>
+      <c r="F1" s="157"/>
+      <c r="G1" s="157"/>
+      <c r="H1" s="157"/>
+      <c r="I1" s="157"/>
       <c r="J1" s="4"/>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
@@ -2885,13 +2890,13 @@
     <row r="2" spans="1:12">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
-      <c r="C2" s="150"/>
-      <c r="D2" s="150"/>
-      <c r="E2" s="150"/>
-      <c r="F2" s="150"/>
-      <c r="G2" s="150"/>
-      <c r="H2" s="150"/>
-      <c r="I2" s="150"/>
+      <c r="C2" s="157"/>
+      <c r="D2" s="157"/>
+      <c r="E2" s="157"/>
+      <c r="F2" s="157"/>
+      <c r="G2" s="157"/>
+      <c r="H2" s="157"/>
+      <c r="I2" s="157"/>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
@@ -2938,10 +2943,10 @@
       <c r="A4" s="2">
         <v>1</v>
       </c>
-      <c r="B4" s="151" t="s">
+      <c r="B4" s="158" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="151"/>
+      <c r="C4" s="158"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -3109,13 +3114,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="4"/>
-      <c r="C9" s="152" t="s">
+      <c r="C9" s="159" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="152"/>
-      <c r="E9" s="152"/>
-      <c r="F9" s="152"/>
-      <c r="G9" s="152"/>
+      <c r="D9" s="159"/>
+      <c r="E9" s="159"/>
+      <c r="F9" s="159"/>
+      <c r="G9" s="159"/>
       <c r="H9" s="11"/>
       <c r="I9" s="12">
         <f>SUM(I5:I8)</f>
@@ -3129,10 +3134,10 @@
       <c r="A10" s="2">
         <v>7</v>
       </c>
-      <c r="B10" s="153" t="s">
+      <c r="B10" s="152" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="153"/>
+      <c r="C10" s="152"/>
       <c r="D10" s="6"/>
       <c r="E10" s="7"/>
       <c r="F10" s="8"/>
@@ -3292,13 +3297,13 @@
         <v>12</v>
       </c>
       <c r="B15" s="4"/>
-      <c r="C15" s="152" t="s">
+      <c r="C15" s="159" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="152"/>
-      <c r="E15" s="152"/>
-      <c r="F15" s="152"/>
-      <c r="G15" s="152"/>
+      <c r="D15" s="159"/>
+      <c r="E15" s="159"/>
+      <c r="F15" s="159"/>
+      <c r="G15" s="159"/>
       <c r="H15" s="11"/>
       <c r="I15" s="12">
         <f>SUM(I11:I14)</f>
@@ -3312,10 +3317,10 @@
       <c r="A16" s="2">
         <v>13</v>
       </c>
-      <c r="B16" s="153" t="s">
+      <c r="B16" s="152" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="153"/>
+      <c r="C16" s="152"/>
       <c r="D16" s="6"/>
       <c r="E16" s="7"/>
       <c r="F16" s="9"/>
@@ -3487,13 +3492,13 @@
         <v>18</v>
       </c>
       <c r="B21" s="4"/>
-      <c r="C21" s="157" t="s">
+      <c r="C21" s="153" t="s">
         <v>24</v>
       </c>
-      <c r="D21" s="157"/>
-      <c r="E21" s="157"/>
-      <c r="F21" s="157"/>
-      <c r="G21" s="157"/>
+      <c r="D21" s="153"/>
+      <c r="E21" s="153"/>
+      <c r="F21" s="153"/>
+      <c r="G21" s="153"/>
       <c r="H21" s="25"/>
       <c r="I21" s="12">
         <f>SUM(I17:I20)</f>
@@ -3524,11 +3529,11 @@
       <c r="B23" s="4"/>
       <c r="C23" s="26"/>
       <c r="D23" s="26"/>
-      <c r="E23" s="154" t="s">
+      <c r="E23" s="149" t="s">
         <v>177</v>
       </c>
-      <c r="F23" s="154"/>
-      <c r="G23" s="154"/>
+      <c r="F23" s="149"/>
+      <c r="G23" s="149"/>
       <c r="H23" s="127"/>
       <c r="I23" s="128">
         <f>I18+I20</f>
@@ -3556,10 +3561,10 @@
       <c r="A25" s="2">
         <v>20</v>
       </c>
-      <c r="B25" s="153" t="s">
+      <c r="B25" s="152" t="s">
         <v>39</v>
       </c>
-      <c r="C25" s="153"/>
+      <c r="C25" s="152"/>
       <c r="D25" s="26"/>
       <c r="E25" s="26"/>
       <c r="F25" s="26"/>
@@ -3647,7 +3652,7 @@
         <v>23</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C28" s="26"/>
       <c r="D28" s="6" t="s">
@@ -3755,14 +3760,14 @@
         <v>26</v>
       </c>
       <c r="B31" s="4"/>
-      <c r="C31" s="158" t="s">
+      <c r="C31" s="154" t="s">
         <v>24</v>
       </c>
-      <c r="D31" s="158"/>
-      <c r="E31" s="158"/>
-      <c r="F31" s="158"/>
-      <c r="G31" s="158"/>
-      <c r="H31" s="158"/>
+      <c r="D31" s="154"/>
+      <c r="E31" s="154"/>
+      <c r="F31" s="154"/>
+      <c r="G31" s="154"/>
+      <c r="H31" s="154"/>
       <c r="I31" s="12">
         <f>SUM(I26:I30)</f>
         <v>69997.600000000006</v>
@@ -3775,10 +3780,10 @@
       <c r="A32" s="2">
         <v>27</v>
       </c>
-      <c r="B32" s="153" t="s">
+      <c r="B32" s="152" t="s">
         <v>45</v>
       </c>
-      <c r="C32" s="153"/>
+      <c r="C32" s="152"/>
       <c r="D32" s="6"/>
       <c r="E32" s="26"/>
       <c r="F32" s="26"/>
@@ -3832,7 +3837,7 @@
         <v>29</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C34" s="26"/>
       <c r="D34" s="6" t="s">
@@ -3875,21 +3880,21 @@
         <v>15</v>
       </c>
       <c r="E35" s="26">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F35" s="26">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="G35" s="9">
         <f t="shared" si="2"/>
-        <v>13000</v>
+        <v>4500</v>
       </c>
       <c r="H35" s="26">
         <v>18</v>
       </c>
       <c r="I35" s="9">
         <f t="shared" ref="I35:I36" si="3">G35*(1+H35/100)</f>
-        <v>15340</v>
+        <v>5310</v>
       </c>
       <c r="J35" s="26" t="s">
         <v>46</v>
@@ -3943,49 +3948,49 @@
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
-      <c r="D37" s="159" t="s">
+      <c r="D37" s="155" t="s">
         <v>24</v>
       </c>
-      <c r="E37" s="159"/>
-      <c r="F37" s="159"/>
-      <c r="G37" s="159"/>
-      <c r="H37" s="159"/>
+      <c r="E37" s="155"/>
+      <c r="F37" s="155"/>
+      <c r="G37" s="155"/>
+      <c r="H37" s="155"/>
       <c r="I37" s="27">
         <f>SUM(I33:I36)</f>
-        <v>51212</v>
+        <v>41182</v>
       </c>
       <c r="J37" s="4"/>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
     </row>
     <row r="39" spans="1:12">
-      <c r="F39" s="154" t="s">
+      <c r="F39" s="149" t="s">
         <v>176</v>
       </c>
-      <c r="G39" s="154"/>
-      <c r="H39" s="154"/>
+      <c r="G39" s="149"/>
+      <c r="H39" s="149"/>
       <c r="I39" s="129">
         <f>I33+I35</f>
-        <v>18172</v>
+        <v>8142</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="15.75">
-      <c r="C41" s="155" t="s">
-        <v>178</v>
-      </c>
-      <c r="D41" s="155"/>
-      <c r="E41" s="155"/>
-      <c r="F41" s="155"/>
-      <c r="G41" s="155"/>
-      <c r="H41" s="155"/>
+      <c r="C41" s="150" t="s">
+        <v>183</v>
+      </c>
+      <c r="D41" s="150"/>
+      <c r="E41" s="150"/>
+      <c r="F41" s="150"/>
+      <c r="G41" s="150"/>
+      <c r="H41" s="150"/>
       <c r="I41" s="132">
         <f>I23+I39</f>
-        <v>37524</v>
+        <v>27494</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="30">
       <c r="B45" s="131" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
@@ -4003,11 +4008,21 @@
       <c r="F46" s="4"/>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1">
-      <c r="C47" s="156"/>
-      <c r="D47" s="156"/>
+      <c r="C47" s="151"/>
+      <c r="D47" s="151"/>
+    </row>
+    <row r="48" spans="1:12">
+      <c r="E48" t="s">
+        <v>146</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C1:I2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="C15:G15"/>
     <mergeCell ref="F39:H39"/>
     <mergeCell ref="E23:G23"/>
     <mergeCell ref="C41:H41"/>
@@ -4018,11 +4033,6 @@
     <mergeCell ref="C31:H31"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="D37:H37"/>
-    <mergeCell ref="C1:I2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="C15:G15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4049,28 +4059,28 @@
     <row r="1" spans="1:12" ht="16.5" customHeight="1">
       <c r="A1" s="28"/>
       <c r="B1" s="28"/>
-      <c r="C1" s="171" t="s">
+      <c r="C1" s="161" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="171"/>
-      <c r="E1" s="171"/>
-      <c r="F1" s="171"/>
-      <c r="G1" s="171"/>
-      <c r="H1" s="171"/>
-      <c r="I1" s="171"/>
+      <c r="D1" s="161"/>
+      <c r="E1" s="161"/>
+      <c r="F1" s="161"/>
+      <c r="G1" s="161"/>
+      <c r="H1" s="161"/>
+      <c r="I1" s="161"/>
       <c r="J1" s="28"/>
       <c r="K1" s="28"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="28"/>
       <c r="B2" s="28"/>
-      <c r="C2" s="172"/>
-      <c r="D2" s="172"/>
-      <c r="E2" s="172"/>
-      <c r="F2" s="172"/>
-      <c r="G2" s="172"/>
-      <c r="H2" s="172"/>
-      <c r="I2" s="172"/>
+      <c r="C2" s="162"/>
+      <c r="D2" s="162"/>
+      <c r="E2" s="162"/>
+      <c r="F2" s="162"/>
+      <c r="G2" s="162"/>
+      <c r="H2" s="162"/>
+      <c r="I2" s="162"/>
       <c r="J2" s="28"/>
       <c r="K2" s="28"/>
     </row>
@@ -4116,11 +4126,11 @@
       <c r="A4" s="64">
         <v>1</v>
       </c>
-      <c r="B4" s="170" t="s">
+      <c r="B4" s="160" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="170"/>
-      <c r="D4" s="170"/>
+      <c r="C4" s="160"/>
+      <c r="D4" s="160"/>
       <c r="E4" s="65"/>
       <c r="F4" s="66"/>
       <c r="G4" s="67"/>
@@ -4246,13 +4256,13 @@
       </c>
       <c r="B8" s="78"/>
       <c r="C8" s="71"/>
-      <c r="D8" s="162" t="s">
+      <c r="D8" s="167" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="162"/>
-      <c r="F8" s="162"/>
-      <c r="G8" s="162"/>
-      <c r="H8" s="162"/>
+      <c r="E8" s="167"/>
+      <c r="F8" s="167"/>
+      <c r="G8" s="167"/>
+      <c r="H8" s="167"/>
       <c r="I8" s="79">
         <f>SUM(I5:I7)</f>
         <v>102660</v>
@@ -4281,11 +4291,11 @@
       <c r="A10" s="64">
         <v>7</v>
       </c>
-      <c r="B10" s="165" t="s">
+      <c r="B10" s="170" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="165"/>
-      <c r="D10" s="165"/>
+      <c r="C10" s="170"/>
+      <c r="D10" s="170"/>
       <c r="E10" s="81"/>
       <c r="F10" s="81"/>
       <c r="G10" s="81"/>
@@ -4410,12 +4420,12 @@
       <c r="B14" s="91"/>
       <c r="C14" s="92"/>
       <c r="D14" s="93"/>
-      <c r="E14" s="166" t="s">
+      <c r="E14" s="171" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="166"/>
-      <c r="G14" s="166"/>
-      <c r="H14" s="166"/>
+      <c r="F14" s="171"/>
+      <c r="G14" s="171"/>
+      <c r="H14" s="171"/>
       <c r="I14" s="94">
         <v>118236</v>
       </c>
@@ -4443,11 +4453,11 @@
       <c r="A16" s="64">
         <v>13</v>
       </c>
-      <c r="B16" s="173" t="s">
+      <c r="B16" s="163" t="s">
         <v>155</v>
       </c>
-      <c r="C16" s="173"/>
-      <c r="D16" s="173"/>
+      <c r="C16" s="163"/>
+      <c r="D16" s="163"/>
       <c r="E16" s="103"/>
       <c r="F16" s="103"/>
       <c r="G16" s="103"/>
@@ -4570,13 +4580,13 @@
         <v>17</v>
       </c>
       <c r="B20" s="110"/>
-      <c r="C20" s="174" t="s">
+      <c r="C20" s="164" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="174"/>
-      <c r="E20" s="174"/>
-      <c r="F20" s="174"/>
-      <c r="G20" s="174"/>
+      <c r="D20" s="164"/>
+      <c r="E20" s="164"/>
+      <c r="F20" s="164"/>
+      <c r="G20" s="164"/>
       <c r="H20" s="111"/>
       <c r="I20" s="112">
         <v>117457.2</v>
@@ -4589,11 +4599,11 @@
       <c r="A21" s="64">
         <v>18</v>
       </c>
-      <c r="B21" s="167" t="s">
+      <c r="B21" s="172" t="s">
         <v>71</v>
       </c>
-      <c r="C21" s="167"/>
-      <c r="D21" s="167"/>
+      <c r="C21" s="172"/>
+      <c r="D21" s="172"/>
       <c r="E21" s="99"/>
       <c r="F21" s="100"/>
       <c r="G21" s="100"/>
@@ -4711,12 +4721,12 @@
       </c>
       <c r="B25" s="114"/>
       <c r="C25" s="97"/>
-      <c r="D25" s="161" t="s">
+      <c r="D25" s="166" t="s">
         <v>24</v>
       </c>
-      <c r="E25" s="161"/>
-      <c r="F25" s="161"/>
-      <c r="G25" s="161"/>
+      <c r="E25" s="166"/>
+      <c r="F25" s="166"/>
+      <c r="G25" s="166"/>
       <c r="H25" s="11"/>
       <c r="I25" s="12">
         <v>135936</v>
@@ -4745,11 +4755,11 @@
       <c r="A27" s="64">
         <v>24</v>
       </c>
-      <c r="B27" s="164" t="s">
+      <c r="B27" s="169" t="s">
         <v>77</v>
       </c>
-      <c r="C27" s="164"/>
-      <c r="D27" s="164"/>
+      <c r="C27" s="169"/>
+      <c r="D27" s="169"/>
       <c r="E27" s="65"/>
       <c r="F27" s="115"/>
       <c r="G27" s="115"/>
@@ -4867,12 +4877,12 @@
       </c>
       <c r="B31" s="114"/>
       <c r="C31" s="50"/>
-      <c r="D31" s="161" t="s">
+      <c r="D31" s="166" t="s">
         <v>24</v>
       </c>
-      <c r="E31" s="161"/>
-      <c r="F31" s="161"/>
-      <c r="G31" s="161"/>
+      <c r="E31" s="166"/>
+      <c r="F31" s="166"/>
+      <c r="G31" s="166"/>
       <c r="H31" s="11"/>
       <c r="I31" s="12">
         <v>147586.14000000001</v>
@@ -5018,11 +5028,11 @@
       <c r="B36" s="97"/>
       <c r="C36" s="117"/>
       <c r="D36" s="117"/>
-      <c r="E36" s="169" t="s">
+      <c r="E36" s="174" t="s">
         <v>24</v>
       </c>
-      <c r="F36" s="169"/>
-      <c r="G36" s="169"/>
+      <c r="F36" s="174"/>
+      <c r="G36" s="174"/>
       <c r="H36" s="118"/>
       <c r="I36" s="119">
         <f>SUM(I33:I35)</f>
@@ -5036,12 +5046,12 @@
       <c r="A37" s="64">
         <v>34</v>
       </c>
-      <c r="B37" s="167" t="s">
+      <c r="B37" s="172" t="s">
         <v>161</v>
       </c>
-      <c r="C37" s="167"/>
-      <c r="D37" s="167"/>
-      <c r="E37" s="167"/>
+      <c r="C37" s="172"/>
+      <c r="D37" s="172"/>
+      <c r="E37" s="172"/>
       <c r="F37" s="115"/>
       <c r="G37" s="115"/>
       <c r="H37" s="65"/>
@@ -5173,11 +5183,11 @@
       <c r="B41" s="97"/>
       <c r="C41" s="117"/>
       <c r="D41" s="117"/>
-      <c r="E41" s="169" t="s">
+      <c r="E41" s="174" t="s">
         <v>24</v>
       </c>
-      <c r="F41" s="169"/>
-      <c r="G41" s="169"/>
+      <c r="F41" s="174"/>
+      <c r="G41" s="174"/>
       <c r="H41" s="118"/>
       <c r="I41" s="119">
         <f>SUM(I38:I40)</f>
@@ -5191,11 +5201,11 @@
       <c r="A42" s="64">
         <v>39</v>
       </c>
-      <c r="B42" s="160" t="s">
+      <c r="B42" s="165" t="s">
         <v>160</v>
       </c>
-      <c r="C42" s="160"/>
-      <c r="D42" s="160"/>
+      <c r="C42" s="165"/>
+      <c r="D42" s="165"/>
       <c r="E42" s="121"/>
       <c r="F42" s="122"/>
       <c r="G42" s="122"/>
@@ -5319,12 +5329,12 @@
       </c>
       <c r="B46" s="114"/>
       <c r="C46" s="5"/>
-      <c r="D46" s="161" t="s">
+      <c r="D46" s="166" t="s">
         <v>24</v>
       </c>
-      <c r="E46" s="161"/>
-      <c r="F46" s="161"/>
-      <c r="G46" s="161"/>
+      <c r="E46" s="166"/>
+      <c r="F46" s="166"/>
+      <c r="G46" s="166"/>
       <c r="H46" s="11"/>
       <c r="I46" s="12">
         <v>124608</v>
@@ -5353,12 +5363,12 @@
       <c r="A48" s="64">
         <v>45</v>
       </c>
-      <c r="B48" s="168" t="s">
+      <c r="B48" s="173" t="s">
         <v>159</v>
       </c>
-      <c r="C48" s="168"/>
-      <c r="D48" s="168"/>
-      <c r="E48" s="168"/>
+      <c r="C48" s="173"/>
+      <c r="D48" s="173"/>
+      <c r="E48" s="173"/>
       <c r="F48" s="115"/>
       <c r="G48" s="115"/>
       <c r="H48" s="65"/>
@@ -5482,11 +5492,11 @@
       <c r="B52" s="97"/>
       <c r="C52" s="50"/>
       <c r="D52" s="50"/>
-      <c r="E52" s="163" t="s">
+      <c r="E52" s="168" t="s">
         <v>24</v>
       </c>
-      <c r="F52" s="163"/>
-      <c r="G52" s="163"/>
+      <c r="F52" s="168"/>
+      <c r="G52" s="168"/>
       <c r="H52" s="126"/>
       <c r="I52" s="119">
         <v>152821.79999999999</v>
@@ -5502,11 +5512,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="C1:I2"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="B42:D42"/>
     <mergeCell ref="D46:G46"/>
     <mergeCell ref="D8:H8"/>
     <mergeCell ref="E52:G52"/>
@@ -5520,6 +5525,11 @@
     <mergeCell ref="E36:G36"/>
     <mergeCell ref="B37:E37"/>
     <mergeCell ref="E41:G41"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="C1:I2"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="B42:D42"/>
   </mergeCells>
   <phoneticPr fontId="59" type="noConversion"/>
   <hyperlinks>
@@ -5727,7 +5737,7 @@
         <v>98</v>
       </c>
       <c r="E6" s="48">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F6" s="48">
         <v>10.9</v>
@@ -5740,15 +5750,15 @@
         <v>95</v>
       </c>
       <c r="I6" s="48">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="J6" s="48">
         <f>G6*(1+I6/100)</f>
-        <v>643.1</v>
+        <v>572.25</v>
       </c>
       <c r="K6" s="46">
         <f>E6*J6</f>
-        <v>16077.5</v>
+        <v>17167.5</v>
       </c>
       <c r="L6" s="48" t="s">
         <v>99</v>
@@ -5963,11 +5973,11 @@
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="34"/>
-      <c r="E7" s="158" t="s">
+      <c r="E7" s="154" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="158"/>
-      <c r="G7" s="158"/>
+      <c r="F7" s="154"/>
+      <c r="G7" s="154"/>
       <c r="H7" s="25"/>
       <c r="I7" s="25">
         <f>SUM(I5:I6)</f>
@@ -6074,11 +6084,11 @@
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="34"/>
-      <c r="E11" s="158" t="s">
+      <c r="E11" s="154" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="158"/>
-      <c r="G11" s="158"/>
+      <c r="F11" s="154"/>
+      <c r="G11" s="154"/>
       <c r="H11" s="25"/>
       <c r="I11" s="25">
         <f>SUM(I9:I10)</f>
@@ -6461,7 +6471,7 @@
         <v>165</v>
       </c>
       <c r="F2" s="57" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G2" s="130" t="s">
         <v>7</v>
@@ -6485,7 +6495,7 @@
     <row r="3" spans="1:12" ht="15.75">
       <c r="A3" s="140"/>
       <c r="B3" s="146" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C3" s="147"/>
       <c r="D3" s="138"/>
@@ -6539,7 +6549,7 @@
     <row r="5" spans="1:12" ht="15.75">
       <c r="A5" s="6"/>
       <c r="B5" s="146" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C5" s="148"/>
       <c r="D5" s="6"/>

--- a/master Quotations_October_2026/Master_Quotation_Comparison Sheet.xlsx
+++ b/master Quotations_October_2026/Master_Quotation_Comparison Sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Purchase_List_October_2026\master Quotations_October_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1D50ECD-8E41-4308-8EC5-610F72A81FFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C466F1EE-6722-4B88-8B4C-C4D62BA7C649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" tabRatio="783" xr2:uid="{EA74EA6A-41FE-42B7-B5E3-F15DF1371829}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" tabRatio="783" activeTab="4" xr2:uid="{EA74EA6A-41FE-42B7-B5E3-F15DF1371829}"/>
   </bookViews>
   <sheets>
     <sheet name="Cutting &amp; Grinding wheels" sheetId="1" r:id="rId1"/>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="186">
   <si>
     <t>CUTTING &amp; GRINDING WHEEL  MASTER SUPPLIER QUOTATION COMPARISON SHEET - KRISHI INFRATECH</t>
   </si>
@@ -422,29 +422,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">"HIKOKI" </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="4"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>GRINDING WHEEL (4")(C414033AZ) 100X4X16MM (796204)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="4"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>"HIKOKI</t>
     </r>
     <r>
@@ -456,29 +433,6 @@
         <scheme val="minor"/>
       </rPr>
       <t>" CUT OFF WHEEL (7")180X3X22MM (702170Z) DIA :180MM(7"), MAKE : HITACHI, THICK : 3MM, BORE : 22MM</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="4"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">"HIKOKI" </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="4"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>GRINDING WHEEL 7" (180 X 6 X 22) (796264)</t>
     </r>
   </si>
   <si>
@@ -1018,9 +972,6 @@
     <t>QUOTATION COMPARISON SHEET FOR BARBENDING MACHINE ,VIBRATOR</t>
   </si>
   <si>
-    <t>1. ALTECH CONSTRUCTION EQUIPMENTS,Hydarabad,6281068801</t>
-  </si>
-  <si>
     <t>S.No.</t>
   </si>
   <si>
@@ -1079,9 +1030,6 @@
   </si>
   <si>
     <t>• Transportation: Extra</t>
-  </si>
-  <si>
-    <t>2. SA ENGINEERING, Hydarabad,9985097685</t>
   </si>
   <si>
     <t>BAR BENDING MACHINE (Up to 32MM Regular, 5Hp Brake Motor, 3Phase, 400kg)</t>
@@ -1350,6 +1298,24 @@
   <si>
     <t>4" &amp; 7" Cutting &amp; Grinding  wheels Total</t>
   </si>
+  <si>
+    <t>2. SA ENGINEERING, Hydarabad,6281068801</t>
+  </si>
+  <si>
+    <t>1. ALTECH CONSTRUCTION EQUIPMENTS,Hydarabad,9985097685</t>
+  </si>
+  <si>
+    <t>"HIKOKI" GRINDING WHEEL (4")(C414033AZ) 100X4X16MM (796204)</t>
+  </si>
+  <si>
+    <t>"HIKOKI" GRINDING WHEEL 7" (180 X 6 X 22) (796264)</t>
+  </si>
+  <si>
+    <t>4" CUTTING WHEELS "BOSCH"</t>
+  </si>
+  <si>
+    <t>7" CUTTING WHEELS "BOSCH"</t>
+  </si>
 </sst>
 </file>
 
@@ -1358,7 +1324,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="\₹#,##0.00"/>
   </numFmts>
-  <fonts count="67">
+  <fonts count="68">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1479,12 +1445,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="4"/>
-      <name val="Palatino Linotype"/>
-      <family val="1"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="4"/>
       <name val="Segoe UI"/>
@@ -1805,6 +1765,20 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="4"/>
+      <name val="Palatino Linotype"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="4"/>
+      <name val="Segoe UI"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -2018,9 +1992,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="182">
+  <cellXfs count="187">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2074,22 +2048,19 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2101,14 +2072,14 @@
     <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2121,7 +2092,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2133,15 +2104,15 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="47" fillId="16" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="46" fillId="16" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2156,34 +2127,34 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="46" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2201,7 +2172,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2214,55 +2185,55 @@
     <xf numFmtId="4" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="38" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="38" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="38" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="42" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="37" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="37" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="37" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="42" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="38" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="41" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="41" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="37" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2277,10 +2248,10 @@
     <xf numFmtId="4" fontId="10" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2295,10 +2266,10 @@
     <xf numFmtId="4" fontId="10" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2311,79 +2282,79 @@
     <xf numFmtId="4" fontId="10" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="30" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="30" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="29" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="29" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="63" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="62" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2394,7 +2365,7 @@
     </xf>
     <xf numFmtId="4" fontId="1" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -2410,134 +2381,152 @@
     <xf numFmtId="4" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="46" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="64" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="47" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="65" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2854,15 +2843,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D11C5405-7040-4163-93EF-7BD4AFBEFA7F}">
-  <dimension ref="A1:L48"/>
+  <dimension ref="A1:L47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.42578125" customWidth="1"/>
     <col min="2" max="2" width="59.28515625" customWidth="1"/>
     <col min="3" max="3" width="13.140625" customWidth="1"/>
     <col min="4" max="4" width="11.42578125" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="19.5703125" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="11.85546875" customWidth="1"/>
     <col min="9" max="9" width="19.28515625" customWidth="1"/>
@@ -2874,15 +2863,15 @@
     <row r="1" spans="1:12">
       <c r="A1" s="4"/>
       <c r="B1" s="4"/>
-      <c r="C1" s="156" t="s">
+      <c r="C1" s="143" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="157"/>
-      <c r="E1" s="157"/>
-      <c r="F1" s="157"/>
-      <c r="G1" s="157"/>
-      <c r="H1" s="157"/>
-      <c r="I1" s="157"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
+      <c r="F1" s="144"/>
+      <c r="G1" s="144"/>
+      <c r="H1" s="144"/>
+      <c r="I1" s="144"/>
       <c r="J1" s="4"/>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
@@ -2890,13 +2879,13 @@
     <row r="2" spans="1:12">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
-      <c r="C2" s="157"/>
-      <c r="D2" s="157"/>
-      <c r="E2" s="157"/>
-      <c r="F2" s="157"/>
-      <c r="G2" s="157"/>
-      <c r="H2" s="157"/>
-      <c r="I2" s="157"/>
+      <c r="C2" s="144"/>
+      <c r="D2" s="144"/>
+      <c r="E2" s="144"/>
+      <c r="F2" s="144"/>
+      <c r="G2" s="144"/>
+      <c r="H2" s="144"/>
+      <c r="I2" s="144"/>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
@@ -2936,17 +2925,17 @@
         <v>11</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.5">
       <c r="A4" s="2">
         <v>1</v>
       </c>
-      <c r="B4" s="158" t="s">
+      <c r="B4" s="145" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="158"/>
+      <c r="C4" s="145"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -3114,13 +3103,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="4"/>
-      <c r="C9" s="159" t="s">
+      <c r="C9" s="146" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="159"/>
-      <c r="E9" s="159"/>
-      <c r="F9" s="159"/>
-      <c r="G9" s="159"/>
+      <c r="D9" s="146"/>
+      <c r="E9" s="146"/>
+      <c r="F9" s="146"/>
+      <c r="G9" s="146"/>
       <c r="H9" s="11"/>
       <c r="I9" s="12">
         <f>SUM(I5:I8)</f>
@@ -3134,10 +3123,10 @@
       <c r="A10" s="2">
         <v>7</v>
       </c>
-      <c r="B10" s="152" t="s">
+      <c r="B10" s="147" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="152"/>
+      <c r="C10" s="147"/>
       <c r="D10" s="6"/>
       <c r="E10" s="7"/>
       <c r="F10" s="8"/>
@@ -3297,13 +3286,13 @@
         <v>12</v>
       </c>
       <c r="B15" s="4"/>
-      <c r="C15" s="159" t="s">
+      <c r="C15" s="146" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="159"/>
-      <c r="E15" s="159"/>
-      <c r="F15" s="159"/>
-      <c r="G15" s="159"/>
+      <c r="D15" s="146"/>
+      <c r="E15" s="146"/>
+      <c r="F15" s="146"/>
+      <c r="G15" s="146"/>
       <c r="H15" s="11"/>
       <c r="I15" s="12">
         <f>SUM(I11:I14)</f>
@@ -3317,10 +3306,10 @@
       <c r="A16" s="2">
         <v>13</v>
       </c>
-      <c r="B16" s="152" t="s">
+      <c r="B16" s="147" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="152"/>
+      <c r="C16" s="147"/>
       <c r="D16" s="6"/>
       <c r="E16" s="7"/>
       <c r="F16" s="9"/>
@@ -3373,40 +3362,40 @@
       <c r="A18" s="2">
         <v>15</v>
       </c>
-      <c r="B18" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" s="19">
+      <c r="B18" s="180" t="s">
+        <v>182</v>
+      </c>
+      <c r="C18" s="181">
         <v>68042210</v>
       </c>
-      <c r="D18" s="20" t="s">
+      <c r="D18" s="182" t="s">
         <v>15</v>
       </c>
-      <c r="E18" s="21">
+      <c r="E18" s="183">
         <v>200</v>
       </c>
-      <c r="F18" s="22">
+      <c r="F18" s="184">
         <v>38</v>
       </c>
-      <c r="G18" s="22">
+      <c r="G18" s="184">
         <f t="shared" si="0"/>
         <v>7600</v>
       </c>
-      <c r="H18" s="21">
+      <c r="H18" s="183">
         <v>18</v>
       </c>
-      <c r="I18" s="22">
+      <c r="I18" s="184">
         <f t="shared" si="1"/>
         <v>8968</v>
       </c>
-      <c r="J18" s="23" t="s">
+      <c r="J18" s="185" t="s">
         <v>34</v>
       </c>
-      <c r="K18" s="20" t="s">
+      <c r="K18" s="182" t="s">
         <v>35</v>
       </c>
-      <c r="L18" s="60" t="s">
-        <v>175</v>
+      <c r="L18" s="59" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="30">
@@ -3414,35 +3403,35 @@
         <v>16</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" s="24">
+        <v>36</v>
+      </c>
+      <c r="C19" s="23">
         <v>68042290</v>
       </c>
-      <c r="D19" s="20" t="s">
+      <c r="D19" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="20">
         <v>200</v>
       </c>
-      <c r="F19" s="22">
+      <c r="F19" s="21">
         <v>81</v>
       </c>
-      <c r="G19" s="22">
+      <c r="G19" s="21">
         <f t="shared" si="0"/>
         <v>16200</v>
       </c>
-      <c r="H19" s="21">
+      <c r="H19" s="20">
         <v>18</v>
       </c>
-      <c r="I19" s="22">
+      <c r="I19" s="21">
         <f>G19*(1+H19/100)</f>
         <v>19116</v>
       </c>
-      <c r="J19" s="23" t="s">
+      <c r="J19" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="K19" s="20" t="s">
+      <c r="K19" s="19" t="s">
         <v>35</v>
       </c>
       <c r="L19" s="6"/>
@@ -3451,40 +3440,40 @@
       <c r="A20" s="2">
         <v>17</v>
       </c>
-      <c r="B20" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="19">
+      <c r="B20" s="180" t="s">
+        <v>183</v>
+      </c>
+      <c r="C20" s="181">
         <v>68042210</v>
       </c>
-      <c r="D20" s="20" t="s">
+      <c r="D20" s="182" t="s">
         <v>15</v>
       </c>
-      <c r="E20" s="24">
+      <c r="E20" s="186">
         <v>100</v>
       </c>
-      <c r="F20" s="24">
+      <c r="F20" s="186">
         <v>88</v>
       </c>
-      <c r="G20" s="22">
+      <c r="G20" s="184">
         <f t="shared" si="0"/>
         <v>8800</v>
       </c>
-      <c r="H20" s="21">
+      <c r="H20" s="183">
         <v>18</v>
       </c>
-      <c r="I20" s="22">
+      <c r="I20" s="184">
         <f t="shared" si="1"/>
         <v>10384</v>
       </c>
-      <c r="J20" s="23" t="s">
+      <c r="J20" s="185" t="s">
         <v>34</v>
       </c>
-      <c r="K20" s="20" t="s">
+      <c r="K20" s="182" t="s">
         <v>35</v>
       </c>
-      <c r="L20" s="60" t="s">
-        <v>175</v>
+      <c r="L20" s="59" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="16.5">
@@ -3492,20 +3481,20 @@
         <v>18</v>
       </c>
       <c r="B21" s="4"/>
-      <c r="C21" s="153" t="s">
+      <c r="C21" s="151" t="s">
         <v>24</v>
       </c>
-      <c r="D21" s="153"/>
-      <c r="E21" s="153"/>
-      <c r="F21" s="153"/>
-      <c r="G21" s="153"/>
-      <c r="H21" s="25"/>
+      <c r="D21" s="151"/>
+      <c r="E21" s="151"/>
+      <c r="F21" s="151"/>
+      <c r="G21" s="151"/>
+      <c r="H21" s="24"/>
       <c r="I21" s="12">
         <f>SUM(I17:I20)</f>
         <v>47672</v>
       </c>
-      <c r="J21" s="26"/>
-      <c r="K21" s="26"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="25"/>
       <c r="L21" s="6"/>
     </row>
     <row r="22" spans="1:12" ht="16.5">
@@ -3513,13 +3502,13 @@
       <c r="B22" s="4"/>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
-      <c r="E22" s="133"/>
-      <c r="F22" s="133"/>
-      <c r="G22" s="133"/>
-      <c r="H22" s="25"/>
+      <c r="E22" s="132"/>
+      <c r="F22" s="132"/>
+      <c r="G22" s="132"/>
+      <c r="H22" s="24"/>
       <c r="I22" s="12"/>
-      <c r="J22" s="26"/>
-      <c r="K22" s="26"/>
+      <c r="J22" s="25"/>
+      <c r="K22" s="25"/>
       <c r="L22" s="6"/>
     </row>
     <row r="23" spans="1:12" ht="16.5">
@@ -3527,52 +3516,52 @@
         <v>19</v>
       </c>
       <c r="B23" s="4"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="149" t="s">
-        <v>177</v>
-      </c>
-      <c r="F23" s="149"/>
-      <c r="G23" s="149"/>
-      <c r="H23" s="127"/>
-      <c r="I23" s="128">
+      <c r="C23" s="25"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="148" t="s">
+        <v>173</v>
+      </c>
+      <c r="F23" s="148"/>
+      <c r="G23" s="148"/>
+      <c r="H23" s="126"/>
+      <c r="I23" s="127">
         <f>I18+I20</f>
         <v>19352</v>
       </c>
-      <c r="J23" s="26"/>
-      <c r="K23" s="26"/>
+      <c r="J23" s="25"/>
+      <c r="K23" s="25"/>
       <c r="L23" s="6"/>
     </row>
     <row r="24" spans="1:12" ht="16.5">
       <c r="A24" s="2"/>
       <c r="B24" s="4"/>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="134"/>
-      <c r="F24" s="134"/>
-      <c r="G24" s="134"/>
-      <c r="H24" s="135"/>
-      <c r="I24" s="136"/>
-      <c r="J24" s="26"/>
-      <c r="K24" s="26"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="133"/>
+      <c r="F24" s="133"/>
+      <c r="G24" s="133"/>
+      <c r="H24" s="134"/>
+      <c r="I24" s="135"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="25"/>
       <c r="L24" s="6"/>
     </row>
     <row r="25" spans="1:12" ht="16.5">
       <c r="A25" s="2">
         <v>20</v>
       </c>
-      <c r="B25" s="152" t="s">
-        <v>39</v>
-      </c>
-      <c r="C25" s="152"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
+      <c r="B25" s="147" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="147"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
       <c r="G25" s="9"/>
-      <c r="H25" s="26"/>
+      <c r="H25" s="25"/>
       <c r="I25" s="9"/>
-      <c r="J25" s="26"/>
-      <c r="K25" s="26"/>
+      <c r="J25" s="25"/>
+      <c r="K25" s="25"/>
       <c r="L25" s="6"/>
     </row>
     <row r="26" spans="1:12" ht="16.5">
@@ -3580,33 +3569,33 @@
         <v>21</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C26" s="26"/>
+        <v>38</v>
+      </c>
+      <c r="C26" s="25"/>
       <c r="D26" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E26" s="26">
+      <c r="E26" s="25">
         <v>200</v>
       </c>
-      <c r="F26" s="26">
+      <c r="F26" s="25">
         <v>10.17</v>
       </c>
       <c r="G26" s="9">
         <f t="shared" si="0"/>
         <v>2034</v>
       </c>
-      <c r="H26" s="26">
+      <c r="H26" s="25">
         <v>18</v>
       </c>
       <c r="I26" s="9">
         <f t="shared" si="1"/>
         <v>2400.12</v>
       </c>
-      <c r="J26" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="K26" s="26">
+      <c r="J26" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="K26" s="25">
         <v>8686675543</v>
       </c>
       <c r="L26" s="6"/>
@@ -3616,33 +3605,33 @@
         <v>22</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C27" s="26"/>
+        <v>40</v>
+      </c>
+      <c r="C27" s="25"/>
       <c r="D27" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E27" s="26">
+      <c r="E27" s="25">
         <v>200</v>
       </c>
-      <c r="F27" s="26">
+      <c r="F27" s="25">
         <v>15.25</v>
       </c>
       <c r="G27" s="9">
         <f t="shared" si="0"/>
         <v>3050</v>
       </c>
-      <c r="H27" s="26">
+      <c r="H27" s="25">
         <v>18</v>
       </c>
       <c r="I27" s="9">
         <f t="shared" si="1"/>
         <v>3599</v>
       </c>
-      <c r="J27" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="K27" s="26">
+      <c r="J27" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="K27" s="25">
         <v>8686675543</v>
       </c>
       <c r="L27" s="6"/>
@@ -3652,33 +3641,33 @@
         <v>23</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="C28" s="26"/>
+        <v>175</v>
+      </c>
+      <c r="C28" s="25"/>
       <c r="D28" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E28" s="26">
+      <c r="E28" s="25">
         <v>200</v>
       </c>
-      <c r="F28" s="26">
+      <c r="F28" s="25">
         <v>42.37</v>
       </c>
       <c r="G28" s="9">
         <f t="shared" si="0"/>
         <v>8474</v>
       </c>
-      <c r="H28" s="26">
+      <c r="H28" s="25">
         <v>18</v>
       </c>
       <c r="I28" s="9">
         <f t="shared" si="1"/>
         <v>9999.32</v>
       </c>
-      <c r="J28" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="K28" s="26">
+      <c r="J28" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="K28" s="25">
         <v>8686675543</v>
       </c>
       <c r="L28" s="6"/>
@@ -3688,33 +3677,33 @@
         <v>24</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C29" s="26"/>
+        <v>41</v>
+      </c>
+      <c r="C29" s="25"/>
       <c r="D29" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E29" s="26">
+      <c r="E29" s="25">
         <v>200</v>
       </c>
-      <c r="F29" s="26">
+      <c r="F29" s="25">
         <v>101.69</v>
       </c>
       <c r="G29" s="9">
         <f t="shared" si="0"/>
         <v>20338</v>
       </c>
-      <c r="H29" s="26">
+      <c r="H29" s="25">
         <v>18</v>
       </c>
       <c r="I29" s="9">
         <f t="shared" si="1"/>
         <v>23998.84</v>
       </c>
-      <c r="J29" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="K29" s="26">
+      <c r="J29" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="K29" s="25">
         <v>8686675543</v>
       </c>
       <c r="L29" s="6"/>
@@ -3724,33 +3713,33 @@
         <v>25</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C30" s="26"/>
+        <v>42</v>
+      </c>
+      <c r="C30" s="25"/>
       <c r="D30" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E30" s="26">
+      <c r="E30" s="25">
         <v>200</v>
       </c>
-      <c r="F30" s="26">
+      <c r="F30" s="25">
         <v>127.12</v>
       </c>
       <c r="G30" s="9">
         <f>E30*F30</f>
         <v>25424</v>
       </c>
-      <c r="H30" s="26">
+      <c r="H30" s="25">
         <v>18</v>
       </c>
       <c r="I30" s="9">
         <f>G30*(1+H30/100)</f>
         <v>30000.32</v>
       </c>
-      <c r="J30" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="K30" s="26">
+      <c r="J30" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="K30" s="25">
         <v>8686675543</v>
       </c>
       <c r="L30" s="6"/>
@@ -3760,76 +3749,76 @@
         <v>26</v>
       </c>
       <c r="B31" s="4"/>
-      <c r="C31" s="154" t="s">
+      <c r="C31" s="152" t="s">
         <v>24</v>
       </c>
-      <c r="D31" s="154"/>
-      <c r="E31" s="154"/>
-      <c r="F31" s="154"/>
-      <c r="G31" s="154"/>
-      <c r="H31" s="154"/>
+      <c r="D31" s="152"/>
+      <c r="E31" s="152"/>
+      <c r="F31" s="152"/>
+      <c r="G31" s="152"/>
+      <c r="H31" s="152"/>
       <c r="I31" s="12">
         <f>SUM(I26:I30)</f>
         <v>69997.600000000006</v>
       </c>
-      <c r="J31" s="26"/>
-      <c r="K31" s="26"/>
+      <c r="J31" s="25"/>
+      <c r="K31" s="25"/>
       <c r="L31" s="6"/>
     </row>
     <row r="32" spans="1:12" ht="16.5">
       <c r="A32" s="2">
         <v>27</v>
       </c>
-      <c r="B32" s="152" t="s">
-        <v>45</v>
-      </c>
-      <c r="C32" s="152"/>
+      <c r="B32" s="147" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32" s="147"/>
       <c r="D32" s="6"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="26"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="25"/>
       <c r="G32" s="9"/>
-      <c r="H32" s="26"/>
+      <c r="H32" s="25"/>
       <c r="I32" s="9"/>
-      <c r="J32" s="26"/>
-      <c r="K32" s="26"/>
+      <c r="J32" s="25"/>
+      <c r="K32" s="25"/>
       <c r="L32" s="6"/>
     </row>
     <row r="33" spans="1:12" ht="16.5">
       <c r="A33" s="2">
         <v>28</v>
       </c>
-      <c r="B33" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C33" s="26"/>
-      <c r="D33" s="6" t="s">
+      <c r="B33" s="33" t="s">
+        <v>184</v>
+      </c>
+      <c r="C33" s="24"/>
+      <c r="D33" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="E33" s="26">
+      <c r="E33" s="24">
         <v>200</v>
       </c>
-      <c r="F33" s="26">
+      <c r="F33" s="24">
         <v>12</v>
       </c>
-      <c r="G33" s="9">
+      <c r="G33" s="12">
         <f t="shared" ref="G33:G36" si="2">E33*F33</f>
         <v>2400</v>
       </c>
-      <c r="H33" s="26">
+      <c r="H33" s="24">
         <v>18</v>
       </c>
-      <c r="I33" s="9">
+      <c r="I33" s="12">
         <f>G33*(1+H33/100)</f>
         <v>2832</v>
       </c>
-      <c r="J33" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="K33" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="L33" s="60" t="s">
-        <v>175</v>
+      <c r="J33" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="K33" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="L33" s="59" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="16.5">
@@ -3837,34 +3826,34 @@
         <v>29</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="C34" s="26"/>
+        <v>175</v>
+      </c>
+      <c r="C34" s="25"/>
       <c r="D34" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E34" s="26">
+      <c r="E34" s="25">
         <v>200</v>
       </c>
-      <c r="F34" s="26">
+      <c r="F34" s="25">
         <v>50</v>
       </c>
       <c r="G34" s="9">
         <f>E34*F34</f>
         <v>10000</v>
       </c>
-      <c r="H34" s="26">
+      <c r="H34" s="25">
         <v>18</v>
       </c>
       <c r="I34" s="9">
         <f>G34*(1+H34/100)</f>
         <v>11800</v>
       </c>
-      <c r="J34" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="K34" s="26" t="s">
-        <v>47</v>
+      <c r="J34" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="K34" s="25" t="s">
+        <v>45</v>
       </c>
       <c r="L34" s="6"/>
     </row>
@@ -3872,38 +3861,38 @@
       <c r="A35" s="2">
         <v>30</v>
       </c>
-      <c r="B35" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C35" s="26"/>
-      <c r="D35" s="6" t="s">
+      <c r="B35" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="C35" s="24"/>
+      <c r="D35" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="E35" s="26">
+      <c r="E35" s="24">
         <v>100</v>
       </c>
-      <c r="F35" s="26">
+      <c r="F35" s="24">
         <v>45</v>
       </c>
-      <c r="G35" s="9">
+      <c r="G35" s="12">
         <f t="shared" si="2"/>
         <v>4500</v>
       </c>
-      <c r="H35" s="26">
+      <c r="H35" s="24">
         <v>18</v>
       </c>
-      <c r="I35" s="9">
+      <c r="I35" s="12">
         <f t="shared" ref="I35:I36" si="3">G35*(1+H35/100)</f>
         <v>5310</v>
       </c>
-      <c r="J35" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="K35" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="L35" s="60" t="s">
-        <v>175</v>
+      <c r="J35" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="K35" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="L35" s="59" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="16.5">
@@ -3911,34 +3900,34 @@
         <v>31</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C36" s="26"/>
+        <v>46</v>
+      </c>
+      <c r="C36" s="25"/>
       <c r="D36" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E36" s="26">
+      <c r="E36" s="25">
         <v>200</v>
       </c>
-      <c r="F36" s="26">
+      <c r="F36" s="25">
         <v>90</v>
       </c>
       <c r="G36" s="9">
         <f t="shared" si="2"/>
         <v>18000</v>
       </c>
-      <c r="H36" s="26">
+      <c r="H36" s="25">
         <v>18</v>
       </c>
       <c r="I36" s="9">
         <f t="shared" si="3"/>
         <v>21240</v>
       </c>
-      <c r="J36" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="K36" s="26" t="s">
-        <v>47</v>
+      <c r="J36" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="K36" s="25" t="s">
+        <v>45</v>
       </c>
       <c r="L36" s="4"/>
     </row>
@@ -3948,14 +3937,14 @@
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
-      <c r="D37" s="155" t="s">
+      <c r="D37" s="153" t="s">
         <v>24</v>
       </c>
-      <c r="E37" s="155"/>
-      <c r="F37" s="155"/>
-      <c r="G37" s="155"/>
-      <c r="H37" s="155"/>
-      <c r="I37" s="27">
+      <c r="E37" s="153"/>
+      <c r="F37" s="153"/>
+      <c r="G37" s="153"/>
+      <c r="H37" s="153"/>
+      <c r="I37" s="26">
         <f>SUM(I33:I36)</f>
         <v>41182</v>
       </c>
@@ -3964,37 +3953,37 @@
       <c r="L37" s="4"/>
     </row>
     <row r="39" spans="1:12">
-      <c r="F39" s="149" t="s">
-        <v>176</v>
-      </c>
-      <c r="G39" s="149"/>
-      <c r="H39" s="149"/>
-      <c r="I39" s="129">
+      <c r="F39" s="148" t="s">
+        <v>172</v>
+      </c>
+      <c r="G39" s="148"/>
+      <c r="H39" s="148"/>
+      <c r="I39" s="128">
         <f>I33+I35</f>
         <v>8142</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="15.75">
-      <c r="C41" s="150" t="s">
-        <v>183</v>
-      </c>
-      <c r="D41" s="150"/>
-      <c r="E41" s="150"/>
-      <c r="F41" s="150"/>
-      <c r="G41" s="150"/>
-      <c r="H41" s="150"/>
-      <c r="I41" s="132">
+      <c r="C41" s="149" t="s">
+        <v>179</v>
+      </c>
+      <c r="D41" s="149"/>
+      <c r="E41" s="149"/>
+      <c r="F41" s="149"/>
+      <c r="G41" s="149"/>
+      <c r="H41" s="149"/>
+      <c r="I41" s="131">
         <f>I23+I39</f>
         <v>27494</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="30">
-      <c r="B45" s="131" t="s">
-        <v>178</v>
+      <c r="B45" s="130" t="s">
+        <v>174</v>
       </c>
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
-      <c r="E45" s="26"/>
+      <c r="E45" s="25"/>
       <c r="F45" s="6">
         <f>17640+11600+39000</f>
         <v>68240</v>
@@ -4008,21 +3997,11 @@
       <c r="F46" s="4"/>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1">
-      <c r="C47" s="151"/>
-      <c r="D47" s="151"/>
-    </row>
-    <row r="48" spans="1:12">
-      <c r="E48" t="s">
-        <v>146</v>
-      </c>
+      <c r="C47" s="150"/>
+      <c r="D47" s="150"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C1:I2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="C15:G15"/>
     <mergeCell ref="F39:H39"/>
     <mergeCell ref="E23:G23"/>
     <mergeCell ref="C41:H41"/>
@@ -4033,6 +4012,11 @@
     <mergeCell ref="C31:H31"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="D37:H37"/>
+    <mergeCell ref="C1:I2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="C15:G15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4057,580 +4041,580 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A1" s="28"/>
-      <c r="B1" s="28"/>
-      <c r="C1" s="161" t="s">
-        <v>49</v>
-      </c>
-      <c r="D1" s="161"/>
-      <c r="E1" s="161"/>
-      <c r="F1" s="161"/>
-      <c r="G1" s="161"/>
-      <c r="H1" s="161"/>
-      <c r="I1" s="161"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
+      <c r="A1" s="27"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="164" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" s="164"/>
+      <c r="E1" s="164"/>
+      <c r="F1" s="164"/>
+      <c r="G1" s="164"/>
+      <c r="H1" s="164"/>
+      <c r="I1" s="164"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="28"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="162"/>
-      <c r="D2" s="162"/>
-      <c r="E2" s="162"/>
-      <c r="F2" s="162"/>
-      <c r="G2" s="162"/>
-      <c r="H2" s="162"/>
-      <c r="I2" s="162"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
+      <c r="A2" s="27"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="165"/>
+      <c r="D2" s="165"/>
+      <c r="E2" s="165"/>
+      <c r="F2" s="165"/>
+      <c r="G2" s="165"/>
+      <c r="H2" s="165"/>
+      <c r="I2" s="165"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
     </row>
     <row r="3" spans="1:12" ht="33">
-      <c r="A3" s="62" t="s">
+      <c r="A3" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="63" t="s">
+      <c r="B3" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="63" t="s">
+      <c r="C3" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="63" t="s">
+      <c r="D3" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="63" t="s">
+      <c r="E3" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="63" t="s">
+      <c r="F3" s="62" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="62" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="K3" s="62" t="s">
+        <v>11</v>
+      </c>
+      <c r="L3" s="60" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="45" customHeight="1">
+      <c r="A4" s="63">
+        <v>1</v>
+      </c>
+      <c r="B4" s="163" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="163"/>
+      <c r="D4" s="163"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="4"/>
+    </row>
+    <row r="5" spans="1:12" ht="49.5">
+      <c r="A5" s="63">
+        <v>2</v>
+      </c>
+      <c r="B5" s="69" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="70">
+        <v>83111000</v>
+      </c>
+      <c r="D5" s="71" t="s">
         <v>50</v>
       </c>
-      <c r="G3" s="63" t="s">
-        <v>7</v>
-      </c>
-      <c r="H3" s="63" t="s">
-        <v>8</v>
-      </c>
-      <c r="I3" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="63" t="s">
-        <v>10</v>
-      </c>
-      <c r="K3" s="63" t="s">
-        <v>11</v>
-      </c>
-      <c r="L3" s="61" t="s">
+      <c r="E5" s="72">
+        <v>400</v>
+      </c>
+      <c r="F5" s="73">
+        <v>93</v>
+      </c>
+      <c r="G5" s="73">
+        <v>37200</v>
+      </c>
+      <c r="H5" s="72">
+        <v>18</v>
+      </c>
+      <c r="I5" s="73">
+        <v>43896</v>
+      </c>
+      <c r="J5" s="74" t="s">
+        <v>143</v>
+      </c>
+      <c r="K5" s="75" t="s">
+        <v>62</v>
+      </c>
+      <c r="L5" s="4"/>
+    </row>
+    <row r="6" spans="1:12" ht="49.5">
+      <c r="A6" s="63">
+        <v>3</v>
+      </c>
+      <c r="B6" s="69" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="70">
+        <v>83111000</v>
+      </c>
+      <c r="D6" s="71" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="72">
+        <v>300</v>
+      </c>
+      <c r="F6" s="73">
+        <v>83</v>
+      </c>
+      <c r="G6" s="73">
+        <v>24900</v>
+      </c>
+      <c r="H6" s="72">
+        <v>18</v>
+      </c>
+      <c r="I6" s="73">
+        <v>29382</v>
+      </c>
+      <c r="J6" s="74" t="s">
+        <v>61</v>
+      </c>
+      <c r="K6" s="75" t="s">
+        <v>62</v>
+      </c>
+      <c r="L6" s="76" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="45" customHeight="1">
-      <c r="A4" s="64">
-        <v>1</v>
-      </c>
-      <c r="B4" s="160" t="s">
+    <row r="7" spans="1:12" ht="49.5">
+      <c r="A7" s="63">
+        <v>4</v>
+      </c>
+      <c r="B7" s="69" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="70">
+        <v>83111000</v>
+      </c>
+      <c r="D7" s="71" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="72">
+        <v>300</v>
+      </c>
+      <c r="F7" s="73">
+        <v>83</v>
+      </c>
+      <c r="G7" s="73">
+        <v>24900</v>
+      </c>
+      <c r="H7" s="72">
+        <v>18</v>
+      </c>
+      <c r="I7" s="73">
+        <v>29382</v>
+      </c>
+      <c r="J7" s="74" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="160"/>
-      <c r="D4" s="160"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="66"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="68"/>
-      <c r="K4" s="69"/>
-      <c r="L4" s="4"/>
-    </row>
-    <row r="5" spans="1:12" ht="49.5">
-      <c r="A5" s="64">
-        <v>2</v>
-      </c>
-      <c r="B5" s="70" t="s">
+      <c r="K7" s="75" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="71">
-        <v>83111000</v>
-      </c>
-      <c r="D5" s="72" t="s">
-        <v>52</v>
-      </c>
-      <c r="E5" s="73">
-        <v>400</v>
-      </c>
-      <c r="F5" s="74">
-        <v>93</v>
-      </c>
-      <c r="G5" s="74">
-        <v>37200</v>
-      </c>
-      <c r="H5" s="73">
-        <v>18</v>
-      </c>
-      <c r="I5" s="74">
-        <v>43896</v>
-      </c>
-      <c r="J5" s="75" t="s">
-        <v>147</v>
-      </c>
-      <c r="K5" s="76" t="s">
-        <v>64</v>
-      </c>
-      <c r="L5" s="4"/>
-    </row>
-    <row r="6" spans="1:12" ht="49.5">
-      <c r="A6" s="64">
-        <v>3</v>
-      </c>
-      <c r="B6" s="70" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" s="71">
-        <v>83111000</v>
-      </c>
-      <c r="D6" s="72" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="73">
-        <v>300</v>
-      </c>
-      <c r="F6" s="74">
-        <v>83</v>
-      </c>
-      <c r="G6" s="74">
-        <v>24900</v>
-      </c>
-      <c r="H6" s="73">
-        <v>18</v>
-      </c>
-      <c r="I6" s="74">
-        <v>29382</v>
-      </c>
-      <c r="J6" s="75" t="s">
-        <v>63</v>
-      </c>
-      <c r="K6" s="76" t="s">
-        <v>64</v>
-      </c>
-      <c r="L6" s="77" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="49.5">
-      <c r="A7" s="64">
-        <v>4</v>
-      </c>
-      <c r="B7" s="70" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" s="71">
-        <v>83111000</v>
-      </c>
-      <c r="D7" s="72" t="s">
-        <v>52</v>
-      </c>
-      <c r="E7" s="73">
-        <v>300</v>
-      </c>
-      <c r="F7" s="74">
-        <v>83</v>
-      </c>
-      <c r="G7" s="74">
-        <v>24900</v>
-      </c>
-      <c r="H7" s="73">
-        <v>18</v>
-      </c>
-      <c r="I7" s="74">
-        <v>29382</v>
-      </c>
-      <c r="J7" s="75" t="s">
-        <v>63</v>
-      </c>
-      <c r="K7" s="76" t="s">
-        <v>64</v>
-      </c>
       <c r="L7" s="4"/>
     </row>
     <row r="8" spans="1:12" ht="16.5">
-      <c r="A8" s="64">
+      <c r="A8" s="63">
         <v>5</v>
       </c>
-      <c r="B8" s="78"/>
-      <c r="C8" s="71"/>
-      <c r="D8" s="167" t="s">
+      <c r="B8" s="77"/>
+      <c r="C8" s="70"/>
+      <c r="D8" s="155" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="167"/>
-      <c r="F8" s="167"/>
-      <c r="G8" s="167"/>
-      <c r="H8" s="167"/>
-      <c r="I8" s="79">
+      <c r="E8" s="155"/>
+      <c r="F8" s="155"/>
+      <c r="G8" s="155"/>
+      <c r="H8" s="155"/>
+      <c r="I8" s="78">
         <f>SUM(I5:I7)</f>
         <v>102660</v>
       </c>
-      <c r="J8" s="75"/>
-      <c r="K8" s="80"/>
+      <c r="J8" s="74"/>
+      <c r="K8" s="79"/>
       <c r="L8" s="4"/>
     </row>
     <row r="9" spans="1:12" ht="16.5">
-      <c r="A9" s="64">
+      <c r="A9" s="63">
         <v>6</v>
       </c>
-      <c r="B9" s="78"/>
-      <c r="C9" s="81"/>
-      <c r="D9" s="81"/>
-      <c r="E9" s="81"/>
-      <c r="F9" s="81"/>
-      <c r="G9" s="81"/>
-      <c r="H9" s="82"/>
-      <c r="I9" s="79"/>
-      <c r="J9" s="83"/>
-      <c r="K9" s="84"/>
+      <c r="B9" s="77"/>
+      <c r="C9" s="80"/>
+      <c r="D9" s="80"/>
+      <c r="E9" s="80"/>
+      <c r="F9" s="80"/>
+      <c r="G9" s="80"/>
+      <c r="H9" s="81"/>
+      <c r="I9" s="78"/>
+      <c r="J9" s="82"/>
+      <c r="K9" s="83"/>
       <c r="L9" s="4"/>
     </row>
     <row r="10" spans="1:12" ht="42" customHeight="1">
-      <c r="A10" s="64">
+      <c r="A10" s="63">
         <v>7</v>
       </c>
-      <c r="B10" s="170" t="s">
+      <c r="B10" s="158" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" s="158"/>
+      <c r="D10" s="158"/>
+      <c r="E10" s="80"/>
+      <c r="F10" s="80"/>
+      <c r="G10" s="80"/>
+      <c r="H10" s="81"/>
+      <c r="I10" s="78"/>
+      <c r="J10" s="82"/>
+      <c r="K10" s="83"/>
+      <c r="L10" s="4"/>
+    </row>
+    <row r="11" spans="1:12" ht="75">
+      <c r="A11" s="63">
+        <v>8</v>
+      </c>
+      <c r="B11" s="84" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" s="85">
+        <v>83111000</v>
+      </c>
+      <c r="D11" s="86" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" s="87">
+        <v>400</v>
+      </c>
+      <c r="F11" s="88">
+        <v>105</v>
+      </c>
+      <c r="G11" s="88">
+        <v>42000</v>
+      </c>
+      <c r="H11" s="87">
+        <v>18</v>
+      </c>
+      <c r="I11" s="88">
+        <v>49560</v>
+      </c>
+      <c r="J11" s="88" t="s">
+        <v>65</v>
+      </c>
+      <c r="K11" s="89" t="s">
+        <v>35</v>
+      </c>
+      <c r="L11" s="4"/>
+    </row>
+    <row r="12" spans="1:12" ht="60">
+      <c r="A12" s="63">
+        <v>9</v>
+      </c>
+      <c r="B12" s="84" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="170"/>
-      <c r="D10" s="170"/>
-      <c r="E10" s="81"/>
-      <c r="F10" s="81"/>
-      <c r="G10" s="81"/>
-      <c r="H10" s="82"/>
-      <c r="I10" s="79"/>
-      <c r="J10" s="83"/>
-      <c r="K10" s="84"/>
-      <c r="L10" s="4"/>
-    </row>
-    <row r="11" spans="1:12" ht="75">
-      <c r="A11" s="64">
-        <v>8</v>
-      </c>
-      <c r="B11" s="85" t="s">
+      <c r="C12" s="85">
+        <v>83111000</v>
+      </c>
+      <c r="D12" s="86" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="87">
+        <v>300</v>
+      </c>
+      <c r="F12" s="88">
+        <v>97</v>
+      </c>
+      <c r="G12" s="88">
+        <v>29100</v>
+      </c>
+      <c r="H12" s="87">
+        <v>18</v>
+      </c>
+      <c r="I12" s="88">
+        <v>34338</v>
+      </c>
+      <c r="J12" s="88" t="s">
+        <v>65</v>
+      </c>
+      <c r="K12" s="89" t="s">
+        <v>35</v>
+      </c>
+      <c r="L12" s="4"/>
+    </row>
+    <row r="13" spans="1:12" ht="60">
+      <c r="A13" s="63">
+        <v>10</v>
+      </c>
+      <c r="B13" s="84" t="s">
         <v>68</v>
       </c>
-      <c r="C11" s="86">
+      <c r="C13" s="85">
         <v>83111000</v>
       </c>
-      <c r="D11" s="87" t="s">
+      <c r="D13" s="86" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" s="87">
+        <v>300</v>
+      </c>
+      <c r="F13" s="88">
+        <v>97</v>
+      </c>
+      <c r="G13" s="88">
+        <v>29100</v>
+      </c>
+      <c r="H13" s="87">
+        <v>18</v>
+      </c>
+      <c r="I13" s="88">
+        <v>34338</v>
+      </c>
+      <c r="J13" s="88" t="s">
+        <v>65</v>
+      </c>
+      <c r="K13" s="89" t="s">
+        <v>35</v>
+      </c>
+      <c r="L13" s="4"/>
+    </row>
+    <row r="14" spans="1:12" ht="16.5">
+      <c r="A14" s="63">
+        <v>11</v>
+      </c>
+      <c r="B14" s="90"/>
+      <c r="C14" s="91"/>
+      <c r="D14" s="92"/>
+      <c r="E14" s="159" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="159"/>
+      <c r="G14" s="159"/>
+      <c r="H14" s="159"/>
+      <c r="I14" s="93">
+        <v>118236</v>
+      </c>
+      <c r="J14" s="94"/>
+      <c r="K14" s="95"/>
+      <c r="L14" s="4"/>
+    </row>
+    <row r="15" spans="1:12" ht="16.5">
+      <c r="A15" s="63">
+        <v>12</v>
+      </c>
+      <c r="B15" s="96"/>
+      <c r="C15" s="96"/>
+      <c r="D15" s="97"/>
+      <c r="E15" s="98"/>
+      <c r="F15" s="99"/>
+      <c r="G15" s="99"/>
+      <c r="H15" s="98"/>
+      <c r="I15" s="99"/>
+      <c r="J15" s="100"/>
+      <c r="K15" s="101"/>
+      <c r="L15" s="4"/>
+    </row>
+    <row r="16" spans="1:12" ht="16.5">
+      <c r="A16" s="63">
+        <v>13</v>
+      </c>
+      <c r="B16" s="166" t="s">
+        <v>151</v>
+      </c>
+      <c r="C16" s="166"/>
+      <c r="D16" s="166"/>
+      <c r="E16" s="102"/>
+      <c r="F16" s="102"/>
+      <c r="G16" s="102"/>
+      <c r="H16" s="102"/>
+      <c r="I16" s="102"/>
+      <c r="J16" s="102"/>
+      <c r="K16" s="102"/>
+      <c r="L16" s="4"/>
+    </row>
+    <row r="17" spans="1:12" ht="30">
+      <c r="A17" s="63">
+        <v>14</v>
+      </c>
+      <c r="B17" s="103" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="104">
+        <v>83111000</v>
+      </c>
+      <c r="D17" s="105" t="s">
+        <v>50</v>
+      </c>
+      <c r="E17" s="106">
+        <v>400</v>
+      </c>
+      <c r="F17" s="107">
+        <v>106.5</v>
+      </c>
+      <c r="G17" s="107">
+        <v>42600</v>
+      </c>
+      <c r="H17" s="106">
+        <v>18</v>
+      </c>
+      <c r="I17" s="107">
+        <v>50268</v>
+      </c>
+      <c r="J17" s="107" t="s">
+        <v>51</v>
+      </c>
+      <c r="K17" s="108" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="88">
-        <v>400</v>
-      </c>
-      <c r="F11" s="89">
-        <v>105</v>
-      </c>
-      <c r="G11" s="89">
-        <v>42000</v>
-      </c>
-      <c r="H11" s="88">
+      <c r="L17" s="4"/>
+    </row>
+    <row r="18" spans="1:12" ht="30">
+      <c r="A18" s="63">
+        <v>15</v>
+      </c>
+      <c r="B18" s="103" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="104">
+        <v>83111000</v>
+      </c>
+      <c r="D18" s="105" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18" s="106">
+        <v>300</v>
+      </c>
+      <c r="F18" s="107">
+        <v>94.9</v>
+      </c>
+      <c r="G18" s="107">
+        <v>28470</v>
+      </c>
+      <c r="H18" s="106">
         <v>18</v>
       </c>
-      <c r="I11" s="89">
-        <v>49560</v>
-      </c>
-      <c r="J11" s="89" t="s">
-        <v>67</v>
-      </c>
-      <c r="K11" s="90" t="s">
-        <v>35</v>
-      </c>
-      <c r="L11" s="4"/>
-    </row>
-    <row r="12" spans="1:12" ht="60">
-      <c r="A12" s="64">
-        <v>9</v>
-      </c>
-      <c r="B12" s="85" t="s">
+      <c r="I18" s="107">
+        <v>33594.6</v>
+      </c>
+      <c r="J18" s="107" t="s">
+        <v>51</v>
+      </c>
+      <c r="K18" s="108" t="s">
+        <v>52</v>
+      </c>
+      <c r="L18" s="4"/>
+    </row>
+    <row r="19" spans="1:12" ht="30">
+      <c r="A19" s="63">
+        <v>16</v>
+      </c>
+      <c r="B19" s="103" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="104">
+        <v>83111000</v>
+      </c>
+      <c r="D19" s="105" t="s">
+        <v>50</v>
+      </c>
+      <c r="E19" s="106">
+        <v>300</v>
+      </c>
+      <c r="F19" s="107">
+        <v>94.9</v>
+      </c>
+      <c r="G19" s="107">
+        <v>28470</v>
+      </c>
+      <c r="H19" s="106">
+        <v>18</v>
+      </c>
+      <c r="I19" s="107">
+        <v>33594.6</v>
+      </c>
+      <c r="J19" s="107" t="s">
+        <v>51</v>
+      </c>
+      <c r="K19" s="108" t="s">
+        <v>52</v>
+      </c>
+      <c r="L19" s="4"/>
+    </row>
+    <row r="20" spans="1:12" ht="16.5">
+      <c r="A20" s="63">
+        <v>17</v>
+      </c>
+      <c r="B20" s="109"/>
+      <c r="C20" s="167" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="167"/>
+      <c r="E20" s="167"/>
+      <c r="F20" s="167"/>
+      <c r="G20" s="167"/>
+      <c r="H20" s="110"/>
+      <c r="I20" s="111">
+        <v>117457.2</v>
+      </c>
+      <c r="J20" s="107"/>
+      <c r="K20" s="108"/>
+      <c r="L20" s="4"/>
+    </row>
+    <row r="21" spans="1:12" ht="34.5" customHeight="1">
+      <c r="A21" s="63">
+        <v>18</v>
+      </c>
+      <c r="B21" s="160" t="s">
         <v>69</v>
       </c>
-      <c r="C12" s="86">
-        <v>83111000</v>
-      </c>
-      <c r="D12" s="87" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12" s="88">
-        <v>300</v>
-      </c>
-      <c r="F12" s="89">
-        <v>97</v>
-      </c>
-      <c r="G12" s="89">
-        <v>29100</v>
-      </c>
-      <c r="H12" s="88">
-        <v>18</v>
-      </c>
-      <c r="I12" s="89">
-        <v>34338</v>
-      </c>
-      <c r="J12" s="89" t="s">
-        <v>67</v>
-      </c>
-      <c r="K12" s="90" t="s">
-        <v>35</v>
-      </c>
-      <c r="L12" s="4"/>
-    </row>
-    <row r="13" spans="1:12" ht="60">
-      <c r="A13" s="64">
-        <v>10</v>
-      </c>
-      <c r="B13" s="85" t="s">
+      <c r="C21" s="160"/>
+      <c r="D21" s="160"/>
+      <c r="E21" s="98"/>
+      <c r="F21" s="99"/>
+      <c r="G21" s="99"/>
+      <c r="H21" s="98"/>
+      <c r="I21" s="99"/>
+      <c r="J21" s="100"/>
+      <c r="K21" s="101"/>
+      <c r="L21" s="4"/>
+    </row>
+    <row r="22" spans="1:12" ht="30">
+      <c r="A22" s="63">
+        <v>19</v>
+      </c>
+      <c r="B22" s="112" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="86">
-        <v>83111000</v>
-      </c>
-      <c r="D13" s="87" t="s">
-        <v>52</v>
-      </c>
-      <c r="E13" s="88">
-        <v>300</v>
-      </c>
-      <c r="F13" s="89">
-        <v>97</v>
-      </c>
-      <c r="G13" s="89">
-        <v>29100</v>
-      </c>
-      <c r="H13" s="88">
-        <v>18</v>
-      </c>
-      <c r="I13" s="89">
-        <v>34338</v>
-      </c>
-      <c r="J13" s="89" t="s">
-        <v>67</v>
-      </c>
-      <c r="K13" s="90" t="s">
-        <v>35</v>
-      </c>
-      <c r="L13" s="4"/>
-    </row>
-    <row r="14" spans="1:12" ht="16.5">
-      <c r="A14" s="64">
-        <v>11</v>
-      </c>
-      <c r="B14" s="91"/>
-      <c r="C14" s="92"/>
-      <c r="D14" s="93"/>
-      <c r="E14" s="171" t="s">
-        <v>24</v>
-      </c>
-      <c r="F14" s="171"/>
-      <c r="G14" s="171"/>
-      <c r="H14" s="171"/>
-      <c r="I14" s="94">
-        <v>118236</v>
-      </c>
-      <c r="J14" s="95"/>
-      <c r="K14" s="96"/>
-      <c r="L14" s="4"/>
-    </row>
-    <row r="15" spans="1:12" ht="16.5">
-      <c r="A15" s="64">
-        <v>12</v>
-      </c>
-      <c r="B15" s="97"/>
-      <c r="C15" s="97"/>
-      <c r="D15" s="98"/>
-      <c r="E15" s="99"/>
-      <c r="F15" s="100"/>
-      <c r="G15" s="100"/>
-      <c r="H15" s="99"/>
-      <c r="I15" s="100"/>
-      <c r="J15" s="101"/>
-      <c r="K15" s="102"/>
-      <c r="L15" s="4"/>
-    </row>
-    <row r="16" spans="1:12" ht="16.5">
-      <c r="A16" s="64">
-        <v>13</v>
-      </c>
-      <c r="B16" s="163" t="s">
-        <v>155</v>
-      </c>
-      <c r="C16" s="163"/>
-      <c r="D16" s="163"/>
-      <c r="E16" s="103"/>
-      <c r="F16" s="103"/>
-      <c r="G16" s="103"/>
-      <c r="H16" s="103"/>
-      <c r="I16" s="103"/>
-      <c r="J16" s="103"/>
-      <c r="K16" s="103"/>
-      <c r="L16" s="4"/>
-    </row>
-    <row r="17" spans="1:12" ht="30">
-      <c r="A17" s="64">
-        <v>14</v>
-      </c>
-      <c r="B17" s="104" t="s">
-        <v>51</v>
-      </c>
-      <c r="C17" s="105">
-        <v>83111000</v>
-      </c>
-      <c r="D17" s="106" t="s">
-        <v>52</v>
-      </c>
-      <c r="E17" s="107">
-        <v>400</v>
-      </c>
-      <c r="F17" s="108">
-        <v>106.5</v>
-      </c>
-      <c r="G17" s="108">
-        <v>42600</v>
-      </c>
-      <c r="H17" s="107">
-        <v>18</v>
-      </c>
-      <c r="I17" s="108">
-        <v>50268</v>
-      </c>
-      <c r="J17" s="108" t="s">
-        <v>53</v>
-      </c>
-      <c r="K17" s="109" t="s">
-        <v>54</v>
-      </c>
-      <c r="L17" s="4"/>
-    </row>
-    <row r="18" spans="1:12" ht="30">
-      <c r="A18" s="64">
-        <v>15</v>
-      </c>
-      <c r="B18" s="104" t="s">
-        <v>55</v>
-      </c>
-      <c r="C18" s="105">
-        <v>83111000</v>
-      </c>
-      <c r="D18" s="106" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18" s="107">
-        <v>300</v>
-      </c>
-      <c r="F18" s="108">
-        <v>94.9</v>
-      </c>
-      <c r="G18" s="108">
-        <v>28470</v>
-      </c>
-      <c r="H18" s="107">
-        <v>18</v>
-      </c>
-      <c r="I18" s="108">
-        <v>33594.6</v>
-      </c>
-      <c r="J18" s="108" t="s">
-        <v>53</v>
-      </c>
-      <c r="K18" s="109" t="s">
-        <v>54</v>
-      </c>
-      <c r="L18" s="4"/>
-    </row>
-    <row r="19" spans="1:12" ht="30">
-      <c r="A19" s="64">
-        <v>16</v>
-      </c>
-      <c r="B19" s="104" t="s">
-        <v>56</v>
-      </c>
-      <c r="C19" s="105">
-        <v>83111000</v>
-      </c>
-      <c r="D19" s="106" t="s">
-        <v>52</v>
-      </c>
-      <c r="E19" s="107">
-        <v>300</v>
-      </c>
-      <c r="F19" s="108">
-        <v>94.9</v>
-      </c>
-      <c r="G19" s="108">
-        <v>28470</v>
-      </c>
-      <c r="H19" s="107">
-        <v>18</v>
-      </c>
-      <c r="I19" s="108">
-        <v>33594.6</v>
-      </c>
-      <c r="J19" s="108" t="s">
-        <v>53</v>
-      </c>
-      <c r="K19" s="109" t="s">
-        <v>54</v>
-      </c>
-      <c r="L19" s="4"/>
-    </row>
-    <row r="20" spans="1:12" ht="16.5">
-      <c r="A20" s="64">
-        <v>17</v>
-      </c>
-      <c r="B20" s="110"/>
-      <c r="C20" s="164" t="s">
-        <v>24</v>
-      </c>
-      <c r="D20" s="164"/>
-      <c r="E20" s="164"/>
-      <c r="F20" s="164"/>
-      <c r="G20" s="164"/>
-      <c r="H20" s="111"/>
-      <c r="I20" s="112">
-        <v>117457.2</v>
-      </c>
-      <c r="J20" s="108"/>
-      <c r="K20" s="109"/>
-      <c r="L20" s="4"/>
-    </row>
-    <row r="21" spans="1:12" ht="34.5" customHeight="1">
-      <c r="A21" s="64">
-        <v>18</v>
-      </c>
-      <c r="B21" s="172" t="s">
-        <v>71</v>
-      </c>
-      <c r="C21" s="172"/>
-      <c r="D21" s="172"/>
-      <c r="E21" s="99"/>
-      <c r="F21" s="100"/>
-      <c r="G21" s="100"/>
-      <c r="H21" s="99"/>
-      <c r="I21" s="100"/>
-      <c r="J21" s="101"/>
-      <c r="K21" s="102"/>
-      <c r="L21" s="4"/>
-    </row>
-    <row r="22" spans="1:12" ht="30">
-      <c r="A22" s="64">
-        <v>19</v>
-      </c>
-      <c r="B22" s="113" t="s">
-        <v>72</v>
-      </c>
-      <c r="C22" s="97"/>
+      <c r="C22" s="96"/>
       <c r="D22" s="15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E22" s="7">
         <v>400</v>
       </c>
-      <c r="F22" s="50">
+      <c r="F22" s="49">
         <v>117</v>
       </c>
-      <c r="G22" s="50">
+      <c r="G22" s="49">
         <v>46800</v>
       </c>
       <c r="H22" s="7">
@@ -4639,32 +4623,32 @@
       <c r="I22" s="9">
         <v>55224</v>
       </c>
-      <c r="J22" s="50" t="s">
+      <c r="J22" s="49" t="s">
+        <v>71</v>
+      </c>
+      <c r="K22" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="L22" s="4"/>
+    </row>
+    <row r="23" spans="1:12" ht="30">
+      <c r="A23" s="63">
+        <v>20</v>
+      </c>
+      <c r="B23" s="112" t="s">
         <v>73</v>
       </c>
-      <c r="K22" s="50" t="s">
-        <v>74</v>
-      </c>
-      <c r="L22" s="4"/>
-    </row>
-    <row r="23" spans="1:12" ht="30">
-      <c r="A23" s="64">
-        <v>20</v>
-      </c>
-      <c r="B23" s="113" t="s">
-        <v>75</v>
-      </c>
-      <c r="C23" s="97"/>
+      <c r="C23" s="96"/>
       <c r="D23" s="15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E23" s="7">
         <v>300</v>
       </c>
-      <c r="F23" s="50">
+      <c r="F23" s="49">
         <v>115</v>
       </c>
-      <c r="G23" s="50">
+      <c r="G23" s="49">
         <v>34500</v>
       </c>
       <c r="H23" s="7">
@@ -4673,24 +4657,24 @@
       <c r="I23" s="9">
         <v>40710</v>
       </c>
-      <c r="J23" s="50" t="s">
-        <v>73</v>
-      </c>
-      <c r="K23" s="50" t="s">
+      <c r="J23" s="49" t="s">
+        <v>71</v>
+      </c>
+      <c r="K23" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="L23" s="4"/>
+    </row>
+    <row r="24" spans="1:12" ht="30">
+      <c r="A24" s="63">
+        <v>21</v>
+      </c>
+      <c r="B24" s="112" t="s">
         <v>74</v>
       </c>
-      <c r="L23" s="4"/>
-    </row>
-    <row r="24" spans="1:12" ht="30">
-      <c r="A24" s="64">
-        <v>21</v>
-      </c>
-      <c r="B24" s="113" t="s">
-        <v>76</v>
-      </c>
-      <c r="C24" s="97"/>
+      <c r="C24" s="96"/>
       <c r="D24" s="15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E24" s="7">
         <v>300</v>
@@ -4707,36 +4691,36 @@
       <c r="I24" s="9">
         <v>40002</v>
       </c>
-      <c r="J24" s="50" t="s">
-        <v>73</v>
-      </c>
-      <c r="K24" s="50" t="s">
-        <v>74</v>
+      <c r="J24" s="49" t="s">
+        <v>71</v>
+      </c>
+      <c r="K24" s="49" t="s">
+        <v>72</v>
       </c>
       <c r="L24" s="4"/>
     </row>
     <row r="25" spans="1:12" ht="16.5">
-      <c r="A25" s="64">
+      <c r="A25" s="63">
         <v>22</v>
       </c>
-      <c r="B25" s="114"/>
-      <c r="C25" s="97"/>
-      <c r="D25" s="166" t="s">
+      <c r="B25" s="113"/>
+      <c r="C25" s="96"/>
+      <c r="D25" s="154" t="s">
         <v>24</v>
       </c>
-      <c r="E25" s="166"/>
-      <c r="F25" s="166"/>
-      <c r="G25" s="166"/>
+      <c r="E25" s="154"/>
+      <c r="F25" s="154"/>
+      <c r="G25" s="154"/>
       <c r="H25" s="11"/>
       <c r="I25" s="12">
         <v>135936</v>
       </c>
-      <c r="J25" s="50"/>
-      <c r="K25" s="50"/>
+      <c r="J25" s="49"/>
+      <c r="K25" s="49"/>
       <c r="L25" s="4"/>
     </row>
     <row r="26" spans="1:12" ht="16.5">
-      <c r="A26" s="64">
+      <c r="A26" s="63">
         <v>23</v>
       </c>
       <c r="B26" s="4"/>
@@ -4752,33 +4736,33 @@
       <c r="L26" s="4"/>
     </row>
     <row r="27" spans="1:12" ht="17.25">
-      <c r="A27" s="64">
+      <c r="A27" s="63">
         <v>24</v>
       </c>
-      <c r="B27" s="169" t="s">
-        <v>77</v>
-      </c>
-      <c r="C27" s="169"/>
-      <c r="D27" s="169"/>
-      <c r="E27" s="65"/>
-      <c r="F27" s="115"/>
-      <c r="G27" s="115"/>
-      <c r="H27" s="65"/>
-      <c r="I27" s="67"/>
-      <c r="J27" s="97"/>
-      <c r="K27" s="116"/>
+      <c r="B27" s="157" t="s">
+        <v>75</v>
+      </c>
+      <c r="C27" s="157"/>
+      <c r="D27" s="157"/>
+      <c r="E27" s="64"/>
+      <c r="F27" s="114"/>
+      <c r="G27" s="114"/>
+      <c r="H27" s="64"/>
+      <c r="I27" s="66"/>
+      <c r="J27" s="96"/>
+      <c r="K27" s="115"/>
       <c r="L27" s="4"/>
     </row>
     <row r="28" spans="1:12" ht="60">
-      <c r="A28" s="64">
+      <c r="A28" s="63">
         <v>25</v>
       </c>
-      <c r="B28" s="114" t="s">
-        <v>78</v>
-      </c>
-      <c r="C28" s="50"/>
+      <c r="B28" s="113" t="s">
+        <v>76</v>
+      </c>
+      <c r="C28" s="49"/>
       <c r="D28" s="15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E28" s="7">
         <v>400</v>
@@ -4795,24 +4779,24 @@
       <c r="I28" s="9">
         <v>59953.440000000002</v>
       </c>
-      <c r="J28" s="50" t="s">
+      <c r="J28" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="K28" s="49" t="s">
+        <v>78</v>
+      </c>
+      <c r="L28" s="4"/>
+    </row>
+    <row r="29" spans="1:12" ht="45">
+      <c r="A29" s="63">
+        <v>26</v>
+      </c>
+      <c r="B29" s="113" t="s">
         <v>79</v>
       </c>
-      <c r="K28" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="L28" s="4"/>
-    </row>
-    <row r="29" spans="1:12" ht="45">
-      <c r="A29" s="64">
-        <v>26</v>
-      </c>
-      <c r="B29" s="114" t="s">
-        <v>81</v>
-      </c>
-      <c r="C29" s="50"/>
+      <c r="C29" s="49"/>
       <c r="D29" s="15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E29" s="7">
         <v>300</v>
@@ -4829,24 +4813,24 @@
       <c r="I29" s="9">
         <v>44250</v>
       </c>
-      <c r="J29" s="50" t="s">
-        <v>79</v>
-      </c>
-      <c r="K29" s="50" t="s">
+      <c r="J29" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="K29" s="49" t="s">
+        <v>78</v>
+      </c>
+      <c r="L29" s="4"/>
+    </row>
+    <row r="30" spans="1:12" ht="60">
+      <c r="A30" s="63">
+        <v>27</v>
+      </c>
+      <c r="B30" s="113" t="s">
         <v>80</v>
       </c>
-      <c r="L29" s="4"/>
-    </row>
-    <row r="30" spans="1:12" ht="60">
-      <c r="A30" s="64">
-        <v>27</v>
-      </c>
-      <c r="B30" s="114" t="s">
-        <v>82</v>
-      </c>
-      <c r="C30" s="50"/>
+      <c r="C30" s="49"/>
       <c r="D30" s="15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E30" s="7">
         <v>300</v>
@@ -4863,62 +4847,62 @@
       <c r="I30" s="9">
         <v>43382.7</v>
       </c>
-      <c r="J30" s="50" t="s">
-        <v>79</v>
-      </c>
-      <c r="K30" s="50" t="s">
-        <v>80</v>
+      <c r="J30" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="K30" s="49" t="s">
+        <v>78</v>
       </c>
       <c r="L30" s="4"/>
     </row>
     <row r="31" spans="1:12" ht="16.5">
-      <c r="A31" s="64">
+      <c r="A31" s="63">
         <v>28</v>
       </c>
-      <c r="B31" s="114"/>
-      <c r="C31" s="50"/>
-      <c r="D31" s="166" t="s">
+      <c r="B31" s="113"/>
+      <c r="C31" s="49"/>
+      <c r="D31" s="154" t="s">
         <v>24</v>
       </c>
-      <c r="E31" s="166"/>
-      <c r="F31" s="166"/>
-      <c r="G31" s="166"/>
+      <c r="E31" s="154"/>
+      <c r="F31" s="154"/>
+      <c r="G31" s="154"/>
       <c r="H31" s="11"/>
       <c r="I31" s="12">
         <v>147586.14000000001</v>
       </c>
-      <c r="J31" s="50"/>
-      <c r="K31" s="50"/>
+      <c r="J31" s="49"/>
+      <c r="K31" s="49"/>
       <c r="L31" s="4"/>
     </row>
     <row r="32" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A32" s="64">
+      <c r="A32" s="63">
         <v>29</v>
       </c>
-      <c r="B32" s="114"/>
-      <c r="C32" s="50"/>
+      <c r="B32" s="113"/>
+      <c r="C32" s="49"/>
       <c r="D32" s="15"/>
       <c r="E32" s="7"/>
       <c r="F32" s="9"/>
       <c r="G32" s="9"/>
       <c r="H32" s="7"/>
       <c r="I32" s="9"/>
-      <c r="J32" s="50"/>
-      <c r="K32" s="50"/>
+      <c r="J32" s="49"/>
+      <c r="K32" s="49"/>
       <c r="L32" s="4"/>
     </row>
     <row r="33" spans="1:12" ht="30.75">
-      <c r="A33" s="64">
+      <c r="A33" s="63">
         <v>30</v>
       </c>
-      <c r="B33" s="49" t="s">
-        <v>149</v>
+      <c r="B33" s="48" t="s">
+        <v>145</v>
       </c>
       <c r="C33" s="5">
         <v>83111000</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E33" s="7">
         <v>400</v>
@@ -4938,25 +4922,25 @@
         <v>43660</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="K33" s="51" t="s">
-        <v>148</v>
+        <v>150</v>
+      </c>
+      <c r="K33" s="50" t="s">
+        <v>144</v>
       </c>
       <c r="L33" s="4"/>
     </row>
     <row r="34" spans="1:12" ht="30.75">
-      <c r="A34" s="64">
+      <c r="A34" s="63">
         <v>31</v>
       </c>
-      <c r="B34" s="49" t="s">
-        <v>150</v>
+      <c r="B34" s="48" t="s">
+        <v>146</v>
       </c>
       <c r="C34" s="5">
         <v>83111000</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E34" s="7">
         <v>300</v>
@@ -4976,25 +4960,25 @@
         <v>39825</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="K34" s="51" t="s">
-        <v>148</v>
+        <v>150</v>
+      </c>
+      <c r="K34" s="50" t="s">
+        <v>144</v>
       </c>
       <c r="L34" s="4"/>
     </row>
     <row r="35" spans="1:12" ht="30.75">
-      <c r="A35" s="64">
+      <c r="A35" s="63">
         <v>32</v>
       </c>
-      <c r="B35" s="49" t="s">
-        <v>151</v>
+      <c r="B35" s="48" t="s">
+        <v>147</v>
       </c>
       <c r="C35" s="5">
         <v>83111000</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E35" s="7">
         <v>300</v>
@@ -5014,66 +4998,66 @@
         <v>46020</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="K35" s="51" t="s">
-        <v>148</v>
+        <v>150</v>
+      </c>
+      <c r="K35" s="50" t="s">
+        <v>144</v>
       </c>
       <c r="L35" s="4"/>
     </row>
     <row r="36" spans="1:12" ht="16.5">
-      <c r="A36" s="64">
+      <c r="A36" s="63">
         <v>33</v>
       </c>
-      <c r="B36" s="97"/>
-      <c r="C36" s="117"/>
-      <c r="D36" s="117"/>
-      <c r="E36" s="174" t="s">
+      <c r="B36" s="96"/>
+      <c r="C36" s="116"/>
+      <c r="D36" s="116"/>
+      <c r="E36" s="162" t="s">
         <v>24</v>
       </c>
-      <c r="F36" s="174"/>
-      <c r="G36" s="174"/>
-      <c r="H36" s="118"/>
-      <c r="I36" s="119">
+      <c r="F36" s="162"/>
+      <c r="G36" s="162"/>
+      <c r="H36" s="117"/>
+      <c r="I36" s="118">
         <f>SUM(I33:I35)</f>
         <v>129505</v>
       </c>
-      <c r="J36" s="118"/>
-      <c r="K36" s="52"/>
+      <c r="J36" s="117"/>
+      <c r="K36" s="51"/>
       <c r="L36" s="4"/>
     </row>
     <row r="37" spans="1:12" ht="16.5">
-      <c r="A37" s="64">
+      <c r="A37" s="63">
         <v>34</v>
       </c>
-      <c r="B37" s="172" t="s">
-        <v>161</v>
-      </c>
-      <c r="C37" s="172"/>
-      <c r="D37" s="172"/>
-      <c r="E37" s="172"/>
-      <c r="F37" s="115"/>
-      <c r="G37" s="115"/>
-      <c r="H37" s="65"/>
-      <c r="I37" s="67" t="s">
+      <c r="B37" s="160" t="s">
         <v>157</v>
       </c>
-      <c r="J37" s="97"/>
-      <c r="K37" s="120"/>
+      <c r="C37" s="160"/>
+      <c r="D37" s="160"/>
+      <c r="E37" s="160"/>
+      <c r="F37" s="114"/>
+      <c r="G37" s="114"/>
+      <c r="H37" s="64"/>
+      <c r="I37" s="66" t="s">
+        <v>153</v>
+      </c>
+      <c r="J37" s="96"/>
+      <c r="K37" s="119"/>
       <c r="L37" s="4"/>
     </row>
     <row r="38" spans="1:12" ht="30">
-      <c r="A38" s="64">
+      <c r="A38" s="63">
         <v>35</v>
       </c>
-      <c r="B38" s="113" t="s">
-        <v>57</v>
+      <c r="B38" s="112" t="s">
+        <v>55</v>
       </c>
       <c r="C38" s="5">
         <v>83111000</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E38" s="7">
         <v>400</v>
@@ -5093,25 +5077,25 @@
         <v>49206</v>
       </c>
       <c r="J38" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="K38" s="51" t="s">
-        <v>148</v>
+        <v>152</v>
+      </c>
+      <c r="K38" s="50" t="s">
+        <v>144</v>
       </c>
       <c r="L38" s="4"/>
     </row>
     <row r="39" spans="1:12" ht="30">
-      <c r="A39" s="64">
+      <c r="A39" s="63">
         <v>36</v>
       </c>
-      <c r="B39" s="113" t="s">
-        <v>59</v>
+      <c r="B39" s="112" t="s">
+        <v>57</v>
       </c>
       <c r="C39" s="5">
         <v>83111000</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E39" s="7">
         <v>300</v>
@@ -5131,25 +5115,25 @@
         <v>37701</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="K39" s="51" t="s">
-        <v>148</v>
+        <v>152</v>
+      </c>
+      <c r="K39" s="50" t="s">
+        <v>144</v>
       </c>
       <c r="L39" s="4"/>
     </row>
     <row r="40" spans="1:12" ht="30">
-      <c r="A40" s="64">
+      <c r="A40" s="63">
         <v>37</v>
       </c>
-      <c r="B40" s="113" t="s">
-        <v>60</v>
+      <c r="B40" s="112" t="s">
+        <v>58</v>
       </c>
       <c r="C40" s="5">
         <v>83111000</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E40" s="7">
         <v>300</v>
@@ -5169,64 +5153,64 @@
         <v>31258.199999999997</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="K40" s="51" t="s">
-        <v>148</v>
+        <v>152</v>
+      </c>
+      <c r="K40" s="50" t="s">
+        <v>144</v>
       </c>
       <c r="L40" s="4"/>
     </row>
     <row r="41" spans="1:12" ht="16.5">
-      <c r="A41" s="64">
+      <c r="A41" s="63">
         <v>38</v>
       </c>
-      <c r="B41" s="97"/>
-      <c r="C41" s="117"/>
-      <c r="D41" s="117"/>
-      <c r="E41" s="174" t="s">
+      <c r="B41" s="96"/>
+      <c r="C41" s="116"/>
+      <c r="D41" s="116"/>
+      <c r="E41" s="162" t="s">
         <v>24</v>
       </c>
-      <c r="F41" s="174"/>
-      <c r="G41" s="174"/>
-      <c r="H41" s="118"/>
-      <c r="I41" s="119">
+      <c r="F41" s="162"/>
+      <c r="G41" s="162"/>
+      <c r="H41" s="117"/>
+      <c r="I41" s="118">
         <f>SUM(I38:I40)</f>
         <v>118165.2</v>
       </c>
-      <c r="J41" s="118"/>
-      <c r="K41" s="50"/>
+      <c r="J41" s="117"/>
+      <c r="K41" s="49"/>
       <c r="L41" s="4"/>
     </row>
     <row r="42" spans="1:12" ht="16.5">
-      <c r="A42" s="64">
+      <c r="A42" s="63">
         <v>39</v>
       </c>
-      <c r="B42" s="165" t="s">
-        <v>160</v>
-      </c>
-      <c r="C42" s="165"/>
-      <c r="D42" s="165"/>
-      <c r="E42" s="121"/>
-      <c r="F42" s="122"/>
-      <c r="G42" s="122"/>
-      <c r="H42" s="121"/>
-      <c r="I42" s="122"/>
-      <c r="J42" s="123"/>
-      <c r="K42" s="124"/>
+      <c r="B42" s="168" t="s">
+        <v>156</v>
+      </c>
+      <c r="C42" s="168"/>
+      <c r="D42" s="168"/>
+      <c r="E42" s="120"/>
+      <c r="F42" s="121"/>
+      <c r="G42" s="121"/>
+      <c r="H42" s="120"/>
+      <c r="I42" s="121"/>
+      <c r="J42" s="122"/>
+      <c r="K42" s="123"/>
       <c r="L42" s="4"/>
     </row>
     <row r="43" spans="1:12" ht="30">
-      <c r="A43" s="64">
+      <c r="A43" s="63">
         <v>40</v>
       </c>
-      <c r="B43" s="113" t="s">
-        <v>57</v>
+      <c r="B43" s="112" t="s">
+        <v>55</v>
       </c>
       <c r="C43" s="5">
         <v>83111000</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E43" s="7">
         <v>400</v>
@@ -5246,23 +5230,23 @@
       <c r="J43" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K43" s="69" t="s">
-        <v>58</v>
+      <c r="K43" s="68" t="s">
+        <v>56</v>
       </c>
       <c r="L43" s="4"/>
     </row>
     <row r="44" spans="1:12" ht="30">
-      <c r="A44" s="64">
+      <c r="A44" s="63">
         <v>41</v>
       </c>
-      <c r="B44" s="113" t="s">
-        <v>59</v>
+      <c r="B44" s="112" t="s">
+        <v>57</v>
       </c>
       <c r="C44" s="5">
         <v>83111000</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E44" s="7">
         <v>300</v>
@@ -5282,23 +5266,23 @@
       <c r="J44" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K44" s="69" t="s">
+      <c r="K44" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="L44" s="4"/>
+    </row>
+    <row r="45" spans="1:12" ht="30">
+      <c r="A45" s="63">
+        <v>42</v>
+      </c>
+      <c r="B45" s="112" t="s">
         <v>58</v>
-      </c>
-      <c r="L44" s="4"/>
-    </row>
-    <row r="45" spans="1:12" ht="30">
-      <c r="A45" s="64">
-        <v>42</v>
-      </c>
-      <c r="B45" s="113" t="s">
-        <v>60</v>
       </c>
       <c r="C45" s="5">
         <v>83111000</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E45" s="7">
         <v>300</v>
@@ -5318,33 +5302,33 @@
       <c r="J45" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K45" s="69" t="s">
-        <v>58</v>
+      <c r="K45" s="68" t="s">
+        <v>56</v>
       </c>
       <c r="L45" s="4"/>
     </row>
     <row r="46" spans="1:12" ht="16.5">
-      <c r="A46" s="64">
+      <c r="A46" s="63">
         <v>43</v>
       </c>
-      <c r="B46" s="114"/>
+      <c r="B46" s="113"/>
       <c r="C46" s="5"/>
-      <c r="D46" s="166" t="s">
+      <c r="D46" s="154" t="s">
         <v>24</v>
       </c>
-      <c r="E46" s="166"/>
-      <c r="F46" s="166"/>
-      <c r="G46" s="166"/>
+      <c r="E46" s="154"/>
+      <c r="F46" s="154"/>
+      <c r="G46" s="154"/>
       <c r="H46" s="11"/>
       <c r="I46" s="12">
         <v>124608</v>
       </c>
       <c r="J46" s="9"/>
-      <c r="K46" s="69"/>
+      <c r="K46" s="68"/>
       <c r="L46" s="4"/>
     </row>
     <row r="47" spans="1:12" ht="16.5">
-      <c r="A47" s="64">
+      <c r="A47" s="63">
         <v>44</v>
       </c>
       <c r="B47" s="4"/>
@@ -5360,35 +5344,35 @@
       <c r="L47" s="4"/>
     </row>
     <row r="48" spans="1:12" ht="16.5">
-      <c r="A48" s="64">
+      <c r="A48" s="63">
         <v>45</v>
       </c>
-      <c r="B48" s="173" t="s">
-        <v>159</v>
-      </c>
-      <c r="C48" s="173"/>
-      <c r="D48" s="173"/>
-      <c r="E48" s="173"/>
-      <c r="F48" s="115"/>
-      <c r="G48" s="115"/>
-      <c r="H48" s="65"/>
-      <c r="I48" s="67"/>
-      <c r="J48" s="97"/>
-      <c r="K48" s="116"/>
+      <c r="B48" s="161" t="s">
+        <v>155</v>
+      </c>
+      <c r="C48" s="161"/>
+      <c r="D48" s="161"/>
+      <c r="E48" s="161"/>
+      <c r="F48" s="114"/>
+      <c r="G48" s="114"/>
+      <c r="H48" s="64"/>
+      <c r="I48" s="66"/>
+      <c r="J48" s="96"/>
+      <c r="K48" s="115"/>
       <c r="L48" s="4"/>
     </row>
     <row r="49" spans="1:12" ht="30">
-      <c r="A49" s="64">
+      <c r="A49" s="63">
         <v>46</v>
       </c>
-      <c r="B49" s="113" t="s">
-        <v>57</v>
+      <c r="B49" s="112" t="s">
+        <v>55</v>
       </c>
       <c r="C49" s="5">
         <v>83111000</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E49" s="7">
         <v>400</v>
@@ -5406,25 +5390,25 @@
         <v>64003.199999999997</v>
       </c>
       <c r="J49" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K49" s="125" t="s">
-        <v>84</v>
+        <v>81</v>
+      </c>
+      <c r="K49" s="124" t="s">
+        <v>82</v>
       </c>
       <c r="L49" s="4"/>
     </row>
     <row r="50" spans="1:12" ht="30">
-      <c r="A50" s="64">
+      <c r="A50" s="63">
         <v>47</v>
       </c>
-      <c r="B50" s="113" t="s">
-        <v>59</v>
+      <c r="B50" s="112" t="s">
+        <v>57</v>
       </c>
       <c r="C50" s="5">
         <v>83111000</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E50" s="7">
         <v>300</v>
@@ -5442,25 +5426,25 @@
         <v>38409</v>
       </c>
       <c r="J50" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K50" s="125" t="s">
-        <v>84</v>
+        <v>81</v>
+      </c>
+      <c r="K50" s="124" t="s">
+        <v>82</v>
       </c>
       <c r="L50" s="4"/>
     </row>
     <row r="51" spans="1:12" ht="30">
-      <c r="A51" s="64">
+      <c r="A51" s="63">
         <v>48</v>
       </c>
-      <c r="B51" s="113" t="s">
-        <v>60</v>
+      <c r="B51" s="112" t="s">
+        <v>58</v>
       </c>
       <c r="C51" s="5">
         <v>83111000</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E51" s="7">
         <v>300</v>
@@ -5478,40 +5462,45 @@
         <v>50409.599999999999</v>
       </c>
       <c r="J51" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K51" s="125" t="s">
-        <v>84</v>
+        <v>81</v>
+      </c>
+      <c r="K51" s="124" t="s">
+        <v>82</v>
       </c>
       <c r="L51" s="4"/>
     </row>
     <row r="52" spans="1:12" ht="16.5">
-      <c r="A52" s="64">
+      <c r="A52" s="63">
         <v>49</v>
       </c>
-      <c r="B52" s="97"/>
-      <c r="C52" s="50"/>
-      <c r="D52" s="50"/>
-      <c r="E52" s="168" t="s">
+      <c r="B52" s="96"/>
+      <c r="C52" s="49"/>
+      <c r="D52" s="49"/>
+      <c r="E52" s="156" t="s">
         <v>24</v>
       </c>
-      <c r="F52" s="168"/>
-      <c r="G52" s="168"/>
-      <c r="H52" s="126"/>
-      <c r="I52" s="119">
+      <c r="F52" s="156"/>
+      <c r="G52" s="156"/>
+      <c r="H52" s="125"/>
+      <c r="I52" s="118">
         <v>152821.79999999999</v>
       </c>
-      <c r="J52" s="126"/>
-      <c r="K52" s="50"/>
+      <c r="J52" s="125"/>
+      <c r="K52" s="49"/>
       <c r="L52" s="4"/>
     </row>
     <row r="56" spans="1:12">
       <c r="I56" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="C1:I2"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="B42:D42"/>
     <mergeCell ref="D46:G46"/>
     <mergeCell ref="D8:H8"/>
     <mergeCell ref="E52:G52"/>
@@ -5525,13 +5514,8 @@
     <mergeCell ref="E36:G36"/>
     <mergeCell ref="B37:E37"/>
     <mergeCell ref="E41:G41"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="C1:I2"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="B42:D42"/>
   </mergeCells>
-  <phoneticPr fontId="59" type="noConversion"/>
+  <phoneticPr fontId="58" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="K33" r:id="rId1" display="tel:(984) 984-7406" xr:uid="{36C33CB2-1B0D-4DCD-8A20-C5F42E2F1A7F}"/>
     <hyperlink ref="K34:K35" r:id="rId2" display="tel:(984) 984-7406" xr:uid="{18B6AA11-A32B-472A-83C6-6FA12FE4B747}"/>
@@ -5578,65 +5562,65 @@
       <c r="N1" s="4"/>
     </row>
     <row r="2" spans="1:14" ht="18.75">
-      <c r="A2" s="144" t="s">
+      <c r="A2" s="169" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2" s="170"/>
+      <c r="C2" s="170"/>
+      <c r="D2" s="170"/>
+      <c r="E2" s="170"/>
+      <c r="F2" s="170"/>
+      <c r="G2" s="170"/>
+      <c r="H2" s="170"/>
+      <c r="I2" s="170"/>
+      <c r="J2" s="170"/>
+      <c r="K2" s="170"/>
+      <c r="L2" s="170"/>
+      <c r="M2" s="170"/>
+      <c r="N2" s="4"/>
+    </row>
+    <row r="3" spans="1:14" ht="30">
+      <c r="A3" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="F3" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" s="52" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="145"/>
-      <c r="C2" s="145"/>
-      <c r="D2" s="145"/>
-      <c r="E2" s="145"/>
-      <c r="F2" s="145"/>
-      <c r="G2" s="145"/>
-      <c r="H2" s="145"/>
-      <c r="I2" s="145"/>
-      <c r="J2" s="145"/>
-      <c r="K2" s="145"/>
-      <c r="L2" s="145"/>
-      <c r="M2" s="145"/>
-      <c r="N2" s="4"/>
-    </row>
-    <row r="3" spans="1:14" ht="30">
-      <c r="A3" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="30" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="30" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="30" t="s">
+      <c r="H3" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="F3" s="30" t="s">
-        <v>50</v>
-      </c>
-      <c r="G3" s="53" t="s">
+      <c r="I3" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="H3" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="I3" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" s="31" t="s">
+      <c r="K3" s="52" t="s">
+        <v>158</v>
+      </c>
+      <c r="L3" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="K3" s="53" t="s">
-        <v>162</v>
-      </c>
-      <c r="L3" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="M3" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="N3" s="53" t="s">
-        <v>169</v>
+      <c r="M3" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="N3" s="52" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="15.75">
@@ -5644,11 +5628,11 @@
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C4" s="6"/>
       <c r="D4" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E4" s="6">
         <v>25</v>
@@ -5661,7 +5645,7 @@
         <v>560</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I4" s="6">
         <v>18</v>
@@ -5670,12 +5654,12 @@
         <f>G4*(1+I4/100)</f>
         <v>660.8</v>
       </c>
-      <c r="K4" s="46">
+      <c r="K4" s="45">
         <f>E4*J4</f>
         <v>16520</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="M4" s="6">
         <v>9848196449</v>
@@ -5687,11 +5671,11 @@
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E5" s="6">
         <v>25</v>
@@ -5704,7 +5688,7 @@
         <v>575</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I5" s="6">
         <v>18</v>
@@ -5713,7 +5697,7 @@
         <f>G5*(1+I5/100)</f>
         <v>678.5</v>
       </c>
-      <c r="K5" s="46">
+      <c r="K5" s="45">
         <f>E5*J5</f>
         <v>16962.5</v>
       </c>
@@ -5726,63 +5710,63 @@
       <c r="N5" s="4"/>
     </row>
     <row r="6" spans="1:14" ht="15.75">
-      <c r="A6" s="26">
+      <c r="A6" s="25">
         <v>3</v>
       </c>
-      <c r="B6" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48" t="s">
-        <v>98</v>
-      </c>
-      <c r="E6" s="48">
+      <c r="B6" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="47"/>
+      <c r="D6" s="47" t="s">
+        <v>96</v>
+      </c>
+      <c r="E6" s="47">
         <v>30</v>
       </c>
-      <c r="F6" s="48">
+      <c r="F6" s="47">
         <v>10.9</v>
       </c>
-      <c r="G6" s="48">
+      <c r="G6" s="47">
         <f>50*F6</f>
         <v>545</v>
       </c>
-      <c r="H6" s="48" t="s">
-        <v>95</v>
-      </c>
-      <c r="I6" s="48">
+      <c r="H6" s="47" t="s">
+        <v>93</v>
+      </c>
+      <c r="I6" s="47">
         <v>5</v>
       </c>
-      <c r="J6" s="48">
+      <c r="J6" s="47">
         <f>G6*(1+I6/100)</f>
         <v>572.25</v>
       </c>
-      <c r="K6" s="46">
+      <c r="K6" s="45">
         <f>E6*J6</f>
         <v>17167.5</v>
       </c>
-      <c r="L6" s="48" t="s">
-        <v>99</v>
-      </c>
-      <c r="M6" s="48">
+      <c r="L6" s="47" t="s">
+        <v>97</v>
+      </c>
+      <c r="M6" s="47">
         <v>7989960246</v>
       </c>
-      <c r="N6" s="60" t="s">
-        <v>172</v>
+      <c r="N6" s="59" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15.75">
-      <c r="A7" s="32"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="29"/>
-      <c r="J7" s="29"/>
-      <c r="K7" s="47"/>
-      <c r="L7" s="29"/>
-      <c r="M7" s="29"/>
+      <c r="A7" s="31"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="28"/>
+      <c r="K7" s="46"/>
+      <c r="L7" s="28"/>
+      <c r="M7" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5813,15 +5797,15 @@
     <row r="1" spans="1:12">
       <c r="A1" s="4"/>
       <c r="B1" s="4"/>
-      <c r="C1" s="175" t="s">
-        <v>100</v>
-      </c>
-      <c r="D1" s="176"/>
-      <c r="E1" s="176"/>
-      <c r="F1" s="176"/>
-      <c r="G1" s="176"/>
-      <c r="H1" s="176"/>
-      <c r="I1" s="176"/>
+      <c r="C1" s="171" t="s">
+        <v>98</v>
+      </c>
+      <c r="D1" s="172"/>
+      <c r="E1" s="172"/>
+      <c r="F1" s="172"/>
+      <c r="G1" s="172"/>
+      <c r="H1" s="172"/>
+      <c r="I1" s="172"/>
       <c r="J1" s="4"/>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
@@ -5829,13 +5813,13 @@
     <row r="2" spans="1:12">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
-      <c r="C2" s="176"/>
-      <c r="D2" s="176"/>
-      <c r="E2" s="176"/>
-      <c r="F2" s="176"/>
-      <c r="G2" s="176"/>
-      <c r="H2" s="176"/>
-      <c r="I2" s="176"/>
+      <c r="C2" s="172"/>
+      <c r="D2" s="172"/>
+      <c r="E2" s="172"/>
+      <c r="F2" s="172"/>
+      <c r="G2" s="172"/>
+      <c r="H2" s="172"/>
+      <c r="I2" s="172"/>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
@@ -5854,13 +5838,13 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>8</v>
@@ -5875,17 +5859,17 @@
         <v>11</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="177" t="s">
-        <v>102</v>
-      </c>
-      <c r="B4" s="177"/>
-      <c r="C4" s="177"/>
-      <c r="D4" s="177"/>
-      <c r="E4" s="26"/>
+      <c r="A4" s="173" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4" s="173"/>
+      <c r="C4" s="173"/>
+      <c r="D4" s="173"/>
+      <c r="E4" s="25"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
@@ -5895,106 +5879,106 @@
       <c r="L4" s="4"/>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="26">
+      <c r="A5" s="25">
         <v>1</v>
       </c>
-      <c r="B5" s="33" t="s">
-        <v>103</v>
-      </c>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="E5" s="26">
+      <c r="B5" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="E5" s="25">
         <v>130</v>
       </c>
-      <c r="F5" s="26">
+      <c r="F5" s="25">
         <v>34</v>
       </c>
-      <c r="G5" s="26">
+      <c r="G5" s="25">
         <f>F5*E5</f>
         <v>4420</v>
       </c>
-      <c r="H5" s="26">
+      <c r="H5" s="25">
         <v>18</v>
       </c>
-      <c r="I5" s="26">
+      <c r="I5" s="25">
         <f>G5*(1+H5/100)</f>
         <v>5215.5999999999995</v>
       </c>
-      <c r="J5" s="26" t="s">
+      <c r="J5" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="K5" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="L5" s="4"/>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="25">
+        <v>2</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="K5" s="26" t="s">
-        <v>106</v>
-      </c>
-      <c r="L5" s="4"/>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="26">
-        <v>2</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>107</v>
-      </c>
       <c r="C6" s="4"/>
-      <c r="D6" s="26" t="s">
-        <v>152</v>
-      </c>
-      <c r="E6" s="26">
+      <c r="D6" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="E6" s="25">
         <v>25</v>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="25">
         <v>900</v>
       </c>
-      <c r="G6" s="26">
+      <c r="G6" s="25">
         <f>F6*E6</f>
         <v>22500</v>
       </c>
-      <c r="H6" s="26">
+      <c r="H6" s="25">
         <v>18</v>
       </c>
-      <c r="I6" s="26">
+      <c r="I6" s="25">
         <f>G6*(1+H6/100)</f>
         <v>26550</v>
       </c>
-      <c r="J6" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="K6" s="26" t="s">
-        <v>108</v>
+      <c r="J6" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="K6" s="25" t="s">
+        <v>106</v>
       </c>
       <c r="L6" s="4"/>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="26">
+      <c r="A7" s="25">
         <v>3</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="154" t="s">
+      <c r="D7" s="33"/>
+      <c r="E7" s="152" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="154"/>
-      <c r="G7" s="154"/>
-      <c r="H7" s="25"/>
-      <c r="I7" s="25">
+      <c r="F7" s="152"/>
+      <c r="G7" s="152"/>
+      <c r="H7" s="24"/>
+      <c r="I7" s="24">
         <f>SUM(I5:I6)</f>
         <v>31765.599999999999</v>
       </c>
-      <c r="J7" s="26"/>
-      <c r="K7" s="26"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
       <c r="L7" s="4"/>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="177" t="s">
-        <v>109</v>
-      </c>
-      <c r="B8" s="177"/>
-      <c r="C8" s="177"/>
-      <c r="D8" s="177"/>
-      <c r="E8" s="26"/>
+      <c r="A8" s="173" t="s">
+        <v>107</v>
+      </c>
+      <c r="B8" s="173"/>
+      <c r="C8" s="173"/>
+      <c r="D8" s="173"/>
+      <c r="E8" s="25"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
@@ -6004,15 +5988,15 @@
       <c r="L8" s="4"/>
     </row>
     <row r="9" spans="1:12" ht="30">
-      <c r="A9" s="26">
+      <c r="A9" s="25">
         <v>4</v>
       </c>
-      <c r="B9" s="35" t="s">
-        <v>110</v>
+      <c r="B9" s="34" t="s">
+        <v>108</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E9" s="6">
         <v>135</v>
@@ -6032,45 +6016,45 @@
         <v>5949.8549999999996</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K9" s="6">
         <v>9848196449</v>
       </c>
-      <c r="L9" s="59" t="s">
-        <v>171</v>
+      <c r="L9" s="58" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="26">
+      <c r="A10" s="25">
         <v>5</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C10" s="4"/>
-      <c r="D10" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="E10" s="26">
+      <c r="D10" s="25" t="s">
+        <v>109</v>
+      </c>
+      <c r="E10" s="25">
         <v>25</v>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="25">
         <v>335</v>
       </c>
-      <c r="G10" s="26">
+      <c r="G10" s="25">
         <f>F10*E10</f>
         <v>8375</v>
       </c>
-      <c r="H10" s="26">
+      <c r="H10" s="25">
         <v>18</v>
       </c>
-      <c r="I10" s="26">
+      <c r="I10" s="25">
         <f>G10*(1+H10/100)</f>
         <v>9882.5</v>
       </c>
-      <c r="J10" s="26" t="s">
-        <v>105</v>
+      <c r="J10" s="25" t="s">
+        <v>103</v>
       </c>
       <c r="K10" s="6">
         <v>9848196449</v>
@@ -6078,24 +6062,24 @@
       <c r="L10" s="4"/>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="26">
+      <c r="A11" s="25">
         <v>6</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
-      <c r="D11" s="34"/>
-      <c r="E11" s="154" t="s">
+      <c r="D11" s="33"/>
+      <c r="E11" s="152" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="154"/>
-      <c r="G11" s="154"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="25">
+      <c r="F11" s="152"/>
+      <c r="G11" s="152"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="24">
         <f>SUM(I9:I10)</f>
         <v>15832.355</v>
       </c>
-      <c r="J11" s="26"/>
-      <c r="K11" s="26"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
       <c r="L11" s="4"/>
     </row>
   </sheetData>
@@ -6126,289 +6110,289 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21">
-      <c r="A1" s="178" t="s">
+      <c r="A1" s="174" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" s="175"/>
+      <c r="C1" s="175"/>
+      <c r="D1" s="175"/>
+      <c r="E1" s="175"/>
+      <c r="F1" s="175"/>
+      <c r="G1" s="175"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.75">
+      <c r="A3" s="176" t="s">
+        <v>181</v>
+      </c>
+      <c r="B3" s="176"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="35" t="s">
+        <v>112</v>
+      </c>
+      <c r="B4" s="35" t="s">
         <v>113</v>
       </c>
-      <c r="B1" s="179"/>
-      <c r="C1" s="179"/>
-      <c r="D1" s="179"/>
-      <c r="E1" s="179"/>
-      <c r="F1" s="179"/>
-      <c r="G1" s="179"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75">
-      <c r="A3" s="180" t="s">
+      <c r="C4" s="35" t="s">
         <v>114</v>
       </c>
-      <c r="B3" s="180"/>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="36" t="s">
+      <c r="D4" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="35" t="s">
         <v>115</v>
       </c>
-      <c r="B4" s="36" t="s">
+      <c r="F4" s="35" t="s">
         <v>116</v>
       </c>
-      <c r="C4" s="36" t="s">
+      <c r="G4" s="35" t="s">
         <v>117</v>
       </c>
-      <c r="D4" s="36" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="36" t="s">
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="36">
+        <v>1</v>
+      </c>
+      <c r="B5" s="37" t="s">
         <v>118</v>
       </c>
-      <c r="F4" s="36" t="s">
+      <c r="C5" s="36" t="s">
         <v>119</v>
       </c>
-      <c r="G4" s="36" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="37">
+      <c r="D5" s="36">
         <v>1</v>
       </c>
-      <c r="B5" s="38" t="s">
-        <v>121</v>
-      </c>
-      <c r="C5" s="37" t="s">
-        <v>122</v>
-      </c>
-      <c r="D5" s="37">
-        <v>1</v>
-      </c>
-      <c r="E5" s="39">
+      <c r="E5" s="38">
         <v>135000</v>
       </c>
-      <c r="F5" s="39">
+      <c r="F5" s="38">
         <v>130000</v>
       </c>
-      <c r="G5" s="39">
+      <c r="G5" s="38">
         <f>D5*F5</f>
         <v>130000</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="37">
+      <c r="A6" s="36">
         <v>2</v>
       </c>
-      <c r="B6" s="38" t="s">
-        <v>123</v>
-      </c>
-      <c r="C6" s="37" t="s">
-        <v>124</v>
-      </c>
-      <c r="D6" s="37">
+      <c r="B6" s="37" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6" s="36" t="s">
+        <v>121</v>
+      </c>
+      <c r="D6" s="36">
         <v>1</v>
       </c>
-      <c r="E6" s="39">
+      <c r="E6" s="38">
         <v>125000</v>
       </c>
-      <c r="F6" s="39">
+      <c r="F6" s="38">
         <v>120000</v>
       </c>
-      <c r="G6" s="39">
+      <c r="G6" s="38">
         <f>D6*F6</f>
         <v>120000</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="B7" s="40" t="s">
-        <v>125</v>
-      </c>
-      <c r="G7" s="41">
+      <c r="B7" s="39" t="s">
+        <v>122</v>
+      </c>
+      <c r="G7" s="40">
         <f>SUM(G5:G6)</f>
         <v>250000</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="B8" s="40" t="s">
-        <v>126</v>
-      </c>
-      <c r="G8" s="41">
+      <c r="B8" s="39" t="s">
+        <v>123</v>
+      </c>
+      <c r="G8" s="40">
         <f>G7*0.18</f>
         <v>45000</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15.75" thickBot="1">
-      <c r="B9" s="40" t="s">
-        <v>127</v>
-      </c>
-      <c r="G9" s="42">
+      <c r="B9" s="39" t="s">
+        <v>124</v>
+      </c>
+      <c r="G9" s="41">
         <f>G7+G8</f>
         <v>295000</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15.75" thickTop="1"/>
     <row r="11" spans="1:7">
-      <c r="B11" s="40" t="s">
+      <c r="B11" s="39" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="B12" s="42" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="B13" s="42" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="B14" s="42" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
-      <c r="B12" s="43" t="s">
+    <row r="15" spans="1:7" ht="24.75">
+      <c r="B15" s="43" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
-      <c r="B13" s="43" t="s">
+    <row r="16" spans="1:7">
+      <c r="B16" s="42" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
-      <c r="B14" s="43" t="s">
+    <row r="17" spans="1:7">
+      <c r="B17" s="42" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="24.75">
-      <c r="B15" s="44" t="s">
+    <row r="20" spans="1:7" ht="15.75">
+      <c r="A20" s="176" t="s">
+        <v>180</v>
+      </c>
+      <c r="B20" s="177"/>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="35" t="s">
+        <v>112</v>
+      </c>
+      <c r="B21" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="C21" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="D21" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="E21" s="35" t="s">
+        <v>115</v>
+      </c>
+      <c r="F21" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="G21" s="35" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="30">
+      <c r="A22" s="36">
+        <v>1</v>
+      </c>
+      <c r="B22" s="44" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="B16" s="43" t="s">
+      <c r="C22" s="36" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="B17" s="43" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="15.75">
-      <c r="A20" s="180" t="s">
-        <v>135</v>
-      </c>
-      <c r="B20" s="181"/>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="36" t="s">
-        <v>115</v>
-      </c>
-      <c r="B21" s="36" t="s">
-        <v>116</v>
-      </c>
-      <c r="C21" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="D21" s="36" t="s">
-        <v>5</v>
-      </c>
-      <c r="E21" s="36" t="s">
-        <v>118</v>
-      </c>
-      <c r="F21" s="36" t="s">
-        <v>119</v>
-      </c>
-      <c r="G21" s="36" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="30">
-      <c r="A22" s="37">
+      <c r="D22" s="36">
         <v>1</v>
       </c>
-      <c r="B22" s="45" t="s">
-        <v>136</v>
-      </c>
-      <c r="C22" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="D22" s="37">
-        <v>1</v>
-      </c>
-      <c r="E22" s="39">
+      <c r="E22" s="38">
         <v>88000</v>
       </c>
-      <c r="F22" s="39">
+      <c r="F22" s="38">
         <v>88000</v>
       </c>
-      <c r="G22" s="39">
+      <c r="G22" s="38">
         <f>D22*F22</f>
         <v>88000</v>
       </c>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="37">
+      <c r="A23" s="36">
         <v>2</v>
       </c>
-      <c r="B23" s="38" t="s">
-        <v>138</v>
-      </c>
-      <c r="C23" s="37" t="s">
-        <v>139</v>
-      </c>
-      <c r="D23" s="37">
+      <c r="B23" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="C23" s="36" t="s">
+        <v>135</v>
+      </c>
+      <c r="D23" s="36">
         <v>1</v>
       </c>
-      <c r="E23" s="39">
+      <c r="E23" s="38">
         <v>5500</v>
       </c>
-      <c r="F23" s="39">
+      <c r="F23" s="38">
         <v>5500</v>
       </c>
-      <c r="G23" s="39">
+      <c r="G23" s="38">
         <f>D23*F23</f>
         <v>5500</v>
       </c>
     </row>
     <row r="24" spans="1:7">
-      <c r="B24" s="40" t="s">
-        <v>125</v>
-      </c>
-      <c r="G24" s="41">
+      <c r="B24" s="39" t="s">
+        <v>122</v>
+      </c>
+      <c r="G24" s="40">
         <f>SUM(G22:G23)</f>
         <v>93500</v>
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="B25" s="40" t="s">
-        <v>126</v>
-      </c>
-      <c r="G25" s="41">
+      <c r="B25" s="39" t="s">
+        <v>123</v>
+      </c>
+      <c r="G25" s="40">
         <f>G24*0.18</f>
         <v>16830</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15.75" thickBot="1">
-      <c r="B26" s="40" t="s">
-        <v>140</v>
-      </c>
-      <c r="G26" s="42">
+      <c r="B26" s="39" t="s">
+        <v>136</v>
+      </c>
+      <c r="G26" s="41">
         <f>G24+G25</f>
         <v>110330</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15.75" thickTop="1"/>
     <row r="28" spans="1:7">
-      <c r="B28" s="40" t="s">
-        <v>146</v>
+      <c r="B28" s="39" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="29" spans="1:7">
-      <c r="B29" s="43" t="s">
+      <c r="B29" s="42" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="B30" s="42" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="B31" s="42" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="B32" s="42" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" s="42" t="s">
         <v>141</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="B30" s="43" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="B31" s="43" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="B32" s="43" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2">
-      <c r="B33" s="43" t="s">
-        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -6439,87 +6423,87 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18.75">
-      <c r="A1" s="144" t="s">
-        <v>163</v>
-      </c>
-      <c r="B1" s="145"/>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
-      <c r="F1" s="145"/>
-      <c r="G1" s="145"/>
-      <c r="H1" s="145"/>
-      <c r="I1" s="145"/>
-      <c r="J1" s="145"/>
-      <c r="K1" s="145"/>
+      <c r="A1" s="169" t="s">
+        <v>159</v>
+      </c>
+      <c r="B1" s="170"/>
+      <c r="C1" s="170"/>
+      <c r="D1" s="170"/>
+      <c r="E1" s="170"/>
+      <c r="F1" s="170"/>
+      <c r="G1" s="170"/>
+      <c r="H1" s="170"/>
+      <c r="I1" s="170"/>
+      <c r="J1" s="170"/>
+      <c r="K1" s="170"/>
       <c r="L1" s="4"/>
     </row>
     <row r="2" spans="1:12" ht="30">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="55" t="s">
+      <c r="C2" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="58" t="s">
+      <c r="D2" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="56" t="s">
+      <c r="E2" s="55" t="s">
+        <v>161</v>
+      </c>
+      <c r="F2" s="56" t="s">
+        <v>178</v>
+      </c>
+      <c r="G2" s="129" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="54" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="56" t="s">
+        <v>158</v>
+      </c>
+      <c r="J2" s="55" t="s">
+        <v>162</v>
+      </c>
+      <c r="K2" s="54" t="s">
+        <v>90</v>
+      </c>
+      <c r="L2" s="56" t="s">
         <v>165</v>
       </c>
-      <c r="F2" s="57" t="s">
-        <v>182</v>
-      </c>
-      <c r="G2" s="130" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="55" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="57" t="s">
-        <v>162</v>
-      </c>
-      <c r="J2" s="56" t="s">
-        <v>166</v>
-      </c>
-      <c r="K2" s="55" t="s">
-        <v>92</v>
-      </c>
-      <c r="L2" s="57" t="s">
-        <v>169</v>
-      </c>
     </row>
     <row r="3" spans="1:12" ht="15.75">
-      <c r="A3" s="140"/>
-      <c r="B3" s="146" t="s">
-        <v>180</v>
-      </c>
-      <c r="C3" s="147"/>
-      <c r="D3" s="138"/>
-      <c r="E3" s="139"/>
-      <c r="F3" s="139"/>
-      <c r="G3" s="140"/>
-      <c r="H3" s="137"/>
-      <c r="I3" s="141"/>
-      <c r="J3" s="139"/>
-      <c r="K3" s="137"/>
-      <c r="L3" s="141"/>
+      <c r="A3" s="139"/>
+      <c r="B3" s="178" t="s">
+        <v>176</v>
+      </c>
+      <c r="C3" s="179"/>
+      <c r="D3" s="137"/>
+      <c r="E3" s="138"/>
+      <c r="F3" s="138"/>
+      <c r="G3" s="139"/>
+      <c r="H3" s="136"/>
+      <c r="I3" s="140"/>
+      <c r="J3" s="138"/>
+      <c r="K3" s="136"/>
+      <c r="L3" s="140"/>
     </row>
     <row r="4" spans="1:12" ht="15.75">
       <c r="A4" s="6">
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C4" s="6">
         <v>7318</v>
       </c>
       <c r="D4" s="6"/>
-      <c r="E4" s="54">
+      <c r="E4" s="53">
         <v>1000</v>
       </c>
       <c r="F4" s="6">
@@ -6532,48 +6516,48 @@
       <c r="H4" s="6">
         <v>18</v>
       </c>
-      <c r="I4" s="46">
+      <c r="I4" s="45">
         <f>G4*(1+H4/100)</f>
         <v>11682</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K4" s="6">
         <v>9100868002</v>
       </c>
-      <c r="L4" s="60" t="s">
-        <v>170</v>
+      <c r="L4" s="59" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15.75">
       <c r="A5" s="6"/>
-      <c r="B5" s="146" t="s">
-        <v>181</v>
-      </c>
-      <c r="C5" s="148"/>
+      <c r="B5" s="178" t="s">
+        <v>177</v>
+      </c>
+      <c r="C5" s="152"/>
       <c r="D5" s="6"/>
-      <c r="E5" s="54"/>
+      <c r="E5" s="53"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
-      <c r="I5" s="46"/>
+      <c r="I5" s="45"/>
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
-      <c r="L5" s="142"/>
+      <c r="L5" s="141"/>
     </row>
     <row r="6" spans="1:12" ht="15.75">
       <c r="A6" s="6">
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C6" s="6">
         <v>7318</v>
       </c>
       <c r="D6" s="6"/>
-      <c r="E6" s="54">
+      <c r="E6" s="53">
         <v>1000</v>
       </c>
       <c r="F6" s="6">
@@ -6586,34 +6570,34 @@
       <c r="H6" s="6">
         <v>18</v>
       </c>
-      <c r="I6" s="46">
+      <c r="I6" s="45">
         <f>G6*(1+H6/100)</f>
         <v>13924</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="L6" s="4"/>
     </row>
     <row r="7" spans="1:12" ht="15.75">
-      <c r="A7" s="26"/>
-      <c r="B7" s="34"/>
-      <c r="C7" s="48"/>
+      <c r="A7" s="25"/>
+      <c r="B7" s="33"/>
+      <c r="C7" s="47"/>
       <c r="D7" s="6"/>
-      <c r="E7" s="48"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="46"/>
-      <c r="J7" s="48"/>
-      <c r="K7" s="48"/>
+      <c r="E7" s="47"/>
+      <c r="F7" s="47"/>
+      <c r="G7" s="47"/>
+      <c r="H7" s="47"/>
+      <c r="I7" s="45"/>
+      <c r="J7" s="47"/>
+      <c r="K7" s="47"/>
       <c r="L7" s="4"/>
     </row>
     <row r="20" spans="3:3">
-      <c r="C20" s="143"/>
+      <c r="C20" s="142"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/master Quotations_October_2026/Master_Quotation_Comparison Sheet.xlsx
+++ b/master Quotations_October_2026/Master_Quotation_Comparison Sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Purchase_List_October_2026\master Quotations_October_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C466F1EE-6722-4B88-8B4C-C4D62BA7C649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5654956-A2B0-4629-9731-0857800AEE39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" tabRatio="783" activeTab="4" xr2:uid="{EA74EA6A-41FE-42B7-B5E3-F15DF1371829}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" tabRatio="783" activeTab="5" xr2:uid="{EA74EA6A-41FE-42B7-B5E3-F15DF1371829}"/>
   </bookViews>
   <sheets>
     <sheet name="Cutting &amp; Grinding wheels" sheetId="1" r:id="rId1"/>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="193">
   <si>
     <t>CUTTING &amp; GRINDING WHEEL  MASTER SUPPLIER QUOTATION COMPARISON SHEET - KRISHI INFRATECH</t>
   </si>
@@ -1315,6 +1315,27 @@
   </si>
   <si>
     <t>7" CUTTING WHEELS "BOSCH"</t>
+  </si>
+  <si>
+    <t>Column1</t>
+  </si>
+  <si>
+    <t>Column2</t>
+  </si>
+  <si>
+    <t>Column3</t>
+  </si>
+  <si>
+    <t>Column4</t>
+  </si>
+  <si>
+    <t>Column5</t>
+  </si>
+  <si>
+    <t>Column6</t>
+  </si>
+  <si>
+    <t>Column7</t>
   </si>
 </sst>
 </file>
@@ -1898,7 +1919,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -1957,15 +1978,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -1989,12 +2001,73 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="187">
+  <cellXfs count="196">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2076,12 +2149,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2139,40 +2206,16 @@
     <xf numFmtId="0" fontId="55" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2209,9 +2252,6 @@
     <xf numFmtId="0" fontId="40" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2354,9 +2394,6 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2364,7 +2401,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="1" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2400,83 +2436,105 @@
     <xf numFmtId="0" fontId="46" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2488,52 +2546,1135 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="45" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="62" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="45">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF1F497D"/>
+          <bgColor rgb="FF1F497D"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF1F497D"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF1F497D"/>
+          <bgColor rgb="FF1F497D"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF1F497D"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF1F497D"/>
+          <bgColor rgb="FF1F497D"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2544,6 +3685,130 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{9231F5AC-9E99-4C89-850E-94488CBAA783}" name="Table9" displayName="Table9" ref="A3:L38" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="3" tableBorderDxfId="4">
+  <autoFilter ref="A3:L38" xr:uid="{9231F5AC-9E99-4C89-850E-94488CBAA783}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{15DCA7B0-3D7B-4203-9F3B-509E9970E44D}" name="S NO" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{A2BAC475-5BB6-4A08-A3A5-86FDC571BCC0}" name="Item Description &amp; Specifications" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{E101B100-6086-4641-9EC4-4CEE1C1B97C3}" name="HSN/SAC"/>
+    <tableColumn id="4" xr3:uid="{25161CD0-91E8-41A2-B439-4005B949CCF5}" name="UOM"/>
+    <tableColumn id="5" xr3:uid="{E3D18BCE-BE59-4568-ABD7-009363BC2324}" name="Qty"/>
+    <tableColumn id="6" xr3:uid="{E54CB389-4A01-4183-99F6-57F308315692}" name="Unit Rate (For pcs)"/>
+    <tableColumn id="7" xr3:uid="{40DDBC35-51AB-4475-B80D-F0E41804AB4E}" name="Taxable Amt"/>
+    <tableColumn id="8" xr3:uid="{7EF57418-AA91-4798-AAB2-D4EB3FDB8726}" name="GST (%)"/>
+    <tableColumn id="9" xr3:uid="{1006A575-F345-4706-9AB4-6712D61F9D67}" name="Total Amount"/>
+    <tableColumn id="10" xr3:uid="{6B21B842-49D4-4CEB-A52D-511E039B9D6B}" name="Dealers "/>
+    <tableColumn id="11" xr3:uid="{4EA7FC07-0A83-4004-BFC1-0BB453C33D4C}" name="Contact Dedails"/>
+    <tableColumn id="12" xr3:uid="{A9FCFBFF-D7D8-4634-A7A2-CB83F8568350}" name="FINALIZED THE QUOTATIOS"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{692DD7FC-8CA9-4ABC-8808-3FC7867B81E1}" name="Table8" displayName="Table8" ref="A3:L52" totalsRowShown="0" headerRowDxfId="5" dataDxfId="6" tableBorderDxfId="19">
+  <autoFilter ref="A3:L52" xr:uid="{692DD7FC-8CA9-4ABC-8808-3FC7867B81E1}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{34A670BD-8C56-40F7-9E3F-F54B415B4BF4}" name="S NO" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{79DE1427-32A3-4EFC-B258-F9270008D831}" name="Item Description &amp; Specifications" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{B6E62923-C94E-4375-8E7B-BBBC7CAE4F64}" name="HSN/SAC" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{897C79C9-8593-4848-B7EA-9CB855EC96C3}" name="UOM" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{618259BE-5755-4179-9A0B-5A53C520E8EC}" name="Qty" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{7D77A70E-D8BC-4011-ADC6-ECD0A744DE56}" name="Unit Rate (For Kg)" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{3247422F-5FDB-4CC3-8CF4-8C5FBC325AD5}" name="Taxable Amt" dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{BB479B2E-5DBA-4EE5-B910-57F9B172D88F}" name="GST (%)" dataDxfId="11"/>
+    <tableColumn id="9" xr3:uid="{12CC6DBC-1AAE-42C4-9B86-BADB5D0E2204}" name="Total Amount" dataDxfId="10"/>
+    <tableColumn id="10" xr3:uid="{53241028-E677-42AD-9820-82D7937BB922}" name="Dealers " dataDxfId="9"/>
+    <tableColumn id="11" xr3:uid="{82679904-6DF9-4180-AE0A-8EE0BEA156C9}" name="Contact Dedails" dataDxfId="8"/>
+    <tableColumn id="12" xr3:uid="{2D906F7D-CC5F-4B3B-AB2D-4548041C3791}" name="FINALIZED THE QUOTATIONS" dataDxfId="7"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{2AD88B90-673D-4084-97BF-6D76EA18850F}" name="Table7" displayName="Table7" ref="A3:N7" totalsRowShown="0" headerRowDxfId="20" headerRowBorderDxfId="22" tableBorderDxfId="23">
+  <autoFilter ref="A3:N7" xr:uid="{2AD88B90-673D-4084-97BF-6D76EA18850F}"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{CD6F4AD7-D6AE-4A92-943F-DC823DA0A332}" name="S NO"/>
+    <tableColumn id="2" xr3:uid="{E8A9B9EC-11CC-472F-9F52-923E601D7553}" name="Item Description &amp; Specifications"/>
+    <tableColumn id="3" xr3:uid="{611E176E-9348-4F9D-B615-D5B7E8B358ED}" name="HSN/SAC"/>
+    <tableColumn id="4" xr3:uid="{3E23EAFA-1E46-4240-B809-B4B91C71E735}" name="UOM"/>
+    <tableColumn id="5" xr3:uid="{8C724AC8-CB7A-428F-8F67-55676610C73A}" name="Qty Bags "/>
+    <tableColumn id="6" xr3:uid="{625CAC6A-0168-47D3-A966-CD27A74B10FD}" name="Unit Rate (For Kg)"/>
+    <tableColumn id="7" xr3:uid="{CC223661-1574-4335-9E3D-E6BB5A9C4408}" name="Taxable Amt for Bag"/>
+    <tableColumn id="8" xr3:uid="{8B54CE4A-6FBB-4EC1-85AC-CCA48B35F1AC}" name="Freight"/>
+    <tableColumn id="9" xr3:uid="{7142DD92-5D38-4C6A-A1DB-33EF10E207F1}" name="GST (%)"/>
+    <tableColumn id="10" xr3:uid="{F29F0486-851E-4324-81B3-AD2E6AE009C7}" name="Total Amount for bag "/>
+    <tableColumn id="11" xr3:uid="{2F7E89AB-39DC-438C-ACD4-9B5805CDC8FB}" name="Total with Tax" dataDxfId="21"/>
+    <tableColumn id="12" xr3:uid="{6BDD29B9-9070-43AE-9656-72B69C396229}" name="STORE"/>
+    <tableColumn id="13" xr3:uid="{5323C67C-4949-49E6-B044-8695C1E254C2}" name="Contact Details"/>
+    <tableColumn id="14" xr3:uid="{A68DEF28-FDA5-4BC3-A22B-8A7ACEC5E8BB}" name="FINALIZED THE QUOTATIONS"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{4EE2FD50-4B41-4CC5-AEA9-E1B5B89A7113}" name="Table6" displayName="Table6" ref="A3:M11" totalsRowShown="0" headerRowDxfId="24" tableBorderDxfId="30">
+  <autoFilter ref="A3:M11" xr:uid="{4EE2FD50-4B41-4CC5-AEA9-E1B5B89A7113}"/>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{66DCE332-0B3B-4A31-B718-F400083CA8BA}" name="S NO" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{DE895A90-5656-4698-BB70-3BEA8FC37888}" name="Item Description &amp; Specifications" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{FEE9F1C6-1D3D-48FB-B64F-6540A9960DD8}" name="HSN/SAC" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{06E033EE-C27E-4C0C-8DC9-77D3F87AC9C3}" name="UOM"/>
+    <tableColumn id="5" xr3:uid="{56076920-0E15-43AF-9EFC-18138F94E9A9}" name="Qty mtr &amp; Liters "/>
+    <tableColumn id="6" xr3:uid="{1066D927-0872-4D5F-A97D-54D83F585C40}" name="Unit Rate (For MTR)"/>
+    <tableColumn id="7" xr3:uid="{C14E6602-A49F-4FC0-BAFA-F941C4CAE7A9}" name="Total"/>
+    <tableColumn id="8" xr3:uid="{F5B152FC-F328-4F0B-AD75-F3C246FB22F5}" name="GST (%)"/>
+    <tableColumn id="9" xr3:uid="{32C1784D-E418-46E4-A7B9-6D1565B8AE8B}" name="Total Amount"/>
+    <tableColumn id="10" xr3:uid="{3223747F-D648-4ACA-AF7A-05E522D2E393}" name="Dealers " dataDxfId="26"/>
+    <tableColumn id="11" xr3:uid="{82107381-EEFA-4048-9526-EB616A423E34}" name="Contact Dedails"/>
+    <tableColumn id="12" xr3:uid="{01A392BE-C66C-41E1-9942-50929A294076}" name="FINALIZED THE QUOTATIONS" dataDxfId="25"/>
+    <tableColumn id="13" xr3:uid="{1198A461-826B-40F3-947B-1D7C532B30AB}" name="Column1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5D5727DD-2B96-438F-B04F-217DAA4C9083}" name="Table1" displayName="Table1" ref="A2:G35" totalsRowShown="0">
+  <autoFilter ref="A2:G35" xr:uid="{5D5727DD-2B96-438F-B04F-217DAA4C9083}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{DB6FCE9B-A800-4280-83F7-A4BC4ACD62BA}" name="Column1"/>
+    <tableColumn id="2" xr3:uid="{55C6AF21-6F1D-46BF-AE24-C8F96E55E5E6}" name="Column2" dataDxfId="44"/>
+    <tableColumn id="3" xr3:uid="{9F646E6F-A456-4B1C-931D-34DF07BB4BD6}" name="Column3"/>
+    <tableColumn id="4" xr3:uid="{430F5188-0041-4B1C-AD4E-0E10B49AF4DB}" name="Column4"/>
+    <tableColumn id="5" xr3:uid="{023B2B72-061D-450A-BE09-D894D12DF81D}" name="Column5"/>
+    <tableColumn id="6" xr3:uid="{13DDC91D-AD75-48CE-BF11-55DA62C7897B}" name="Column6"/>
+    <tableColumn id="7" xr3:uid="{7AB69491-22F4-4FAD-A68E-789582A47CF1}" name="Column7"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{FCCA7426-47D6-4FB9-9119-A9D1120037E1}" name="Table5" displayName="Table5" ref="A2:L8" totalsRowShown="0" headerRowDxfId="31" dataDxfId="32" headerRowBorderDxfId="42" tableBorderDxfId="43">
+  <autoFilter ref="A2:L8" xr:uid="{FCCA7426-47D6-4FB9-9119-A9D1120037E1}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{0A6B7944-27C9-469D-8A14-42D1F16651F1}" name="S NO" dataDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{A59FCE7E-14F7-4130-B4C9-976E7B07A2DD}" name="Item Description &amp; Specifications"/>
+    <tableColumn id="3" xr3:uid="{21021A82-58FA-4010-9DB3-99E6627E09CF}" name="HSN/SAC"/>
+    <tableColumn id="4" xr3:uid="{157DA7B7-947B-4663-A41B-AAE5F7035C4A}" name="UOM" dataDxfId="40"/>
+    <tableColumn id="5" xr3:uid="{54D55FF1-5374-4BF0-8C3B-F1A35D8A622A}" name="Qty " dataDxfId="39"/>
+    <tableColumn id="6" xr3:uid="{BD03382E-3DB5-44B1-B6AD-3E40F9AD3FEF}" name="Unit Rate (For Piece) " dataDxfId="38"/>
+    <tableColumn id="7" xr3:uid="{5911FE18-207B-41FE-A429-1A4ED848F7A6}" name="Taxable Amt" dataDxfId="37"/>
+    <tableColumn id="8" xr3:uid="{F425986C-F961-4E47-A081-337596CCB99C}" name="GST (%)" dataDxfId="36"/>
+    <tableColumn id="9" xr3:uid="{88EDAA09-5E3E-4F00-9D2F-DB2210C81CDC}" name="Total with Tax" dataDxfId="35"/>
+    <tableColumn id="10" xr3:uid="{E3B62E13-54BB-440C-8D9B-54B5BBD0CEF6}" name="location" dataDxfId="34"/>
+    <tableColumn id="11" xr3:uid="{2CF4A07E-39F3-4A97-B98F-F4267CB17B49}" name="Contact Details" dataDxfId="33"/>
+    <tableColumn id="12" xr3:uid="{BE70A232-93FC-457C-A918-B1EE14924F1D}" name="FINALIZED THE QUOTATIONS"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2851,27 +4116,27 @@
     <col min="3" max="3" width="13.140625" customWidth="1"/>
     <col min="4" max="4" width="11.42578125" customWidth="1"/>
     <col min="5" max="5" width="11.85546875" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="6" max="6" width="21.140625" customWidth="1"/>
+    <col min="7" max="7" width="15.42578125" customWidth="1"/>
     <col min="8" max="8" width="11.85546875" customWidth="1"/>
     <col min="9" max="9" width="19.28515625" customWidth="1"/>
     <col min="10" max="10" width="27.140625" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" customWidth="1"/>
-    <col min="12" max="12" width="22.85546875" customWidth="1"/>
+    <col min="11" max="11" width="18.42578125" customWidth="1"/>
+    <col min="12" max="12" width="21.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="4"/>
       <c r="B1" s="4"/>
-      <c r="C1" s="143" t="s">
+      <c r="C1" s="160" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="144"/>
-      <c r="E1" s="144"/>
-      <c r="F1" s="144"/>
-      <c r="G1" s="144"/>
-      <c r="H1" s="144"/>
-      <c r="I1" s="144"/>
+      <c r="D1" s="161"/>
+      <c r="E1" s="161"/>
+      <c r="F1" s="161"/>
+      <c r="G1" s="161"/>
+      <c r="H1" s="161"/>
+      <c r="I1" s="161"/>
       <c r="J1" s="4"/>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
@@ -2879,52 +4144,52 @@
     <row r="2" spans="1:12">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
-      <c r="C2" s="144"/>
-      <c r="D2" s="144"/>
-      <c r="E2" s="144"/>
-      <c r="F2" s="144"/>
-      <c r="G2" s="144"/>
-      <c r="H2" s="144"/>
-      <c r="I2" s="144"/>
+      <c r="C2" s="161"/>
+      <c r="D2" s="161"/>
+      <c r="E2" s="161"/>
+      <c r="F2" s="161"/>
+      <c r="G2" s="161"/>
+      <c r="H2" s="161"/>
+      <c r="I2" s="161"/>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
     </row>
     <row r="3" spans="1:12" ht="33">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="195" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="195" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="195" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="195" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="195" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="195" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="195" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="195" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="195" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="195" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="195" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L3" s="195" t="s">
         <v>170</v>
       </c>
     </row>
@@ -2932,10 +4197,10 @@
       <c r="A4" s="2">
         <v>1</v>
       </c>
-      <c r="B4" s="145" t="s">
+      <c r="B4" s="130" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="145"/>
+      <c r="C4" s="130"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -3103,13 +4368,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="4"/>
-      <c r="C9" s="146" t="s">
+      <c r="C9" s="131" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="146"/>
-      <c r="E9" s="146"/>
-      <c r="F9" s="146"/>
-      <c r="G9" s="146"/>
+      <c r="D9" s="131"/>
+      <c r="E9" s="131"/>
+      <c r="F9" s="131"/>
+      <c r="G9" s="131"/>
       <c r="H9" s="11"/>
       <c r="I9" s="12">
         <f>SUM(I5:I8)</f>
@@ -3123,10 +4388,10 @@
       <c r="A10" s="2">
         <v>7</v>
       </c>
-      <c r="B10" s="147" t="s">
+      <c r="B10" s="132" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="147"/>
+      <c r="C10" s="132"/>
       <c r="D10" s="6"/>
       <c r="E10" s="7"/>
       <c r="F10" s="8"/>
@@ -3286,13 +4551,13 @@
         <v>12</v>
       </c>
       <c r="B15" s="4"/>
-      <c r="C15" s="146" t="s">
+      <c r="C15" s="131" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="146"/>
-      <c r="E15" s="146"/>
-      <c r="F15" s="146"/>
-      <c r="G15" s="146"/>
+      <c r="D15" s="131"/>
+      <c r="E15" s="131"/>
+      <c r="F15" s="131"/>
+      <c r="G15" s="131"/>
       <c r="H15" s="11"/>
       <c r="I15" s="12">
         <f>SUM(I11:I14)</f>
@@ -3306,10 +4571,10 @@
       <c r="A16" s="2">
         <v>13</v>
       </c>
-      <c r="B16" s="147" t="s">
+      <c r="B16" s="132" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="147"/>
+      <c r="C16" s="132"/>
       <c r="D16" s="6"/>
       <c r="E16" s="7"/>
       <c r="F16" s="9"/>
@@ -3362,39 +4627,39 @@
       <c r="A18" s="2">
         <v>15</v>
       </c>
-      <c r="B18" s="180" t="s">
+      <c r="B18" s="148" t="s">
         <v>182</v>
       </c>
-      <c r="C18" s="181">
+      <c r="C18" s="149">
         <v>68042210</v>
       </c>
-      <c r="D18" s="182" t="s">
+      <c r="D18" s="150" t="s">
         <v>15</v>
       </c>
-      <c r="E18" s="183">
+      <c r="E18" s="151">
         <v>200</v>
       </c>
-      <c r="F18" s="184">
+      <c r="F18" s="152">
         <v>38</v>
       </c>
-      <c r="G18" s="184">
+      <c r="G18" s="152">
         <f t="shared" si="0"/>
         <v>7600</v>
       </c>
-      <c r="H18" s="183">
+      <c r="H18" s="151">
         <v>18</v>
       </c>
-      <c r="I18" s="184">
+      <c r="I18" s="152">
         <f t="shared" si="1"/>
         <v>8968</v>
       </c>
-      <c r="J18" s="185" t="s">
+      <c r="J18" s="153" t="s">
         <v>34</v>
       </c>
-      <c r="K18" s="182" t="s">
+      <c r="K18" s="150" t="s">
         <v>35</v>
       </c>
-      <c r="L18" s="59" t="s">
+      <c r="L18" s="52" t="s">
         <v>171</v>
       </c>
     </row>
@@ -3440,39 +4705,39 @@
       <c r="A20" s="2">
         <v>17</v>
       </c>
-      <c r="B20" s="180" t="s">
+      <c r="B20" s="148" t="s">
         <v>183</v>
       </c>
-      <c r="C20" s="181">
+      <c r="C20" s="149">
         <v>68042210</v>
       </c>
-      <c r="D20" s="182" t="s">
+      <c r="D20" s="150" t="s">
         <v>15</v>
       </c>
-      <c r="E20" s="186">
+      <c r="E20" s="154">
         <v>100</v>
       </c>
-      <c r="F20" s="186">
+      <c r="F20" s="154">
         <v>88</v>
       </c>
-      <c r="G20" s="184">
+      <c r="G20" s="152">
         <f t="shared" si="0"/>
         <v>8800</v>
       </c>
-      <c r="H20" s="183">
+      <c r="H20" s="151">
         <v>18</v>
       </c>
-      <c r="I20" s="184">
+      <c r="I20" s="152">
         <f t="shared" si="1"/>
         <v>10384</v>
       </c>
-      <c r="J20" s="185" t="s">
+      <c r="J20" s="153" t="s">
         <v>34</v>
       </c>
-      <c r="K20" s="182" t="s">
+      <c r="K20" s="150" t="s">
         <v>35</v>
       </c>
-      <c r="L20" s="59" t="s">
+      <c r="L20" s="52" t="s">
         <v>171</v>
       </c>
     </row>
@@ -3481,13 +4746,13 @@
         <v>18</v>
       </c>
       <c r="B21" s="4"/>
-      <c r="C21" s="151" t="s">
+      <c r="C21" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D21" s="151"/>
-      <c r="E21" s="151"/>
-      <c r="F21" s="151"/>
-      <c r="G21" s="151"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
       <c r="H21" s="24"/>
       <c r="I21" s="12">
         <f>SUM(I17:I20)</f>
@@ -3502,9 +4767,9 @@
       <c r="B22" s="4"/>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
-      <c r="E22" s="132"/>
-      <c r="F22" s="132"/>
-      <c r="G22" s="132"/>
+      <c r="E22" s="119"/>
+      <c r="F22" s="119"/>
+      <c r="G22" s="119"/>
       <c r="H22" s="24"/>
       <c r="I22" s="12"/>
       <c r="J22" s="25"/>
@@ -3518,13 +4783,13 @@
       <c r="B23" s="4"/>
       <c r="C23" s="25"/>
       <c r="D23" s="25"/>
-      <c r="E23" s="148" t="s">
+      <c r="E23" s="133" t="s">
         <v>173</v>
       </c>
-      <c r="F23" s="148"/>
-      <c r="G23" s="148"/>
-      <c r="H23" s="126"/>
-      <c r="I23" s="127">
+      <c r="F23" s="133"/>
+      <c r="G23" s="133"/>
+      <c r="H23" s="114"/>
+      <c r="I23" s="115">
         <f>I18+I20</f>
         <v>19352</v>
       </c>
@@ -3537,11 +4802,11 @@
       <c r="B24" s="4"/>
       <c r="C24" s="25"/>
       <c r="D24" s="25"/>
-      <c r="E24" s="133"/>
-      <c r="F24" s="133"/>
-      <c r="G24" s="133"/>
-      <c r="H24" s="134"/>
-      <c r="I24" s="135"/>
+      <c r="E24" s="120"/>
+      <c r="F24" s="120"/>
+      <c r="G24" s="120"/>
+      <c r="H24" s="121"/>
+      <c r="I24" s="122"/>
       <c r="J24" s="25"/>
       <c r="K24" s="25"/>
       <c r="L24" s="6"/>
@@ -3550,10 +4815,10 @@
       <c r="A25" s="2">
         <v>20</v>
       </c>
-      <c r="B25" s="147" t="s">
+      <c r="B25" s="132" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="147"/>
+      <c r="C25" s="132"/>
       <c r="D25" s="25"/>
       <c r="E25" s="25"/>
       <c r="F25" s="25"/>
@@ -3749,14 +5014,14 @@
         <v>26</v>
       </c>
       <c r="B31" s="4"/>
-      <c r="C31" s="152" t="s">
+      <c r="C31" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="D31" s="152"/>
-      <c r="E31" s="152"/>
-      <c r="F31" s="152"/>
-      <c r="G31" s="152"/>
-      <c r="H31" s="152"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="24"/>
+      <c r="H31" s="24"/>
       <c r="I31" s="12">
         <f>SUM(I26:I30)</f>
         <v>69997.600000000006</v>
@@ -3769,10 +5034,10 @@
       <c r="A32" s="2">
         <v>27</v>
       </c>
-      <c r="B32" s="147" t="s">
+      <c r="B32" s="132" t="s">
         <v>43</v>
       </c>
-      <c r="C32" s="147"/>
+      <c r="C32" s="132"/>
       <c r="D32" s="6"/>
       <c r="E32" s="25"/>
       <c r="F32" s="25"/>
@@ -3787,11 +5052,11 @@
       <c r="A33" s="2">
         <v>28</v>
       </c>
-      <c r="B33" s="33" t="s">
+      <c r="B33" s="31" t="s">
         <v>184</v>
       </c>
       <c r="C33" s="24"/>
-      <c r="D33" s="47" t="s">
+      <c r="D33" s="45" t="s">
         <v>15</v>
       </c>
       <c r="E33" s="24">
@@ -3817,7 +5082,7 @@
       <c r="K33" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="59" t="s">
+      <c r="L33" s="52" t="s">
         <v>171</v>
       </c>
     </row>
@@ -3861,11 +5126,11 @@
       <c r="A35" s="2">
         <v>30</v>
       </c>
-      <c r="B35" s="33" t="s">
+      <c r="B35" s="31" t="s">
         <v>185</v>
       </c>
       <c r="C35" s="24"/>
-      <c r="D35" s="47" t="s">
+      <c r="D35" s="45" t="s">
         <v>15</v>
       </c>
       <c r="E35" s="24">
@@ -3891,7 +5156,7 @@
       <c r="K35" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="L35" s="59" t="s">
+      <c r="L35" s="52" t="s">
         <v>171</v>
       </c>
     </row>
@@ -3937,13 +5202,13 @@
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
-      <c r="D37" s="153" t="s">
+      <c r="D37" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="E37" s="153"/>
-      <c r="F37" s="153"/>
-      <c r="G37" s="153"/>
-      <c r="H37" s="153"/>
+      <c r="E37" s="45"/>
+      <c r="F37" s="45"/>
+      <c r="G37" s="45"/>
+      <c r="H37" s="45"/>
       <c r="I37" s="26">
         <f>SUM(I33:I36)</f>
         <v>41182</v>
@@ -3953,32 +5218,32 @@
       <c r="L37" s="4"/>
     </row>
     <row r="39" spans="1:12">
-      <c r="F39" s="148" t="s">
+      <c r="F39" s="157" t="s">
         <v>172</v>
       </c>
-      <c r="G39" s="148"/>
-      <c r="H39" s="148"/>
-      <c r="I39" s="128">
+      <c r="G39" s="157"/>
+      <c r="H39" s="157"/>
+      <c r="I39" s="116">
         <f>I33+I35</f>
         <v>8142</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="15.75">
-      <c r="C41" s="149" t="s">
+      <c r="C41" s="158" t="s">
         <v>179</v>
       </c>
-      <c r="D41" s="149"/>
-      <c r="E41" s="149"/>
-      <c r="F41" s="149"/>
-      <c r="G41" s="149"/>
-      <c r="H41" s="149"/>
-      <c r="I41" s="131">
+      <c r="D41" s="158"/>
+      <c r="E41" s="158"/>
+      <c r="F41" s="158"/>
+      <c r="G41" s="158"/>
+      <c r="H41" s="158"/>
+      <c r="I41" s="118">
         <f>I23+I39</f>
         <v>27494</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="30">
-      <c r="B45" s="130" t="s">
+      <c r="B45" s="117" t="s">
         <v>174</v>
       </c>
       <c r="C45" s="4"/>
@@ -3997,28 +5262,20 @@
       <c r="F46" s="4"/>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1">
-      <c r="C47" s="150"/>
-      <c r="D47" s="150"/>
+      <c r="C47" s="159"/>
+      <c r="D47" s="159"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="4">
+    <mergeCell ref="C1:I2"/>
     <mergeCell ref="F39:H39"/>
-    <mergeCell ref="E23:G23"/>
     <mergeCell ref="C41:H41"/>
     <mergeCell ref="C47:D47"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="C31:H31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="C1:I2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="C15:G15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -4029,592 +5286,592 @@
   <cols>
     <col min="2" max="2" width="47.5703125" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="5.42578125" customWidth="1"/>
+    <col min="4" max="4" width="8.140625" customWidth="1"/>
     <col min="5" max="5" width="12.42578125" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" customWidth="1"/>
+    <col min="6" max="6" width="20.85546875" customWidth="1"/>
     <col min="7" max="7" width="17.42578125" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" customWidth="1"/>
-    <col min="9" max="9" width="21.85546875" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" customWidth="1"/>
+    <col min="9" max="9" width="18.28515625" customWidth="1"/>
     <col min="10" max="10" width="27.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.85546875" customWidth="1"/>
-    <col min="12" max="12" width="20.85546875" customWidth="1"/>
+    <col min="11" max="11" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="21.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="16.5" customHeight="1">
       <c r="A1" s="27"/>
       <c r="B1" s="27"/>
-      <c r="C1" s="164" t="s">
+      <c r="C1" s="162" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="164"/>
-      <c r="E1" s="164"/>
-      <c r="F1" s="164"/>
-      <c r="G1" s="164"/>
-      <c r="H1" s="164"/>
-      <c r="I1" s="164"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="162"/>
+      <c r="G1" s="162"/>
+      <c r="H1" s="162"/>
+      <c r="I1" s="162"/>
       <c r="J1" s="27"/>
       <c r="K1" s="27"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="27"/>
       <c r="B2" s="27"/>
-      <c r="C2" s="165"/>
-      <c r="D2" s="165"/>
-      <c r="E2" s="165"/>
-      <c r="F2" s="165"/>
-      <c r="G2" s="165"/>
-      <c r="H2" s="165"/>
-      <c r="I2" s="165"/>
+      <c r="C2" s="163"/>
+      <c r="D2" s="163"/>
+      <c r="E2" s="163"/>
+      <c r="F2" s="163"/>
+      <c r="G2" s="163"/>
+      <c r="H2" s="163"/>
+      <c r="I2" s="163"/>
       <c r="J2" s="27"/>
       <c r="K2" s="27"/>
     </row>
     <row r="3" spans="1:12" ht="33">
-      <c r="A3" s="61" t="s">
+      <c r="A3" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="62" t="s">
+      <c r="C3" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="62" t="s">
+      <c r="D3" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="62" t="s">
+      <c r="E3" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="62" t="s">
+      <c r="F3" s="53" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="62" t="s">
+      <c r="G3" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="62" t="s">
+      <c r="H3" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="62" t="s">
+      <c r="I3" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="62" t="s">
+      <c r="J3" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="62" t="s">
+      <c r="K3" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="60" t="s">
+      <c r="L3" s="188" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="45" customHeight="1">
-      <c r="A4" s="63">
+      <c r="A4" s="187">
         <v>1</v>
       </c>
-      <c r="B4" s="163" t="s">
+      <c r="B4" s="141" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="163"/>
-      <c r="D4" s="163"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="66"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="66"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="68"/>
-      <c r="L4" s="4"/>
+      <c r="C4" s="141"/>
+      <c r="D4" s="141"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
+      <c r="L4" s="169"/>
     </row>
     <row r="5" spans="1:12" ht="49.5">
-      <c r="A5" s="63">
+      <c r="A5" s="187">
         <v>2</v>
       </c>
-      <c r="B5" s="69" t="s">
+      <c r="B5" s="59" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="70">
+      <c r="C5" s="60">
         <v>83111000</v>
       </c>
-      <c r="D5" s="71" t="s">
+      <c r="D5" s="61" t="s">
         <v>50</v>
       </c>
-      <c r="E5" s="72">
+      <c r="E5" s="62">
         <v>400</v>
       </c>
-      <c r="F5" s="73">
+      <c r="F5" s="63">
         <v>93</v>
       </c>
-      <c r="G5" s="73">
+      <c r="G5" s="63">
         <v>37200</v>
       </c>
-      <c r="H5" s="72">
+      <c r="H5" s="62">
         <v>18</v>
       </c>
-      <c r="I5" s="73">
+      <c r="I5" s="63">
         <v>43896</v>
       </c>
-      <c r="J5" s="74" t="s">
+      <c r="J5" s="64" t="s">
         <v>143</v>
       </c>
-      <c r="K5" s="75" t="s">
+      <c r="K5" s="65" t="s">
         <v>62</v>
       </c>
-      <c r="L5" s="4"/>
+      <c r="L5" s="169"/>
     </row>
     <row r="6" spans="1:12" ht="49.5">
-      <c r="A6" s="63">
+      <c r="A6" s="187">
         <v>3</v>
       </c>
-      <c r="B6" s="69" t="s">
+      <c r="B6" s="59" t="s">
         <v>63</v>
       </c>
-      <c r="C6" s="70">
+      <c r="C6" s="60">
         <v>83111000</v>
       </c>
-      <c r="D6" s="71" t="s">
+      <c r="D6" s="61" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="72">
+      <c r="E6" s="62">
         <v>300</v>
       </c>
-      <c r="F6" s="73">
+      <c r="F6" s="63">
         <v>83</v>
       </c>
-      <c r="G6" s="73">
+      <c r="G6" s="63">
         <v>24900</v>
       </c>
-      <c r="H6" s="72">
+      <c r="H6" s="62">
         <v>18</v>
       </c>
-      <c r="I6" s="73">
+      <c r="I6" s="63">
         <v>29382</v>
       </c>
-      <c r="J6" s="74" t="s">
+      <c r="J6" s="64" t="s">
         <v>61</v>
       </c>
-      <c r="K6" s="75" t="s">
+      <c r="K6" s="65" t="s">
         <v>62</v>
       </c>
-      <c r="L6" s="76" t="s">
+      <c r="L6" s="189" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="49.5">
-      <c r="A7" s="63">
+      <c r="A7" s="187">
         <v>4</v>
       </c>
-      <c r="B7" s="69" t="s">
+      <c r="B7" s="59" t="s">
         <v>64</v>
       </c>
-      <c r="C7" s="70">
+      <c r="C7" s="60">
         <v>83111000</v>
       </c>
-      <c r="D7" s="71" t="s">
+      <c r="D7" s="61" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="72">
+      <c r="E7" s="62">
         <v>300</v>
       </c>
-      <c r="F7" s="73">
+      <c r="F7" s="63">
         <v>83</v>
       </c>
-      <c r="G7" s="73">
+      <c r="G7" s="63">
         <v>24900</v>
       </c>
-      <c r="H7" s="72">
+      <c r="H7" s="62">
         <v>18</v>
       </c>
-      <c r="I7" s="73">
+      <c r="I7" s="63">
         <v>29382</v>
       </c>
-      <c r="J7" s="74" t="s">
+      <c r="J7" s="64" t="s">
         <v>61</v>
       </c>
-      <c r="K7" s="75" t="s">
+      <c r="K7" s="65" t="s">
         <v>62</v>
       </c>
-      <c r="L7" s="4"/>
+      <c r="L7" s="169"/>
     </row>
     <row r="8" spans="1:12" ht="16.5">
-      <c r="A8" s="63">
+      <c r="A8" s="187">
         <v>5</v>
       </c>
-      <c r="B8" s="77"/>
-      <c r="C8" s="70"/>
-      <c r="D8" s="155" t="s">
+      <c r="B8" s="66"/>
+      <c r="C8" s="60"/>
+      <c r="D8" s="135" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="155"/>
-      <c r="F8" s="155"/>
-      <c r="G8" s="155"/>
-      <c r="H8" s="155"/>
-      <c r="I8" s="78">
+      <c r="E8" s="135"/>
+      <c r="F8" s="135"/>
+      <c r="G8" s="135"/>
+      <c r="H8" s="135"/>
+      <c r="I8" s="67">
         <f>SUM(I5:I7)</f>
         <v>102660</v>
       </c>
-      <c r="J8" s="74"/>
-      <c r="K8" s="79"/>
-      <c r="L8" s="4"/>
+      <c r="J8" s="64"/>
+      <c r="K8" s="68"/>
+      <c r="L8" s="169"/>
     </row>
     <row r="9" spans="1:12" ht="16.5">
-      <c r="A9" s="63">
+      <c r="A9" s="187">
         <v>6</v>
       </c>
-      <c r="B9" s="77"/>
-      <c r="C9" s="80"/>
-      <c r="D9" s="80"/>
-      <c r="E9" s="80"/>
-      <c r="F9" s="80"/>
-      <c r="G9" s="80"/>
-      <c r="H9" s="81"/>
-      <c r="I9" s="78"/>
-      <c r="J9" s="82"/>
-      <c r="K9" s="83"/>
-      <c r="L9" s="4"/>
+      <c r="B9" s="66"/>
+      <c r="C9" s="69"/>
+      <c r="D9" s="69"/>
+      <c r="E9" s="69"/>
+      <c r="F9" s="69"/>
+      <c r="G9" s="69"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="67"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="169"/>
     </row>
     <row r="10" spans="1:12" ht="42" customHeight="1">
-      <c r="A10" s="63">
+      <c r="A10" s="187">
         <v>7</v>
       </c>
-      <c r="B10" s="158" t="s">
+      <c r="B10" s="137" t="s">
         <v>65</v>
       </c>
-      <c r="C10" s="158"/>
-      <c r="D10" s="158"/>
-      <c r="E10" s="80"/>
-      <c r="F10" s="80"/>
-      <c r="G10" s="80"/>
-      <c r="H10" s="81"/>
-      <c r="I10" s="78"/>
-      <c r="J10" s="82"/>
-      <c r="K10" s="83"/>
-      <c r="L10" s="4"/>
+      <c r="C10" s="137"/>
+      <c r="D10" s="137"/>
+      <c r="E10" s="69"/>
+      <c r="F10" s="69"/>
+      <c r="G10" s="69"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="67"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="169"/>
     </row>
     <row r="11" spans="1:12" ht="75">
-      <c r="A11" s="63">
+      <c r="A11" s="187">
         <v>8</v>
       </c>
-      <c r="B11" s="84" t="s">
+      <c r="B11" s="73" t="s">
         <v>66</v>
       </c>
-      <c r="C11" s="85">
+      <c r="C11" s="74">
         <v>83111000</v>
       </c>
-      <c r="D11" s="86" t="s">
+      <c r="D11" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="E11" s="87">
+      <c r="E11" s="76">
         <v>400</v>
       </c>
-      <c r="F11" s="88">
+      <c r="F11" s="77">
         <v>105</v>
       </c>
-      <c r="G11" s="88">
+      <c r="G11" s="77">
         <v>42000</v>
       </c>
-      <c r="H11" s="87">
+      <c r="H11" s="76">
         <v>18</v>
       </c>
-      <c r="I11" s="88">
+      <c r="I11" s="77">
         <v>49560</v>
       </c>
-      <c r="J11" s="88" t="s">
+      <c r="J11" s="77" t="s">
         <v>65</v>
       </c>
-      <c r="K11" s="89" t="s">
+      <c r="K11" s="78" t="s">
         <v>35</v>
       </c>
-      <c r="L11" s="4"/>
+      <c r="L11" s="169"/>
     </row>
     <row r="12" spans="1:12" ht="60">
-      <c r="A12" s="63">
+      <c r="A12" s="187">
         <v>9</v>
       </c>
-      <c r="B12" s="84" t="s">
+      <c r="B12" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="C12" s="85">
+      <c r="C12" s="74">
         <v>83111000</v>
       </c>
-      <c r="D12" s="86" t="s">
+      <c r="D12" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="87">
+      <c r="E12" s="76">
         <v>300</v>
       </c>
-      <c r="F12" s="88">
+      <c r="F12" s="77">
         <v>97</v>
       </c>
-      <c r="G12" s="88">
+      <c r="G12" s="77">
         <v>29100</v>
       </c>
-      <c r="H12" s="87">
+      <c r="H12" s="76">
         <v>18</v>
       </c>
-      <c r="I12" s="88">
+      <c r="I12" s="77">
         <v>34338</v>
       </c>
-      <c r="J12" s="88" t="s">
+      <c r="J12" s="77" t="s">
         <v>65</v>
       </c>
-      <c r="K12" s="89" t="s">
+      <c r="K12" s="78" t="s">
         <v>35</v>
       </c>
-      <c r="L12" s="4"/>
+      <c r="L12" s="169"/>
     </row>
     <row r="13" spans="1:12" ht="60">
-      <c r="A13" s="63">
+      <c r="A13" s="187">
         <v>10</v>
       </c>
-      <c r="B13" s="84" t="s">
+      <c r="B13" s="73" t="s">
         <v>68</v>
       </c>
-      <c r="C13" s="85">
+      <c r="C13" s="74">
         <v>83111000</v>
       </c>
-      <c r="D13" s="86" t="s">
+      <c r="D13" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="E13" s="87">
+      <c r="E13" s="76">
         <v>300</v>
       </c>
-      <c r="F13" s="88">
+      <c r="F13" s="77">
         <v>97</v>
       </c>
-      <c r="G13" s="88">
+      <c r="G13" s="77">
         <v>29100</v>
       </c>
-      <c r="H13" s="87">
+      <c r="H13" s="76">
         <v>18</v>
       </c>
-      <c r="I13" s="88">
+      <c r="I13" s="77">
         <v>34338</v>
       </c>
-      <c r="J13" s="88" t="s">
+      <c r="J13" s="77" t="s">
         <v>65</v>
       </c>
-      <c r="K13" s="89" t="s">
+      <c r="K13" s="78" t="s">
         <v>35</v>
       </c>
-      <c r="L13" s="4"/>
+      <c r="L13" s="169"/>
     </row>
     <row r="14" spans="1:12" ht="16.5">
-      <c r="A14" s="63">
+      <c r="A14" s="187">
         <v>11</v>
       </c>
-      <c r="B14" s="90"/>
-      <c r="C14" s="91"/>
-      <c r="D14" s="92"/>
-      <c r="E14" s="159" t="s">
+      <c r="B14" s="79"/>
+      <c r="C14" s="80"/>
+      <c r="D14" s="81"/>
+      <c r="E14" s="138" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="159"/>
-      <c r="G14" s="159"/>
-      <c r="H14" s="159"/>
-      <c r="I14" s="93">
+      <c r="F14" s="138"/>
+      <c r="G14" s="138"/>
+      <c r="H14" s="138"/>
+      <c r="I14" s="82">
         <v>118236</v>
       </c>
-      <c r="J14" s="94"/>
-      <c r="K14" s="95"/>
-      <c r="L14" s="4"/>
+      <c r="J14" s="83"/>
+      <c r="K14" s="84"/>
+      <c r="L14" s="169"/>
     </row>
     <row r="15" spans="1:12" ht="16.5">
-      <c r="A15" s="63">
+      <c r="A15" s="187">
         <v>12</v>
       </c>
-      <c r="B15" s="96"/>
-      <c r="C15" s="96"/>
-      <c r="D15" s="97"/>
-      <c r="E15" s="98"/>
-      <c r="F15" s="99"/>
-      <c r="G15" s="99"/>
-      <c r="H15" s="98"/>
-      <c r="I15" s="99"/>
-      <c r="J15" s="100"/>
-      <c r="K15" s="101"/>
-      <c r="L15" s="4"/>
+      <c r="B15" s="85"/>
+      <c r="C15" s="85"/>
+      <c r="D15" s="86"/>
+      <c r="E15" s="87"/>
+      <c r="F15" s="88"/>
+      <c r="G15" s="88"/>
+      <c r="H15" s="87"/>
+      <c r="I15" s="88"/>
+      <c r="J15" s="89"/>
+      <c r="K15" s="90"/>
+      <c r="L15" s="169"/>
     </row>
     <row r="16" spans="1:12" ht="16.5">
-      <c r="A16" s="63">
+      <c r="A16" s="187">
         <v>13</v>
       </c>
-      <c r="B16" s="166" t="s">
+      <c r="B16" s="142" t="s">
         <v>151</v>
       </c>
-      <c r="C16" s="166"/>
-      <c r="D16" s="166"/>
-      <c r="E16" s="102"/>
-      <c r="F16" s="102"/>
-      <c r="G16" s="102"/>
-      <c r="H16" s="102"/>
-      <c r="I16" s="102"/>
-      <c r="J16" s="102"/>
-      <c r="K16" s="102"/>
-      <c r="L16" s="4"/>
+      <c r="C16" s="142"/>
+      <c r="D16" s="142"/>
+      <c r="E16" s="91"/>
+      <c r="F16" s="91"/>
+      <c r="G16" s="91"/>
+      <c r="H16" s="91"/>
+      <c r="I16" s="91"/>
+      <c r="J16" s="91"/>
+      <c r="K16" s="91"/>
+      <c r="L16" s="169"/>
     </row>
     <row r="17" spans="1:12" ht="30">
-      <c r="A17" s="63">
+      <c r="A17" s="187">
         <v>14</v>
       </c>
-      <c r="B17" s="103" t="s">
+      <c r="B17" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="104">
+      <c r="C17" s="93">
         <v>83111000</v>
       </c>
-      <c r="D17" s="105" t="s">
+      <c r="D17" s="94" t="s">
         <v>50</v>
       </c>
-      <c r="E17" s="106">
+      <c r="E17" s="95">
         <v>400</v>
       </c>
-      <c r="F17" s="107">
+      <c r="F17" s="96">
         <v>106.5</v>
       </c>
-      <c r="G17" s="107">
+      <c r="G17" s="96">
         <v>42600</v>
       </c>
-      <c r="H17" s="106">
+      <c r="H17" s="95">
         <v>18</v>
       </c>
-      <c r="I17" s="107">
+      <c r="I17" s="96">
         <v>50268</v>
       </c>
-      <c r="J17" s="107" t="s">
+      <c r="J17" s="96" t="s">
         <v>51</v>
       </c>
-      <c r="K17" s="108" t="s">
+      <c r="K17" s="97" t="s">
         <v>52</v>
       </c>
-      <c r="L17" s="4"/>
+      <c r="L17" s="169"/>
     </row>
     <row r="18" spans="1:12" ht="30">
-      <c r="A18" s="63">
+      <c r="A18" s="187">
         <v>15</v>
       </c>
-      <c r="B18" s="103" t="s">
+      <c r="B18" s="92" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="104">
+      <c r="C18" s="93">
         <v>83111000</v>
       </c>
-      <c r="D18" s="105" t="s">
+      <c r="D18" s="94" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="106">
+      <c r="E18" s="95">
         <v>300</v>
       </c>
-      <c r="F18" s="107">
+      <c r="F18" s="96">
         <v>94.9</v>
       </c>
-      <c r="G18" s="107">
+      <c r="G18" s="96">
         <v>28470</v>
       </c>
-      <c r="H18" s="106">
+      <c r="H18" s="95">
         <v>18</v>
       </c>
-      <c r="I18" s="107">
+      <c r="I18" s="96">
         <v>33594.6</v>
       </c>
-      <c r="J18" s="107" t="s">
+      <c r="J18" s="96" t="s">
         <v>51</v>
       </c>
-      <c r="K18" s="108" t="s">
+      <c r="K18" s="97" t="s">
         <v>52</v>
       </c>
-      <c r="L18" s="4"/>
+      <c r="L18" s="169"/>
     </row>
     <row r="19" spans="1:12" ht="30">
-      <c r="A19" s="63">
+      <c r="A19" s="187">
         <v>16</v>
       </c>
-      <c r="B19" s="103" t="s">
+      <c r="B19" s="92" t="s">
         <v>54</v>
       </c>
-      <c r="C19" s="104">
+      <c r="C19" s="93">
         <v>83111000</v>
       </c>
-      <c r="D19" s="105" t="s">
+      <c r="D19" s="94" t="s">
         <v>50</v>
       </c>
-      <c r="E19" s="106">
+      <c r="E19" s="95">
         <v>300</v>
       </c>
-      <c r="F19" s="107">
+      <c r="F19" s="96">
         <v>94.9</v>
       </c>
-      <c r="G19" s="107">
+      <c r="G19" s="96">
         <v>28470</v>
       </c>
-      <c r="H19" s="106">
+      <c r="H19" s="95">
         <v>18</v>
       </c>
-      <c r="I19" s="107">
+      <c r="I19" s="96">
         <v>33594.6</v>
       </c>
-      <c r="J19" s="107" t="s">
+      <c r="J19" s="96" t="s">
         <v>51</v>
       </c>
-      <c r="K19" s="108" t="s">
+      <c r="K19" s="97" t="s">
         <v>52</v>
       </c>
-      <c r="L19" s="4"/>
+      <c r="L19" s="169"/>
     </row>
     <row r="20" spans="1:12" ht="16.5">
-      <c r="A20" s="63">
+      <c r="A20" s="187">
         <v>17</v>
       </c>
-      <c r="B20" s="109"/>
-      <c r="C20" s="167" t="s">
+      <c r="B20" s="98"/>
+      <c r="C20" s="143" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="167"/>
-      <c r="E20" s="167"/>
-      <c r="F20" s="167"/>
-      <c r="G20" s="167"/>
-      <c r="H20" s="110"/>
-      <c r="I20" s="111">
+      <c r="D20" s="143"/>
+      <c r="E20" s="143"/>
+      <c r="F20" s="143"/>
+      <c r="G20" s="143"/>
+      <c r="H20" s="99"/>
+      <c r="I20" s="100">
         <v>117457.2</v>
       </c>
-      <c r="J20" s="107"/>
-      <c r="K20" s="108"/>
-      <c r="L20" s="4"/>
+      <c r="J20" s="96"/>
+      <c r="K20" s="97"/>
+      <c r="L20" s="169"/>
     </row>
     <row r="21" spans="1:12" ht="34.5" customHeight="1">
-      <c r="A21" s="63">
+      <c r="A21" s="187">
         <v>18</v>
       </c>
-      <c r="B21" s="160" t="s">
+      <c r="B21" s="139" t="s">
         <v>69</v>
       </c>
-      <c r="C21" s="160"/>
-      <c r="D21" s="160"/>
-      <c r="E21" s="98"/>
-      <c r="F21" s="99"/>
-      <c r="G21" s="99"/>
-      <c r="H21" s="98"/>
-      <c r="I21" s="99"/>
-      <c r="J21" s="100"/>
-      <c r="K21" s="101"/>
-      <c r="L21" s="4"/>
+      <c r="C21" s="139"/>
+      <c r="D21" s="139"/>
+      <c r="E21" s="87"/>
+      <c r="F21" s="88"/>
+      <c r="G21" s="88"/>
+      <c r="H21" s="87"/>
+      <c r="I21" s="88"/>
+      <c r="J21" s="89"/>
+      <c r="K21" s="90"/>
+      <c r="L21" s="169"/>
     </row>
     <row r="22" spans="1:12" ht="30">
-      <c r="A22" s="63">
+      <c r="A22" s="187">
         <v>19</v>
       </c>
-      <c r="B22" s="112" t="s">
+      <c r="B22" s="101" t="s">
         <v>70</v>
       </c>
-      <c r="C22" s="96"/>
+      <c r="C22" s="85"/>
       <c r="D22" s="15" t="s">
         <v>50</v>
       </c>
       <c r="E22" s="7">
         <v>400</v>
       </c>
-      <c r="F22" s="49">
+      <c r="F22" s="47">
         <v>117</v>
       </c>
-      <c r="G22" s="49">
+      <c r="G22" s="47">
         <v>46800</v>
       </c>
       <c r="H22" s="7">
@@ -4623,32 +5880,32 @@
       <c r="I22" s="9">
         <v>55224</v>
       </c>
-      <c r="J22" s="49" t="s">
+      <c r="J22" s="47" t="s">
         <v>71</v>
       </c>
-      <c r="K22" s="49" t="s">
+      <c r="K22" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="L22" s="4"/>
+      <c r="L22" s="169"/>
     </row>
     <row r="23" spans="1:12" ht="30">
-      <c r="A23" s="63">
+      <c r="A23" s="187">
         <v>20</v>
       </c>
-      <c r="B23" s="112" t="s">
+      <c r="B23" s="101" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="96"/>
+      <c r="C23" s="85"/>
       <c r="D23" s="15" t="s">
         <v>50</v>
       </c>
       <c r="E23" s="7">
         <v>300</v>
       </c>
-      <c r="F23" s="49">
+      <c r="F23" s="47">
         <v>115</v>
       </c>
-      <c r="G23" s="49">
+      <c r="G23" s="47">
         <v>34500</v>
       </c>
       <c r="H23" s="7">
@@ -4657,22 +5914,22 @@
       <c r="I23" s="9">
         <v>40710</v>
       </c>
-      <c r="J23" s="49" t="s">
+      <c r="J23" s="47" t="s">
         <v>71</v>
       </c>
-      <c r="K23" s="49" t="s">
+      <c r="K23" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="L23" s="4"/>
+      <c r="L23" s="169"/>
     </row>
     <row r="24" spans="1:12" ht="30">
-      <c r="A24" s="63">
+      <c r="A24" s="187">
         <v>21</v>
       </c>
-      <c r="B24" s="112" t="s">
+      <c r="B24" s="101" t="s">
         <v>74</v>
       </c>
-      <c r="C24" s="96"/>
+      <c r="C24" s="85"/>
       <c r="D24" s="15" t="s">
         <v>50</v>
       </c>
@@ -4691,36 +5948,36 @@
       <c r="I24" s="9">
         <v>40002</v>
       </c>
-      <c r="J24" s="49" t="s">
+      <c r="J24" s="47" t="s">
         <v>71</v>
       </c>
-      <c r="K24" s="49" t="s">
+      <c r="K24" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="L24" s="4"/>
+      <c r="L24" s="169"/>
     </row>
     <row r="25" spans="1:12" ht="16.5">
-      <c r="A25" s="63">
+      <c r="A25" s="187">
         <v>22</v>
       </c>
-      <c r="B25" s="113"/>
-      <c r="C25" s="96"/>
-      <c r="D25" s="154" t="s">
+      <c r="B25" s="102"/>
+      <c r="C25" s="85"/>
+      <c r="D25" s="134" t="s">
         <v>24</v>
       </c>
-      <c r="E25" s="154"/>
-      <c r="F25" s="154"/>
-      <c r="G25" s="154"/>
+      <c r="E25" s="134"/>
+      <c r="F25" s="134"/>
+      <c r="G25" s="134"/>
       <c r="H25" s="11"/>
       <c r="I25" s="12">
         <v>135936</v>
       </c>
-      <c r="J25" s="49"/>
-      <c r="K25" s="49"/>
-      <c r="L25" s="4"/>
+      <c r="J25" s="47"/>
+      <c r="K25" s="47"/>
+      <c r="L25" s="169"/>
     </row>
     <row r="26" spans="1:12" ht="16.5">
-      <c r="A26" s="63">
+      <c r="A26" s="187">
         <v>23</v>
       </c>
       <c r="B26" s="4"/>
@@ -4733,34 +5990,34 @@
       <c r="I26" s="4"/>
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
-      <c r="L26" s="4"/>
-    </row>
-    <row r="27" spans="1:12" ht="17.25">
-      <c r="A27" s="63">
+      <c r="L26" s="169"/>
+    </row>
+    <row r="27" spans="1:12" ht="34.5">
+      <c r="A27" s="187">
         <v>24</v>
       </c>
-      <c r="B27" s="157" t="s">
+      <c r="B27" s="136" t="s">
         <v>75</v>
       </c>
-      <c r="C27" s="157"/>
-      <c r="D27" s="157"/>
-      <c r="E27" s="64"/>
-      <c r="F27" s="114"/>
-      <c r="G27" s="114"/>
-      <c r="H27" s="64"/>
-      <c r="I27" s="66"/>
-      <c r="J27" s="96"/>
-      <c r="K27" s="115"/>
-      <c r="L27" s="4"/>
+      <c r="C27" s="136"/>
+      <c r="D27" s="136"/>
+      <c r="E27" s="54"/>
+      <c r="F27" s="103"/>
+      <c r="G27" s="103"/>
+      <c r="H27" s="54"/>
+      <c r="I27" s="56"/>
+      <c r="J27" s="85"/>
+      <c r="K27" s="104"/>
+      <c r="L27" s="169"/>
     </row>
     <row r="28" spans="1:12" ht="60">
-      <c r="A28" s="63">
+      <c r="A28" s="187">
         <v>25</v>
       </c>
-      <c r="B28" s="113" t="s">
+      <c r="B28" s="102" t="s">
         <v>76</v>
       </c>
-      <c r="C28" s="49"/>
+      <c r="C28" s="47"/>
       <c r="D28" s="15" t="s">
         <v>50</v>
       </c>
@@ -4779,22 +6036,22 @@
       <c r="I28" s="9">
         <v>59953.440000000002</v>
       </c>
-      <c r="J28" s="49" t="s">
+      <c r="J28" s="47" t="s">
         <v>77</v>
       </c>
-      <c r="K28" s="49" t="s">
+      <c r="K28" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="L28" s="4"/>
+      <c r="L28" s="169"/>
     </row>
     <row r="29" spans="1:12" ht="45">
-      <c r="A29" s="63">
+      <c r="A29" s="187">
         <v>26</v>
       </c>
-      <c r="B29" s="113" t="s">
+      <c r="B29" s="102" t="s">
         <v>79</v>
       </c>
-      <c r="C29" s="49"/>
+      <c r="C29" s="47"/>
       <c r="D29" s="15" t="s">
         <v>50</v>
       </c>
@@ -4813,22 +6070,22 @@
       <c r="I29" s="9">
         <v>44250</v>
       </c>
-      <c r="J29" s="49" t="s">
+      <c r="J29" s="47" t="s">
         <v>77</v>
       </c>
-      <c r="K29" s="49" t="s">
+      <c r="K29" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="L29" s="4"/>
+      <c r="L29" s="169"/>
     </row>
     <row r="30" spans="1:12" ht="60">
-      <c r="A30" s="63">
+      <c r="A30" s="187">
         <v>27</v>
       </c>
-      <c r="B30" s="113" t="s">
+      <c r="B30" s="102" t="s">
         <v>80</v>
       </c>
-      <c r="C30" s="49"/>
+      <c r="C30" s="47"/>
       <c r="D30" s="15" t="s">
         <v>50</v>
       </c>
@@ -4847,55 +6104,55 @@
       <c r="I30" s="9">
         <v>43382.7</v>
       </c>
-      <c r="J30" s="49" t="s">
+      <c r="J30" s="47" t="s">
         <v>77</v>
       </c>
-      <c r="K30" s="49" t="s">
+      <c r="K30" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="L30" s="4"/>
+      <c r="L30" s="169"/>
     </row>
     <row r="31" spans="1:12" ht="16.5">
-      <c r="A31" s="63">
+      <c r="A31" s="187">
         <v>28</v>
       </c>
-      <c r="B31" s="113"/>
-      <c r="C31" s="49"/>
-      <c r="D31" s="154" t="s">
+      <c r="B31" s="102"/>
+      <c r="C31" s="47"/>
+      <c r="D31" s="134" t="s">
         <v>24</v>
       </c>
-      <c r="E31" s="154"/>
-      <c r="F31" s="154"/>
-      <c r="G31" s="154"/>
+      <c r="E31" s="134"/>
+      <c r="F31" s="134"/>
+      <c r="G31" s="134"/>
       <c r="H31" s="11"/>
       <c r="I31" s="12">
         <v>147586.14000000001</v>
       </c>
-      <c r="J31" s="49"/>
-      <c r="K31" s="49"/>
-      <c r="L31" s="4"/>
+      <c r="J31" s="47"/>
+      <c r="K31" s="47"/>
+      <c r="L31" s="169"/>
     </row>
     <row r="32" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A32" s="63">
+      <c r="A32" s="187">
         <v>29</v>
       </c>
-      <c r="B32" s="113"/>
-      <c r="C32" s="49"/>
+      <c r="B32" s="102"/>
+      <c r="C32" s="47"/>
       <c r="D32" s="15"/>
       <c r="E32" s="7"/>
       <c r="F32" s="9"/>
       <c r="G32" s="9"/>
       <c r="H32" s="7"/>
       <c r="I32" s="9"/>
-      <c r="J32" s="49"/>
-      <c r="K32" s="49"/>
-      <c r="L32" s="4"/>
+      <c r="J32" s="47"/>
+      <c r="K32" s="47"/>
+      <c r="L32" s="169"/>
     </row>
     <row r="33" spans="1:12" ht="30.75">
-      <c r="A33" s="63">
+      <c r="A33" s="187">
         <v>30</v>
       </c>
-      <c r="B33" s="48" t="s">
+      <c r="B33" s="46" t="s">
         <v>145</v>
       </c>
       <c r="C33" s="5">
@@ -4924,16 +6181,16 @@
       <c r="J33" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="K33" s="50" t="s">
+      <c r="K33" s="48" t="s">
         <v>144</v>
       </c>
-      <c r="L33" s="4"/>
+      <c r="L33" s="169"/>
     </row>
     <row r="34" spans="1:12" ht="30.75">
-      <c r="A34" s="63">
+      <c r="A34" s="187">
         <v>31</v>
       </c>
-      <c r="B34" s="48" t="s">
+      <c r="B34" s="46" t="s">
         <v>146</v>
       </c>
       <c r="C34" s="5">
@@ -4962,16 +6219,16 @@
       <c r="J34" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="K34" s="50" t="s">
+      <c r="K34" s="48" t="s">
         <v>144</v>
       </c>
-      <c r="L34" s="4"/>
+      <c r="L34" s="169"/>
     </row>
     <row r="35" spans="1:12" ht="30.75">
-      <c r="A35" s="63">
+      <c r="A35" s="187">
         <v>32</v>
       </c>
-      <c r="B35" s="48" t="s">
+      <c r="B35" s="46" t="s">
         <v>147</v>
       </c>
       <c r="C35" s="5">
@@ -5000,57 +6257,57 @@
       <c r="J35" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="K35" s="50" t="s">
+      <c r="K35" s="48" t="s">
         <v>144</v>
       </c>
-      <c r="L35" s="4"/>
+      <c r="L35" s="169"/>
     </row>
     <row r="36" spans="1:12" ht="16.5">
-      <c r="A36" s="63">
+      <c r="A36" s="187">
         <v>33</v>
       </c>
-      <c r="B36" s="96"/>
-      <c r="C36" s="116"/>
-      <c r="D36" s="116"/>
-      <c r="E36" s="162" t="s">
+      <c r="B36" s="85"/>
+      <c r="C36" s="105"/>
+      <c r="D36" s="105"/>
+      <c r="E36" s="106" t="s">
         <v>24</v>
       </c>
-      <c r="F36" s="162"/>
-      <c r="G36" s="162"/>
-      <c r="H36" s="117"/>
-      <c r="I36" s="118">
+      <c r="F36" s="106"/>
+      <c r="G36" s="106"/>
+      <c r="H36" s="106"/>
+      <c r="I36" s="107">
         <f>SUM(I33:I35)</f>
         <v>129505</v>
       </c>
-      <c r="J36" s="117"/>
-      <c r="K36" s="51"/>
-      <c r="L36" s="4"/>
+      <c r="J36" s="106"/>
+      <c r="K36" s="49"/>
+      <c r="L36" s="169"/>
     </row>
     <row r="37" spans="1:12" ht="16.5">
-      <c r="A37" s="63">
+      <c r="A37" s="187">
         <v>34</v>
       </c>
-      <c r="B37" s="160" t="s">
+      <c r="B37" s="139" t="s">
         <v>157</v>
       </c>
-      <c r="C37" s="160"/>
-      <c r="D37" s="160"/>
-      <c r="E37" s="160"/>
-      <c r="F37" s="114"/>
-      <c r="G37" s="114"/>
-      <c r="H37" s="64"/>
-      <c r="I37" s="66" t="s">
+      <c r="C37" s="139"/>
+      <c r="D37" s="139"/>
+      <c r="E37" s="139"/>
+      <c r="F37" s="103"/>
+      <c r="G37" s="103"/>
+      <c r="H37" s="54"/>
+      <c r="I37" s="56" t="s">
         <v>153</v>
       </c>
-      <c r="J37" s="96"/>
-      <c r="K37" s="119"/>
-      <c r="L37" s="4"/>
+      <c r="J37" s="85"/>
+      <c r="K37" s="108"/>
+      <c r="L37" s="169"/>
     </row>
     <row r="38" spans="1:12" ht="30">
-      <c r="A38" s="63">
+      <c r="A38" s="187">
         <v>35</v>
       </c>
-      <c r="B38" s="112" t="s">
+      <c r="B38" s="101" t="s">
         <v>55</v>
       </c>
       <c r="C38" s="5">
@@ -5079,16 +6336,16 @@
       <c r="J38" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="K38" s="50" t="s">
+      <c r="K38" s="48" t="s">
         <v>144</v>
       </c>
-      <c r="L38" s="4"/>
+      <c r="L38" s="169"/>
     </row>
     <row r="39" spans="1:12" ht="30">
-      <c r="A39" s="63">
+      <c r="A39" s="187">
         <v>36</v>
       </c>
-      <c r="B39" s="112" t="s">
+      <c r="B39" s="101" t="s">
         <v>57</v>
       </c>
       <c r="C39" s="5">
@@ -5117,16 +6374,16 @@
       <c r="J39" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="K39" s="50" t="s">
+      <c r="K39" s="48" t="s">
         <v>144</v>
       </c>
-      <c r="L39" s="4"/>
+      <c r="L39" s="169"/>
     </row>
     <row r="40" spans="1:12" ht="30">
-      <c r="A40" s="63">
+      <c r="A40" s="187">
         <v>37</v>
       </c>
-      <c r="B40" s="112" t="s">
+      <c r="B40" s="101" t="s">
         <v>58</v>
       </c>
       <c r="C40" s="5">
@@ -5155,55 +6412,55 @@
       <c r="J40" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="K40" s="50" t="s">
+      <c r="K40" s="48" t="s">
         <v>144</v>
       </c>
-      <c r="L40" s="4"/>
+      <c r="L40" s="169"/>
     </row>
     <row r="41" spans="1:12" ht="16.5">
-      <c r="A41" s="63">
+      <c r="A41" s="187">
         <v>38</v>
       </c>
-      <c r="B41" s="96"/>
-      <c r="C41" s="116"/>
-      <c r="D41" s="116"/>
-      <c r="E41" s="162" t="s">
+      <c r="B41" s="85"/>
+      <c r="C41" s="105"/>
+      <c r="D41" s="105"/>
+      <c r="E41" s="106" t="s">
         <v>24</v>
       </c>
-      <c r="F41" s="162"/>
-      <c r="G41" s="162"/>
-      <c r="H41" s="117"/>
-      <c r="I41" s="118">
+      <c r="F41" s="106"/>
+      <c r="G41" s="106"/>
+      <c r="H41" s="106"/>
+      <c r="I41" s="107">
         <f>SUM(I38:I40)</f>
         <v>118165.2</v>
       </c>
-      <c r="J41" s="117"/>
-      <c r="K41" s="49"/>
-      <c r="L41" s="4"/>
+      <c r="J41" s="106"/>
+      <c r="K41" s="47"/>
+      <c r="L41" s="169"/>
     </row>
     <row r="42" spans="1:12" ht="16.5">
-      <c r="A42" s="63">
+      <c r="A42" s="187">
         <v>39</v>
       </c>
-      <c r="B42" s="168" t="s">
+      <c r="B42" s="144" t="s">
         <v>156</v>
       </c>
-      <c r="C42" s="168"/>
-      <c r="D42" s="168"/>
-      <c r="E42" s="120"/>
-      <c r="F42" s="121"/>
-      <c r="G42" s="121"/>
-      <c r="H42" s="120"/>
-      <c r="I42" s="121"/>
-      <c r="J42" s="122"/>
-      <c r="K42" s="123"/>
-      <c r="L42" s="4"/>
+      <c r="C42" s="144"/>
+      <c r="D42" s="144"/>
+      <c r="E42" s="109"/>
+      <c r="F42" s="110"/>
+      <c r="G42" s="110"/>
+      <c r="H42" s="109"/>
+      <c r="I42" s="110"/>
+      <c r="J42" s="111"/>
+      <c r="K42" s="112"/>
+      <c r="L42" s="169"/>
     </row>
     <row r="43" spans="1:12" ht="30">
-      <c r="A43" s="63">
+      <c r="A43" s="187">
         <v>40</v>
       </c>
-      <c r="B43" s="112" t="s">
+      <c r="B43" s="101" t="s">
         <v>55</v>
       </c>
       <c r="C43" s="5">
@@ -5230,16 +6487,16 @@
       <c r="J43" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K43" s="68" t="s">
+      <c r="K43" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="L43" s="4"/>
+      <c r="L43" s="169"/>
     </row>
     <row r="44" spans="1:12" ht="30">
-      <c r="A44" s="63">
+      <c r="A44" s="187">
         <v>41</v>
       </c>
-      <c r="B44" s="112" t="s">
+      <c r="B44" s="101" t="s">
         <v>57</v>
       </c>
       <c r="C44" s="5">
@@ -5266,16 +6523,16 @@
       <c r="J44" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K44" s="68" t="s">
+      <c r="K44" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="L44" s="4"/>
+      <c r="L44" s="169"/>
     </row>
     <row r="45" spans="1:12" ht="30">
-      <c r="A45" s="63">
+      <c r="A45" s="187">
         <v>42</v>
       </c>
-      <c r="B45" s="112" t="s">
+      <c r="B45" s="101" t="s">
         <v>58</v>
       </c>
       <c r="C45" s="5">
@@ -5302,33 +6559,33 @@
       <c r="J45" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K45" s="68" t="s">
+      <c r="K45" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="L45" s="4"/>
+      <c r="L45" s="169"/>
     </row>
     <row r="46" spans="1:12" ht="16.5">
-      <c r="A46" s="63">
+      <c r="A46" s="187">
         <v>43</v>
       </c>
-      <c r="B46" s="113"/>
+      <c r="B46" s="102"/>
       <c r="C46" s="5"/>
-      <c r="D46" s="154" t="s">
+      <c r="D46" s="134" t="s">
         <v>24</v>
       </c>
-      <c r="E46" s="154"/>
-      <c r="F46" s="154"/>
-      <c r="G46" s="154"/>
+      <c r="E46" s="134"/>
+      <c r="F46" s="134"/>
+      <c r="G46" s="134"/>
       <c r="H46" s="11"/>
       <c r="I46" s="12">
         <v>124608</v>
       </c>
       <c r="J46" s="9"/>
-      <c r="K46" s="68"/>
-      <c r="L46" s="4"/>
+      <c r="K46" s="58"/>
+      <c r="L46" s="169"/>
     </row>
     <row r="47" spans="1:12" ht="16.5">
-      <c r="A47" s="63">
+      <c r="A47" s="187">
         <v>44</v>
       </c>
       <c r="B47" s="4"/>
@@ -5341,31 +6598,31 @@
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
       <c r="K47" s="4"/>
-      <c r="L47" s="4"/>
+      <c r="L47" s="169"/>
     </row>
     <row r="48" spans="1:12" ht="16.5">
-      <c r="A48" s="63">
+      <c r="A48" s="187">
         <v>45</v>
       </c>
-      <c r="B48" s="161" t="s">
+      <c r="B48" s="140" t="s">
         <v>155</v>
       </c>
-      <c r="C48" s="161"/>
-      <c r="D48" s="161"/>
-      <c r="E48" s="161"/>
-      <c r="F48" s="114"/>
-      <c r="G48" s="114"/>
-      <c r="H48" s="64"/>
-      <c r="I48" s="66"/>
-      <c r="J48" s="96"/>
-      <c r="K48" s="115"/>
-      <c r="L48" s="4"/>
+      <c r="C48" s="140"/>
+      <c r="D48" s="140"/>
+      <c r="E48" s="140"/>
+      <c r="F48" s="103"/>
+      <c r="G48" s="103"/>
+      <c r="H48" s="54"/>
+      <c r="I48" s="56"/>
+      <c r="J48" s="85"/>
+      <c r="K48" s="104"/>
+      <c r="L48" s="169"/>
     </row>
     <row r="49" spans="1:12" ht="30">
-      <c r="A49" s="63">
+      <c r="A49" s="187">
         <v>46</v>
       </c>
-      <c r="B49" s="112" t="s">
+      <c r="B49" s="101" t="s">
         <v>55</v>
       </c>
       <c r="C49" s="5">
@@ -5392,16 +6649,16 @@
       <c r="J49" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="K49" s="124" t="s">
+      <c r="K49" s="113" t="s">
         <v>82</v>
       </c>
-      <c r="L49" s="4"/>
+      <c r="L49" s="169"/>
     </row>
     <row r="50" spans="1:12" ht="30">
-      <c r="A50" s="63">
+      <c r="A50" s="187">
         <v>47</v>
       </c>
-      <c r="B50" s="112" t="s">
+      <c r="B50" s="101" t="s">
         <v>57</v>
       </c>
       <c r="C50" s="5">
@@ -5428,16 +6685,16 @@
       <c r="J50" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="K50" s="124" t="s">
+      <c r="K50" s="113" t="s">
         <v>82</v>
       </c>
-      <c r="L50" s="4"/>
+      <c r="L50" s="169"/>
     </row>
     <row r="51" spans="1:12" ht="30">
-      <c r="A51" s="63">
+      <c r="A51" s="187">
         <v>48</v>
       </c>
-      <c r="B51" s="112" t="s">
+      <c r="B51" s="101" t="s">
         <v>58</v>
       </c>
       <c r="C51" s="5">
@@ -5464,30 +6721,30 @@
       <c r="J51" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="K51" s="124" t="s">
+      <c r="K51" s="113" t="s">
         <v>82</v>
       </c>
-      <c r="L51" s="4"/>
+      <c r="L51" s="169"/>
     </row>
     <row r="52" spans="1:12" ht="16.5">
-      <c r="A52" s="63">
+      <c r="A52" s="190">
         <v>49</v>
       </c>
-      <c r="B52" s="96"/>
-      <c r="C52" s="49"/>
-      <c r="D52" s="49"/>
-      <c r="E52" s="156" t="s">
+      <c r="B52" s="191"/>
+      <c r="C52" s="192"/>
+      <c r="D52" s="192"/>
+      <c r="E52" s="193" t="s">
         <v>24</v>
       </c>
-      <c r="F52" s="156"/>
-      <c r="G52" s="156"/>
-      <c r="H52" s="125"/>
-      <c r="I52" s="118">
+      <c r="F52" s="193"/>
+      <c r="G52" s="193"/>
+      <c r="H52" s="193"/>
+      <c r="I52" s="194">
         <v>152821.79999999999</v>
       </c>
-      <c r="J52" s="125"/>
-      <c r="K52" s="49"/>
-      <c r="L52" s="4"/>
+      <c r="J52" s="193"/>
+      <c r="K52" s="192"/>
+      <c r="L52" s="170"/>
     </row>
     <row r="56" spans="1:12">
       <c r="I56" t="s">
@@ -5495,25 +6752,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="B4:D4"/>
+  <mergeCells count="1">
     <mergeCell ref="C1:I2"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="D46:G46"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="E52:G52"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="D25:G25"/>
-    <mergeCell ref="D31:G31"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="E36:G36"/>
-    <mergeCell ref="B37:E37"/>
-    <mergeCell ref="E41:G41"/>
   </mergeCells>
   <phoneticPr fontId="58" type="noConversion"/>
   <hyperlinks>
@@ -5523,6 +6763,9 @@
     <hyperlink ref="K39:K40" r:id="rId4" display="tel:(984) 984-7406" xr:uid="{D67900C7-64FE-4513-A08A-4645E989E8A7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId5"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -5532,17 +6775,18 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="48.85546875" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" customWidth="1"/>
     <col min="4" max="4" width="14.7109375" customWidth="1"/>
-    <col min="6" max="6" width="17.85546875" customWidth="1"/>
-    <col min="7" max="7" width="16.85546875" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" customWidth="1"/>
+    <col min="7" max="7" width="20.7109375" customWidth="1"/>
     <col min="8" max="8" width="15.42578125" customWidth="1"/>
     <col min="9" max="9" width="12.7109375" customWidth="1"/>
-    <col min="10" max="10" width="20.140625" customWidth="1"/>
+    <col min="10" max="10" width="22.5703125" customWidth="1"/>
     <col min="11" max="11" width="18.42578125" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="16.7109375" customWidth="1"/>
-    <col min="14" max="14" width="17.85546875" customWidth="1"/>
+    <col min="14" max="14" width="28.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -5562,64 +6806,64 @@
       <c r="N1" s="4"/>
     </row>
     <row r="2" spans="1:14" ht="18.75">
-      <c r="A2" s="169" t="s">
+      <c r="A2" s="164" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="170"/>
-      <c r="C2" s="170"/>
-      <c r="D2" s="170"/>
-      <c r="E2" s="170"/>
-      <c r="F2" s="170"/>
-      <c r="G2" s="170"/>
-      <c r="H2" s="170"/>
-      <c r="I2" s="170"/>
-      <c r="J2" s="170"/>
-      <c r="K2" s="170"/>
-      <c r="L2" s="170"/>
-      <c r="M2" s="170"/>
+      <c r="B2" s="165"/>
+      <c r="C2" s="165"/>
+      <c r="D2" s="165"/>
+      <c r="E2" s="165"/>
+      <c r="F2" s="165"/>
+      <c r="G2" s="165"/>
+      <c r="H2" s="165"/>
+      <c r="I2" s="165"/>
+      <c r="J2" s="165"/>
+      <c r="K2" s="165"/>
+      <c r="L2" s="165"/>
+      <c r="M2" s="165"/>
       <c r="N2" s="4"/>
     </row>
     <row r="3" spans="1:14" ht="30">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="184" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="184" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="184" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="184" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="29" t="s">
+      <c r="E3" s="184" t="s">
         <v>84</v>
       </c>
-      <c r="F3" s="29" t="s">
+      <c r="F3" s="184" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="52" t="s">
+      <c r="G3" s="185" t="s">
         <v>85</v>
       </c>
-      <c r="H3" s="29" t="s">
+      <c r="H3" s="184" t="s">
         <v>86</v>
       </c>
-      <c r="I3" s="29" t="s">
+      <c r="I3" s="184" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="30" t="s">
+      <c r="J3" s="186" t="s">
         <v>87</v>
       </c>
-      <c r="K3" s="52" t="s">
+      <c r="K3" s="185" t="s">
         <v>158</v>
       </c>
-      <c r="L3" s="29" t="s">
+      <c r="L3" s="184" t="s">
         <v>89</v>
       </c>
-      <c r="M3" s="29" t="s">
+      <c r="M3" s="184" t="s">
         <v>90</v>
       </c>
-      <c r="N3" s="52" t="s">
+      <c r="N3" s="185" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5654,7 +6898,7 @@
         <f>G4*(1+I4/100)</f>
         <v>660.8</v>
       </c>
-      <c r="K4" s="45">
+      <c r="K4" s="43">
         <f>E4*J4</f>
         <v>16520</v>
       </c>
@@ -5697,7 +6941,7 @@
         <f>G5*(1+I5/100)</f>
         <v>678.5</v>
       </c>
-      <c r="K5" s="45">
+      <c r="K5" s="43">
         <f>E5*J5</f>
         <v>16962.5</v>
       </c>
@@ -5713,49 +6957,49 @@
       <c r="A6" s="25">
         <v>3</v>
       </c>
-      <c r="B6" s="33" t="s">
+      <c r="B6" s="31" t="s">
         <v>91</v>
       </c>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47" t="s">
+      <c r="C6" s="45"/>
+      <c r="D6" s="45" t="s">
         <v>96</v>
       </c>
-      <c r="E6" s="47">
+      <c r="E6" s="45">
         <v>30</v>
       </c>
-      <c r="F6" s="47">
+      <c r="F6" s="45">
         <v>10.9</v>
       </c>
-      <c r="G6" s="47">
+      <c r="G6" s="45">
         <f>50*F6</f>
         <v>545</v>
       </c>
-      <c r="H6" s="47" t="s">
+      <c r="H6" s="45" t="s">
         <v>93</v>
       </c>
-      <c r="I6" s="47">
+      <c r="I6" s="45">
         <v>5</v>
       </c>
-      <c r="J6" s="47">
+      <c r="J6" s="45">
         <f>G6*(1+I6/100)</f>
         <v>572.25</v>
       </c>
-      <c r="K6" s="45">
+      <c r="K6" s="43">
         <f>E6*J6</f>
         <v>17167.5</v>
       </c>
-      <c r="L6" s="47" t="s">
+      <c r="L6" s="45" t="s">
         <v>97</v>
       </c>
-      <c r="M6" s="47">
+      <c r="M6" s="45">
         <v>7989960246</v>
       </c>
-      <c r="N6" s="59" t="s">
+      <c r="N6" s="52" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15.75">
-      <c r="A7" s="31"/>
+      <c r="A7" s="29"/>
       <c r="C7" s="28"/>
       <c r="D7" s="28"/>
       <c r="E7" s="28"/>
@@ -5764,7 +7008,7 @@
       <c r="H7" s="28"/>
       <c r="I7" s="28"/>
       <c r="J7" s="28"/>
-      <c r="K7" s="46"/>
+      <c r="K7" s="44"/>
       <c r="L7" s="28"/>
       <c r="M7" s="28"/>
     </row>
@@ -5773,59 +7017,63 @@
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F5F7FD4-4BC8-42C2-979E-711A9720CDD8}">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="43.140625" customWidth="1"/>
     <col min="3" max="3" width="17.42578125" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="22.140625" customWidth="1"/>
-    <col min="6" max="6" width="18.5703125" customWidth="1"/>
+    <col min="6" max="6" width="23.42578125" customWidth="1"/>
     <col min="7" max="7" width="14.85546875" customWidth="1"/>
     <col min="8" max="8" width="16.28515625" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" customWidth="1"/>
+    <col min="9" max="9" width="17.140625" customWidth="1"/>
     <col min="10" max="10" width="18.28515625" customWidth="1"/>
-    <col min="11" max="11" width="17.5703125" customWidth="1"/>
-    <col min="12" max="12" width="20" customWidth="1"/>
+    <col min="11" max="11" width="18.7109375" customWidth="1"/>
+    <col min="12" max="12" width="33.28515625" customWidth="1"/>
+    <col min="13" max="13" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="4"/>
       <c r="B1" s="4"/>
-      <c r="C1" s="171" t="s">
+      <c r="C1" s="166" t="s">
         <v>98</v>
       </c>
-      <c r="D1" s="172"/>
-      <c r="E1" s="172"/>
-      <c r="F1" s="172"/>
-      <c r="G1" s="172"/>
-      <c r="H1" s="172"/>
-      <c r="I1" s="172"/>
+      <c r="D1" s="167"/>
+      <c r="E1" s="167"/>
+      <c r="F1" s="167"/>
+      <c r="G1" s="167"/>
+      <c r="H1" s="167"/>
+      <c r="I1" s="167"/>
       <c r="J1" s="4"/>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
-      <c r="C2" s="172"/>
-      <c r="D2" s="172"/>
-      <c r="E2" s="172"/>
-      <c r="F2" s="172"/>
-      <c r="G2" s="172"/>
-      <c r="H2" s="172"/>
-      <c r="I2" s="172"/>
+      <c r="C2" s="167"/>
+      <c r="D2" s="167"/>
+      <c r="E2" s="167"/>
+      <c r="F2" s="167"/>
+      <c r="G2" s="167"/>
+      <c r="H2" s="167"/>
+      <c r="I2" s="167"/>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
     </row>
-    <row r="3" spans="1:12" ht="33">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:13" ht="33">
+      <c r="A3" s="182" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -5861,14 +7109,17 @@
       <c r="L3" s="1" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="173" t="s">
+      <c r="M3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="183" t="s">
         <v>100</v>
       </c>
-      <c r="B4" s="173"/>
-      <c r="C4" s="173"/>
-      <c r="D4" s="173"/>
+      <c r="B4" s="145"/>
+      <c r="C4" s="145"/>
+      <c r="D4" s="145"/>
       <c r="E4" s="25"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
@@ -5878,11 +7129,11 @@
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
     </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="25">
+    <row r="5" spans="1:13">
+      <c r="A5" s="168">
         <v>1</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="30" t="s">
         <v>101</v>
       </c>
       <c r="C5" s="25"/>
@@ -5914,8 +7165,8 @@
       </c>
       <c r="L5" s="4"/>
     </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="25">
+    <row r="6" spans="1:13">
+      <c r="A6" s="168">
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -5950,18 +7201,18 @@
       </c>
       <c r="L6" s="4"/>
     </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="25">
+    <row r="7" spans="1:13">
+      <c r="A7" s="168">
         <v>3</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="152" t="s">
+      <c r="D7" s="31"/>
+      <c r="E7" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="152"/>
-      <c r="G7" s="152"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
       <c r="H7" s="24"/>
       <c r="I7" s="24">
         <f>SUM(I5:I6)</f>
@@ -5971,13 +7222,13 @@
       <c r="K7" s="25"/>
       <c r="L7" s="4"/>
     </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="173" t="s">
+    <row r="8" spans="1:13">
+      <c r="A8" s="183" t="s">
         <v>107</v>
       </c>
-      <c r="B8" s="173"/>
-      <c r="C8" s="173"/>
-      <c r="D8" s="173"/>
+      <c r="B8" s="145"/>
+      <c r="C8" s="145"/>
+      <c r="D8" s="145"/>
       <c r="E8" s="25"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
@@ -5987,11 +7238,11 @@
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
     </row>
-    <row r="9" spans="1:12" ht="30">
-      <c r="A9" s="25">
+    <row r="9" spans="1:13" ht="30">
+      <c r="A9" s="168">
         <v>4</v>
       </c>
-      <c r="B9" s="34" t="s">
+      <c r="B9" s="32" t="s">
         <v>108</v>
       </c>
       <c r="C9" s="6"/>
@@ -6021,12 +7272,12 @@
       <c r="K9" s="6">
         <v>9848196449</v>
       </c>
-      <c r="L9" s="58" t="s">
+      <c r="L9" s="51" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="25">
+    <row r="10" spans="1:13">
+      <c r="A10" s="168">
         <v>5</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -6061,18 +7312,18 @@
       </c>
       <c r="L10" s="4"/>
     </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="25">
+    <row r="11" spans="1:13">
+      <c r="A11" s="168">
         <v>6</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="152" t="s">
+      <c r="D11" s="31"/>
+      <c r="E11" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="152"/>
-      <c r="G11" s="152"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="24"/>
       <c r="H11" s="24"/>
       <c r="I11" s="24">
         <f>SUM(I9:I10)</f>
@@ -6083,325 +7334,348 @@
       <c r="L11" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:L3" xr:uid="{2F5F7FD4-4BC8-42C2-979E-711A9720CDD8}"/>
-  <mergeCells count="5">
+  <mergeCells count="1">
     <mergeCell ref="C1:I2"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="E11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA27117F-8538-4DB9-BEB6-56257DF569C4}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
     <col min="2" max="2" width="69.28515625" customWidth="1"/>
     <col min="3" max="3" width="16.140625" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
     <col min="5" max="5" width="17.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.5703125" customWidth="1"/>
     <col min="7" max="7" width="28.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21">
-      <c r="A1" s="174" t="s">
+      <c r="A1" s="155" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="175"/>
-      <c r="C1" s="175"/>
-      <c r="D1" s="175"/>
-      <c r="E1" s="175"/>
-      <c r="F1" s="175"/>
-      <c r="G1" s="175"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75">
-      <c r="A3" s="176" t="s">
+      <c r="B1" s="156"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="156"/>
+      <c r="E1" s="156"/>
+      <c r="F1" s="156"/>
+      <c r="G1" s="156"/>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E2" t="s">
+        <v>190</v>
+      </c>
+      <c r="F2" t="s">
+        <v>191</v>
+      </c>
+      <c r="G2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.75">
+      <c r="A4" s="146" t="s">
         <v>181</v>
       </c>
-      <c r="B3" s="176"/>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="35" t="s">
+      <c r="B4" s="146"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="B4" s="35" t="s">
+      <c r="B5" s="33" t="s">
         <v>113</v>
       </c>
-      <c r="C4" s="35" t="s">
+      <c r="C5" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="D4" s="35" t="s">
+      <c r="D5" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="35" t="s">
+      <c r="E5" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="F4" s="35" t="s">
+      <c r="F5" s="33" t="s">
         <v>116</v>
       </c>
-      <c r="G4" s="35" t="s">
+      <c r="G5" s="33" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="36">
+    <row r="6" spans="1:7">
+      <c r="A6" s="34">
         <v>1</v>
       </c>
-      <c r="B5" s="37" t="s">
+      <c r="B6" s="35" t="s">
         <v>118</v>
       </c>
-      <c r="C5" s="36" t="s">
+      <c r="C6" s="34" t="s">
         <v>119</v>
       </c>
-      <c r="D5" s="36">
+      <c r="D6" s="34">
         <v>1</v>
       </c>
-      <c r="E5" s="38">
+      <c r="E6" s="36">
         <v>135000</v>
       </c>
-      <c r="F5" s="38">
+      <c r="F6" s="36">
         <v>130000</v>
       </c>
-      <c r="G5" s="38">
-        <f>D5*F5</f>
+      <c r="G6" s="36">
+        <f>D6*F6</f>
         <v>130000</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="36">
+    <row r="7" spans="1:7">
+      <c r="A7" s="34">
         <v>2</v>
       </c>
-      <c r="B6" s="37" t="s">
+      <c r="B7" s="35" t="s">
         <v>120</v>
       </c>
-      <c r="C6" s="36" t="s">
+      <c r="C7" s="34" t="s">
         <v>121</v>
       </c>
-      <c r="D6" s="36">
+      <c r="D7" s="34">
         <v>1</v>
       </c>
-      <c r="E6" s="38">
+      <c r="E7" s="36">
         <v>125000</v>
       </c>
-      <c r="F6" s="38">
+      <c r="F7" s="36">
         <v>120000</v>
       </c>
-      <c r="G6" s="38">
-        <f>D6*F6</f>
+      <c r="G7" s="36">
+        <f>D7*F7</f>
         <v>120000</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
-      <c r="B7" s="39" t="s">
+    <row r="8" spans="1:7">
+      <c r="B8" s="37" t="s">
         <v>122</v>
       </c>
-      <c r="G7" s="40">
-        <f>SUM(G5:G6)</f>
+      <c r="G8" s="38">
+        <f>SUM(G6:G7)</f>
         <v>250000</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
-      <c r="B8" s="39" t="s">
+    <row r="9" spans="1:7">
+      <c r="B9" s="37" t="s">
         <v>123</v>
       </c>
-      <c r="G8" s="40">
-        <f>G7*0.18</f>
+      <c r="G9" s="38">
+        <f>G8*0.18</f>
         <v>45000</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15.75" thickBot="1">
-      <c r="B9" s="39" t="s">
+    <row r="10" spans="1:7" ht="15.75" thickBot="1">
+      <c r="B10" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="G9" s="41">
-        <f>G7+G8</f>
+      <c r="G10" s="39">
+        <f>G8+G9</f>
         <v>295000</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15.75" thickTop="1"/>
-    <row r="11" spans="1:7">
-      <c r="B11" s="39" t="s">
+    <row r="11" spans="1:7" ht="15.75" thickTop="1"/>
+    <row r="12" spans="1:7">
+      <c r="B12" s="37" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
-      <c r="B12" s="42" t="s">
+    <row r="13" spans="1:7">
+      <c r="B13" s="40" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
-      <c r="B13" s="42" t="s">
+    <row r="14" spans="1:7">
+      <c r="B14" s="40" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
-      <c r="B14" s="42" t="s">
+    <row r="15" spans="1:7">
+      <c r="B15" s="40" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="24.75">
-      <c r="B15" s="43" t="s">
+    <row r="16" spans="1:7" ht="24.75">
+      <c r="B16" s="41" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
-      <c r="B16" s="42" t="s">
+    <row r="17" spans="1:7">
+      <c r="B17" s="40" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
-      <c r="B17" s="42" t="s">
+    <row r="18" spans="1:7">
+      <c r="B18" s="40" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15.75">
-      <c r="A20" s="176" t="s">
+    <row r="21" spans="1:7" ht="15.75">
+      <c r="A21" s="146" t="s">
         <v>180</v>
       </c>
-      <c r="B20" s="177"/>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="35" t="s">
+      <c r="B21" s="147"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="B21" s="35" t="s">
+      <c r="B22" s="33" t="s">
         <v>113</v>
       </c>
-      <c r="C21" s="35" t="s">
+      <c r="C22" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="D21" s="35" t="s">
+      <c r="D22" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="E21" s="35" t="s">
+      <c r="E22" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="F21" s="35" t="s">
+      <c r="F22" s="33" t="s">
         <v>116</v>
       </c>
-      <c r="G21" s="35" t="s">
+      <c r="G22" s="33" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="30">
-      <c r="A22" s="36">
+    <row r="23" spans="1:7" ht="30">
+      <c r="A23" s="34">
         <v>1</v>
       </c>
-      <c r="B22" s="44" t="s">
+      <c r="B23" s="42" t="s">
         <v>132</v>
       </c>
-      <c r="C22" s="36" t="s">
+      <c r="C23" s="34" t="s">
         <v>133</v>
       </c>
-      <c r="D22" s="36">
+      <c r="D23" s="34">
         <v>1</v>
       </c>
-      <c r="E22" s="38">
+      <c r="E23" s="36">
         <v>88000</v>
       </c>
-      <c r="F22" s="38">
+      <c r="F23" s="36">
         <v>88000</v>
       </c>
-      <c r="G22" s="38">
-        <f>D22*F22</f>
+      <c r="G23" s="36">
+        <f>D23*F23</f>
         <v>88000</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="36">
+    <row r="24" spans="1:7">
+      <c r="A24" s="34">
         <v>2</v>
       </c>
-      <c r="B23" s="37" t="s">
+      <c r="B24" s="35" t="s">
         <v>134</v>
       </c>
-      <c r="C23" s="36" t="s">
+      <c r="C24" s="34" t="s">
         <v>135</v>
       </c>
-      <c r="D23" s="36">
+      <c r="D24" s="34">
         <v>1</v>
       </c>
-      <c r="E23" s="38">
+      <c r="E24" s="36">
         <v>5500</v>
       </c>
-      <c r="F23" s="38">
+      <c r="F24" s="36">
         <v>5500</v>
       </c>
-      <c r="G23" s="38">
-        <f>D23*F23</f>
+      <c r="G24" s="36">
+        <f>D24*F24</f>
         <v>5500</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
-      <c r="B24" s="39" t="s">
+    <row r="25" spans="1:7">
+      <c r="B25" s="37" t="s">
         <v>122</v>
       </c>
-      <c r="G24" s="40">
-        <f>SUM(G22:G23)</f>
+      <c r="G25" s="38">
+        <f>SUM(G23:G24)</f>
         <v>93500</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
-      <c r="B25" s="39" t="s">
+    <row r="26" spans="1:7">
+      <c r="B26" s="37" t="s">
         <v>123</v>
       </c>
-      <c r="G25" s="40">
-        <f>G24*0.18</f>
+      <c r="G26" s="38">
+        <f>G25*0.18</f>
         <v>16830</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15.75" thickBot="1">
-      <c r="B26" s="39" t="s">
+    <row r="27" spans="1:7" ht="15.75" thickBot="1">
+      <c r="B27" s="37" t="s">
         <v>136</v>
       </c>
-      <c r="G26" s="41">
-        <f>G24+G25</f>
+      <c r="G27" s="39">
+        <f>G25+G26</f>
         <v>110330</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15.75" thickTop="1"/>
-    <row r="28" spans="1:7">
-      <c r="B28" s="39" t="s">
+    <row r="28" spans="1:7" ht="15.75" thickTop="1"/>
+    <row r="29" spans="1:7">
+      <c r="B29" s="37" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
-      <c r="B29" s="42" t="s">
+    <row r="30" spans="1:7">
+      <c r="B30" s="40" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
-      <c r="B30" s="42" t="s">
+    <row r="31" spans="1:7">
+      <c r="B31" s="40" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
-      <c r="B31" s="42" t="s">
+    <row r="32" spans="1:7">
+      <c r="B32" s="40" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
-      <c r="B32" s="42" t="s">
+    <row r="33" spans="2:2">
+      <c r="B33" s="40" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="33" spans="2:2">
-      <c r="B33" s="42" t="s">
+    <row r="34" spans="2:2">
+      <c r="B34" s="40" t="s">
         <v>141</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A20:B20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -6413,84 +7687,84 @@
     <col min="2" max="2" width="57.140625" customWidth="1"/>
     <col min="3" max="3" width="17.42578125" customWidth="1"/>
     <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="6" max="6" width="17.140625" customWidth="1"/>
+    <col min="6" max="6" width="21.85546875" customWidth="1"/>
     <col min="7" max="7" width="19.7109375" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="15" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="15.42578125" customWidth="1"/>
     <col min="10" max="10" width="16.5703125" customWidth="1"/>
     <col min="11" max="11" width="16.42578125" customWidth="1"/>
-    <col min="12" max="12" width="20" customWidth="1"/>
+    <col min="12" max="12" width="28.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18.75">
-      <c r="A1" s="169" t="s">
+      <c r="A1" s="171" t="s">
         <v>159</v>
       </c>
-      <c r="B1" s="170"/>
-      <c r="C1" s="170"/>
-      <c r="D1" s="170"/>
-      <c r="E1" s="170"/>
-      <c r="F1" s="170"/>
-      <c r="G1" s="170"/>
-      <c r="H1" s="170"/>
-      <c r="I1" s="170"/>
-      <c r="J1" s="170"/>
-      <c r="K1" s="170"/>
+      <c r="B1" s="172"/>
+      <c r="C1" s="172"/>
+      <c r="D1" s="172"/>
+      <c r="E1" s="172"/>
+      <c r="F1" s="172"/>
+      <c r="G1" s="172"/>
+      <c r="H1" s="172"/>
+      <c r="I1" s="172"/>
+      <c r="J1" s="172"/>
+      <c r="K1" s="173"/>
       <c r="L1" s="4"/>
     </row>
     <row r="2" spans="1:12" ht="30">
-      <c r="A2" s="54" t="s">
+      <c r="A2" s="177" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="177" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="54" t="s">
+      <c r="C2" s="177" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="57" t="s">
+      <c r="D2" s="178" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="55" t="s">
+      <c r="E2" s="179" t="s">
         <v>161</v>
       </c>
-      <c r="F2" s="56" t="s">
+      <c r="F2" s="180" t="s">
         <v>178</v>
       </c>
-      <c r="G2" s="129" t="s">
+      <c r="G2" s="181" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="54" t="s">
+      <c r="H2" s="177" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="56" t="s">
+      <c r="I2" s="180" t="s">
         <v>158</v>
       </c>
-      <c r="J2" s="55" t="s">
+      <c r="J2" s="179" t="s">
         <v>162</v>
       </c>
-      <c r="K2" s="54" t="s">
+      <c r="K2" s="177" t="s">
         <v>90</v>
       </c>
-      <c r="L2" s="56" t="s">
+      <c r="L2" s="180" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15.75">
-      <c r="A3" s="139"/>
-      <c r="B3" s="178" t="s">
+      <c r="A3" s="126"/>
+      <c r="B3" s="174" t="s">
         <v>176</v>
       </c>
-      <c r="C3" s="179"/>
-      <c r="D3" s="137"/>
-      <c r="E3" s="138"/>
-      <c r="F3" s="138"/>
-      <c r="G3" s="139"/>
-      <c r="H3" s="136"/>
-      <c r="I3" s="140"/>
-      <c r="J3" s="138"/>
-      <c r="K3" s="136"/>
-      <c r="L3" s="140"/>
+      <c r="C3" s="175"/>
+      <c r="D3" s="124"/>
+      <c r="E3" s="125"/>
+      <c r="F3" s="125"/>
+      <c r="G3" s="126"/>
+      <c r="H3" s="123"/>
+      <c r="I3" s="127"/>
+      <c r="J3" s="125"/>
+      <c r="K3" s="123"/>
+      <c r="L3" s="127"/>
     </row>
     <row r="4" spans="1:12" ht="15.75">
       <c r="A4" s="6">
@@ -6503,7 +7777,7 @@
         <v>7318</v>
       </c>
       <c r="D4" s="6"/>
-      <c r="E4" s="53">
+      <c r="E4" s="50">
         <v>1000</v>
       </c>
       <c r="F4" s="6">
@@ -6516,7 +7790,7 @@
       <c r="H4" s="6">
         <v>18</v>
       </c>
-      <c r="I4" s="45">
+      <c r="I4" s="43">
         <f>G4*(1+H4/100)</f>
         <v>11682</v>
       </c>
@@ -6526,25 +7800,25 @@
       <c r="K4" s="6">
         <v>9100868002</v>
       </c>
-      <c r="L4" s="59" t="s">
+      <c r="L4" s="52" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15.75">
       <c r="A5" s="6"/>
-      <c r="B5" s="178" t="s">
+      <c r="B5" s="174" t="s">
         <v>177</v>
       </c>
-      <c r="C5" s="152"/>
+      <c r="C5" s="176"/>
       <c r="D5" s="6"/>
-      <c r="E5" s="53"/>
+      <c r="E5" s="50"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
-      <c r="I5" s="45"/>
+      <c r="I5" s="43"/>
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
-      <c r="L5" s="141"/>
+      <c r="L5" s="128"/>
     </row>
     <row r="6" spans="1:12" ht="15.75">
       <c r="A6" s="6">
@@ -6557,7 +7831,7 @@
         <v>7318</v>
       </c>
       <c r="D6" s="6"/>
-      <c r="E6" s="53">
+      <c r="E6" s="50">
         <v>1000</v>
       </c>
       <c r="F6" s="6">
@@ -6570,7 +7844,7 @@
       <c r="H6" s="6">
         <v>18</v>
       </c>
-      <c r="I6" s="45">
+      <c r="I6" s="43">
         <f>G6*(1+H6/100)</f>
         <v>13924</v>
       </c>
@@ -6584,27 +7858,28 @@
     </row>
     <row r="7" spans="1:12" ht="15.75">
       <c r="A7" s="25"/>
-      <c r="B7" s="33"/>
-      <c r="C7" s="47"/>
+      <c r="B7" s="31"/>
+      <c r="C7" s="45"/>
       <c r="D7" s="6"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
-      <c r="G7" s="47"/>
-      <c r="H7" s="47"/>
-      <c r="I7" s="45"/>
-      <c r="J7" s="47"/>
-      <c r="K7" s="47"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="45"/>
+      <c r="K7" s="45"/>
       <c r="L7" s="4"/>
     </row>
     <row r="20" spans="3:3">
-      <c r="C20" s="142"/>
+      <c r="C20" s="129"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B5:C5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>